--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-ballot</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:44:45+00:00</t>
+    <t>2024-03-25T10:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:59:40+00:00</t>
+    <t>2024-03-25T11:06:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5706" uniqueCount="625">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5633" uniqueCount="626">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T08:02:06+00:00</t>
+    <t>2024-05-23T12:05:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -977,40 +977,125 @@
     <t>Organization.identifier:idNatSt.assigner</t>
   </si>
   <si>
-    <t>Organization.identifier:sirene</t>
-  </si>
-  <si>
-    <t>sirene</t>
-  </si>
-  <si>
-    <t>Identifiant SIREN (9 chiffres) ou SIRET (14 chiffres)</t>
-  </si>
-  <si>
-    <t>Organization.identifier:sirene.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier:sirene.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier:sirene.use</t>
-  </si>
-  <si>
-    <t>Organization.identifier:sirene.type</t>
-  </si>
-  <si>
-    <t>Organization.identifier:sirene.type.id</t>
+    <t>Organization.identifier:siren</t>
+  </si>
+  <si>
+    <t>siren</t>
+  </si>
+  <si>
+    <t>Identifiant SIREN (9 chiffres)</t>
+  </si>
+  <si>
+    <t>Organization.identifier:siren.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier:siren.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier:siren.use</t>
+  </si>
+  <si>
+    <t>Organization.identifier:siren.type</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203"/&gt;
+    &lt;code value="SIREN"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>Organization.identifier:siren.system</t>
+  </si>
+  <si>
+    <t>https://sirene.fr</t>
+  </si>
+  <si>
+    <t>Organization.identifier:siren.value</t>
+  </si>
+  <si>
+    <t>Organization.identifier:siren.period</t>
+  </si>
+  <si>
+    <t>Organization.identifier:siren.assigner</t>
+  </si>
+  <si>
+    <t>Organization.identifier:siret</t>
+  </si>
+  <si>
+    <t>siret</t>
+  </si>
+  <si>
+    <t>Identifiant SIRET (14 chiffres)</t>
+  </si>
+  <si>
+    <t>Organization.identifier:siret.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier:siret.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier:siret.use</t>
+  </si>
+  <si>
+    <t>Organization.identifier:siret.type</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203"/&gt;
+    &lt;code value="SIRET"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>Organization.identifier:siret.system</t>
+  </si>
+  <si>
+    <t>Organization.identifier:siret.value</t>
+  </si>
+  <si>
+    <t>Organization.identifier:siret.period</t>
+  </si>
+  <si>
+    <t>Organization.identifier:siret.assigner</t>
+  </si>
+  <si>
+    <t>Organization.identifier:finess</t>
+  </si>
+  <si>
+    <t>finess</t>
+  </si>
+  <si>
+    <t>Identifiant FINESS Entité Géographique (EG) ou Entité Juridique (EJ)</t>
+  </si>
+  <si>
+    <t>Organization.identifier:finess.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier:finess.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier:finess.use</t>
+  </si>
+  <si>
+    <t>Organization.identifier:finess.type</t>
+  </si>
+  <si>
+    <t>Organization.identifier:finess.type.id</t>
   </si>
   <si>
     <t>Organization.identifier.type.id</t>
   </si>
   <si>
-    <t>Organization.identifier:sirene.type.extension</t>
+    <t>Organization.identifier:finess.type.extension</t>
   </si>
   <si>
     <t>Organization.identifier.type.extension</t>
   </si>
   <si>
-    <t>Organization.identifier:sirene.type.coding</t>
+    <t>Organization.identifier:finess.type.coding</t>
   </si>
   <si>
     <t>Organization.identifier.type.coding</t>
@@ -1037,19 +1122,19 @@
     <t>union(., ./translation)</t>
   </si>
   <si>
-    <t>Organization.identifier:sirene.type.coding.id</t>
+    <t>Organization.identifier:finess.type.coding.id</t>
   </si>
   <si>
     <t>Organization.identifier.type.coding.id</t>
   </si>
   <si>
-    <t>Organization.identifier:sirene.type.coding.extension</t>
+    <t>Organization.identifier:finess.type.coding.extension</t>
   </si>
   <si>
     <t>Organization.identifier.type.coding.extension</t>
   </si>
   <si>
-    <t>Organization.identifier:sirene.type.coding.system</t>
+    <t>Organization.identifier:finess.type.coding.system</t>
   </si>
   <si>
     <t>Organization.identifier.type.coding.system</t>
@@ -1079,7 +1164,7 @@
     <t>./codeSystem</t>
   </si>
   <si>
-    <t>Organization.identifier:sirene.type.coding.version</t>
+    <t>Organization.identifier:finess.type.coding.version</t>
   </si>
   <si>
     <t>Organization.identifier.type.coding.version</t>
@@ -1103,13 +1188,13 @@
     <t>./codeSystemVersion</t>
   </si>
   <si>
-    <t>Organization.identifier:sirene.type.coding.code</t>
+    <t>Organization.identifier:finess.type.coding.code</t>
   </si>
   <si>
     <t>Organization.identifier.type.coding.code</t>
   </si>
   <si>
-    <t>SIREN | SIRET</t>
+    <t>FINEJ | FINEG</t>
   </si>
   <si>
     <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
@@ -1130,7 +1215,7 @@
     <t>./code</t>
   </si>
   <si>
-    <t>Organization.identifier:sirene.type.coding.display</t>
+    <t>Organization.identifier:finess.type.coding.display</t>
   </si>
   <si>
     <t>Organization.identifier.type.coding.display</t>
@@ -1154,7 +1239,7 @@
     <t>CV.displayName</t>
   </si>
   <si>
-    <t>Organization.identifier:sirene.type.coding.userSelected</t>
+    <t>Organization.identifier:finess.type.coding.userSelected</t>
   </si>
   <si>
     <t>Organization.identifier.type.coding.userSelected</t>
@@ -1185,7 +1270,7 @@
     <t>CD.codingRationale</t>
   </si>
   <si>
-    <t>Organization.identifier:sirene.type.text</t>
+    <t>Organization.identifier:finess.type.text</t>
   </si>
   <si>
     <t>Organization.identifier.type.text</t>
@@ -1210,78 +1295,6 @@
   </si>
   <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>Organization.identifier:sirene.system</t>
-  </si>
-  <si>
-    <t>https://sirene.fr</t>
-  </si>
-  <si>
-    <t>Organization.identifier:sirene.value</t>
-  </si>
-  <si>
-    <t>Organization.identifier:sirene.period</t>
-  </si>
-  <si>
-    <t>Organization.identifier:sirene.assigner</t>
-  </si>
-  <si>
-    <t>Organization.identifier:finess</t>
-  </si>
-  <si>
-    <t>finess</t>
-  </si>
-  <si>
-    <t>Identifiant FINESS Entité Géographique (EG) ou Entité Juridique (EJ)</t>
-  </si>
-  <si>
-    <t>Organization.identifier:finess.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier:finess.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier:finess.use</t>
-  </si>
-  <si>
-    <t>Organization.identifier:finess.type</t>
-  </si>
-  <si>
-    <t>Organization.identifier:finess.type.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier:finess.type.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier:finess.type.coding</t>
-  </si>
-  <si>
-    <t>Organization.identifier:finess.type.coding.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier:finess.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier:finess.type.coding.system</t>
-  </si>
-  <si>
-    <t>Organization.identifier:finess.type.coding.version</t>
-  </si>
-  <si>
-    <t>Organization.identifier:finess.type.coding.code</t>
-  </si>
-  <si>
-    <t>FINEJ | FINEG</t>
-  </si>
-  <si>
-    <t>Organization.identifier:finess.type.coding.display</t>
-  </si>
-  <si>
-    <t>Organization.identifier:finess.type.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Organization.identifier:finess.type.text</t>
   </si>
   <si>
     <t>Organization.identifier:finess.system</t>
@@ -2265,7 +2278,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN156"/>
+  <dimension ref="A1:AN154"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="63.859375" customWidth="true" bestFit="true"/>
@@ -7389,7 +7402,7 @@
         <v>78</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>78</v>
+        <v>314</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>78</v>
@@ -7457,10 +7470,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>315</v>
+        <v>249</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7480,19 +7493,23 @@
         <v>78</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>105</v>
+        <v>250</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>78</v>
       </c>
@@ -7501,10 +7518,10 @@
         <v>78</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>78</v>
+        <v>316</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>78</v>
+        <v>254</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>78</v>
@@ -7540,7 +7557,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>107</v>
+        <v>255</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7549,19 +7566,19 @@
         <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>78</v>
+        <v>256</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>108</v>
+        <v>257</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>78</v>
+        <v>258</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>78</v>
@@ -7569,21 +7586,21 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>317</v>
+        <v>259</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>78</v>
@@ -7592,19 +7609,19 @@
         <v>78</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>112</v>
+        <v>260</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>113</v>
+        <v>261</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>114</v>
+        <v>262</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7618,7 +7635,7 @@
         <v>78</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>78</v>
+        <v>263</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>78</v>
@@ -7642,40 +7659,40 @@
         <v>78</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>118</v>
+        <v>264</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>78</v>
+        <v>265</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>102</v>
+        <v>266</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>78</v>
+        <v>267</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>78</v>
@@ -7686,7 +7703,7 @@
         <v>318</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>319</v>
+        <v>268</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7697,7 +7714,7 @@
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>78</v>
@@ -7709,20 +7726,18 @@
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>148</v>
+        <v>269</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>320</v>
+        <v>270</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>321</v>
+        <v>271</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>323</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>78</v>
       </c>
@@ -7770,28 +7785,28 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>324</v>
+        <v>273</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>101</v>
+        <v>274</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>326</v>
+        <v>276</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>78</v>
+        <v>277</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>78</v>
@@ -7799,10 +7814,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>328</v>
+        <v>278</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7822,18 +7837,20 @@
         <v>78</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>104</v>
+        <v>279</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>105</v>
+        <v>280</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>281</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>78</v>
@@ -7882,7 +7899,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>107</v>
+        <v>283</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7891,19 +7908,19 @@
         <v>88</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>78</v>
+        <v>284</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>78</v>
+        <v>285</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>108</v>
+        <v>286</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>78</v>
+        <v>287</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>78</v>
@@ -7911,14 +7928,16 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="C50" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="C50" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="D50" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7934,21 +7953,21 @@
         <v>78</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>111</v>
+        <v>218</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>112</v>
+        <v>322</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>220</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
       </c>
@@ -7984,19 +8003,19 @@
         <v>78</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>118</v>
+        <v>217</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -8005,30 +8024,30 @@
         <v>80</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>100</v>
+        <v>224</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>78</v>
+        <v>225</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>102</v>
+        <v>226</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>78</v>
+        <v>227</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>78</v>
+        <v>228</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>332</v>
+        <v>229</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8048,23 +8067,19 @@
         <v>78</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>333</v>
+        <v>105</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>336</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>78</v>
       </c>
@@ -8073,7 +8088,7 @@
         <v>78</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>337</v>
+        <v>78</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>78</v>
@@ -8112,7 +8127,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>338</v>
+        <v>107</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8121,16 +8136,16 @@
         <v>88</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>339</v>
+        <v>78</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>340</v>
+        <v>108</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>78</v>
@@ -8141,21 +8156,21 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>342</v>
+        <v>230</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>78</v>
@@ -8164,19 +8179,19 @@
         <v>78</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>343</v>
+        <v>112</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>344</v>
+        <v>113</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>345</v>
+        <v>114</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8214,37 +8229,37 @@
         <v>78</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>346</v>
+        <v>118</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>347</v>
+        <v>78</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>348</v>
+        <v>102</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>78</v>
@@ -8255,10 +8270,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>349</v>
+        <v>325</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>350</v>
+        <v>231</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8275,7 +8290,7 @@
         <v>78</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J53" t="s" s="2">
         <v>89</v>
@@ -8284,16 +8299,16 @@
         <v>172</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>351</v>
+        <v>232</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>352</v>
+        <v>233</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>353</v>
+        <v>234</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>354</v>
+        <v>235</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -8318,13 +8333,13 @@
         <v>78</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>78</v>
+        <v>236</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>78</v>
+        <v>295</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>78</v>
+        <v>296</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>78</v>
@@ -8342,7 +8357,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>355</v>
+        <v>238</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8357,10 +8372,10 @@
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>356</v>
+        <v>102</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>357</v>
+        <v>239</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>78</v>
@@ -8371,10 +8386,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>358</v>
+        <v>326</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>359</v>
+        <v>240</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8397,19 +8412,19 @@
         <v>89</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>104</v>
+        <v>241</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>360</v>
+        <v>242</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>361</v>
+        <v>243</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>353</v>
+        <v>244</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>362</v>
+        <v>245</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>78</v>
@@ -8419,7 +8434,7 @@
         <v>78</v>
       </c>
       <c r="S54" t="s" s="2">
-        <v>78</v>
+        <v>327</v>
       </c>
       <c r="T54" t="s" s="2">
         <v>78</v>
@@ -8434,13 +8449,13 @@
         <v>78</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>78</v>
+        <v>152</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>78</v>
+        <v>299</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>78</v>
+        <v>300</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>78</v>
@@ -8458,7 +8473,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>363</v>
+        <v>247</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8473,10 +8488,10 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>364</v>
+        <v>248</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>365</v>
+        <v>239</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>78</v>
@@ -8487,10 +8502,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>366</v>
+        <v>328</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>367</v>
+        <v>249</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8513,19 +8528,19 @@
         <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>368</v>
+        <v>132</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>369</v>
+        <v>250</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>370</v>
+        <v>251</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>371</v>
+        <v>252</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>372</v>
+        <v>253</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
@@ -8535,10 +8550,10 @@
         <v>78</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>78</v>
+        <v>316</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>78</v>
+        <v>254</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>78</v>
@@ -8574,7 +8589,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>373</v>
+        <v>255</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8589,13 +8604,13 @@
         <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>374</v>
+        <v>256</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>375</v>
+        <v>257</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>78</v>
+        <v>258</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>78</v>
@@ -8603,10 +8618,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>376</v>
+        <v>329</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>377</v>
+        <v>259</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8632,17 +8647,15 @@
         <v>104</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>378</v>
+        <v>260</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>379</v>
+        <v>261</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>381</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>78</v>
       </c>
@@ -8654,7 +8667,7 @@
         <v>78</v>
       </c>
       <c r="T56" t="s" s="2">
-        <v>78</v>
+        <v>263</v>
       </c>
       <c r="U56" t="s" s="2">
         <v>78</v>
@@ -8690,7 +8703,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>382</v>
+        <v>264</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8705,13 +8718,13 @@
         <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>383</v>
+        <v>265</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>384</v>
+        <v>266</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>78</v>
+        <v>267</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>78</v>
@@ -8719,10 +8732,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>385</v>
+        <v>330</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>249</v>
+        <v>268</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8745,20 +8758,18 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>132</v>
+        <v>269</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>78</v>
       </c>
@@ -8767,10 +8778,10 @@
         <v>78</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>386</v>
+        <v>78</v>
       </c>
       <c r="T57" t="s" s="2">
-        <v>254</v>
+        <v>78</v>
       </c>
       <c r="U57" t="s" s="2">
         <v>78</v>
@@ -8806,7 +8817,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8818,16 +8829,16 @@
         <v>100</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>101</v>
+        <v>274</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>78</v>
@@ -8835,10 +8846,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>259</v>
+        <v>278</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8861,16 +8872,16 @@
         <v>89</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>104</v>
+        <v>279</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8884,7 +8895,7 @@
         <v>78</v>
       </c>
       <c r="T58" t="s" s="2">
-        <v>263</v>
+        <v>78</v>
       </c>
       <c r="U58" t="s" s="2">
         <v>78</v>
@@ -8920,7 +8931,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8932,16 +8943,16 @@
         <v>100</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>101</v>
+        <v>284</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>266</v>
+        <v>286</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>78</v>
@@ -8949,12 +8960,14 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>388</v>
+        <v>332</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="C59" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>333</v>
+      </c>
       <c r="D59" t="s" s="2">
         <v>78</v>
       </c>
@@ -8963,7 +8976,7 @@
         <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>78</v>
@@ -8975,18 +8988,18 @@
         <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>269</v>
+        <v>218</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>220</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>78</v>
       </c>
@@ -9034,39 +9047,39 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>273</v>
+        <v>217</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>100</v>
+        <v>224</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>274</v>
+        <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>275</v>
+        <v>225</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>276</v>
+        <v>226</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>277</v>
+        <v>227</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>78</v>
+        <v>228</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>389</v>
+        <v>335</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>278</v>
+        <v>229</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9086,20 +9099,18 @@
         <v>78</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>279</v>
+        <v>104</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>280</v>
+        <v>105</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>78</v>
@@ -9148,7 +9159,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>283</v>
+        <v>107</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9157,19 +9168,19 @@
         <v>88</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>284</v>
+        <v>78</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>285</v>
+        <v>78</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>286</v>
+        <v>108</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>287</v>
+        <v>78</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>78</v>
@@ -9177,16 +9188,14 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>390</v>
+        <v>336</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="C61" t="s" s="2">
-        <v>391</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9202,21 +9211,21 @@
         <v>78</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>218</v>
+        <v>111</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>392</v>
+        <v>112</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" t="s" s="2">
-        <v>221</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>78</v>
       </c>
@@ -9252,19 +9261,19 @@
         <v>78</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>217</v>
+        <v>118</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9273,30 +9282,30 @@
         <v>80</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>224</v>
+        <v>100</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>225</v>
+        <v>78</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>226</v>
+        <v>102</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>227</v>
+        <v>78</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>228</v>
+        <v>78</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>393</v>
+        <v>337</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9313,22 +9322,26 @@
         <v>78</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>104</v>
+        <v>172</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>105</v>
+        <v>232</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>235</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>78</v>
       </c>
@@ -9352,13 +9365,13 @@
         <v>78</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>78</v>
+        <v>236</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>78</v>
+        <v>295</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>78</v>
+        <v>296</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>78</v>
@@ -9376,7 +9389,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>107</v>
+        <v>238</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9385,16 +9398,16 @@
         <v>88</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>108</v>
+        <v>239</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>78</v>
@@ -9405,21 +9418,21 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>394</v>
+        <v>338</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>78</v>
@@ -9428,21 +9441,23 @@
         <v>78</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>111</v>
+        <v>241</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>112</v>
+        <v>242</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>113</v>
+        <v>243</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O63" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>78</v>
       </c>
@@ -9466,49 +9481,49 @@
         <v>78</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>78</v>
+        <v>152</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>78</v>
+        <v>299</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>78</v>
+        <v>300</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>118</v>
+        <v>247</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>78</v>
+        <v>248</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>102</v>
+        <v>239</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>78</v>
@@ -9519,10 +9534,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>395</v>
+        <v>339</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>231</v>
+        <v>340</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9539,26 +9554,22 @@
         <v>78</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>172</v>
+        <v>104</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>232</v>
+        <v>105</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>235</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>78</v>
       </c>
@@ -9582,13 +9593,13 @@
         <v>78</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>236</v>
+        <v>78</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>295</v>
+        <v>78</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>296</v>
+        <v>78</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>78</v>
@@ -9606,7 +9617,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>238</v>
+        <v>107</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9615,16 +9626,16 @@
         <v>88</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>239</v>
+        <v>108</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>78</v>
@@ -9635,21 +9646,21 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>396</v>
+        <v>341</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>240</v>
+        <v>342</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>78</v>
@@ -9658,23 +9669,21 @@
         <v>78</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>241</v>
+        <v>111</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>242</v>
+        <v>112</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>243</v>
+        <v>113</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>78</v>
       </c>
@@ -9698,49 +9707,49 @@
         <v>78</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>152</v>
+        <v>78</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>299</v>
+        <v>78</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>300</v>
+        <v>78</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>247</v>
+        <v>118</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>239</v>
+        <v>102</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>78</v>
@@ -9751,10 +9760,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>397</v>
+        <v>343</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>315</v>
+        <v>344</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9765,7 +9774,7 @@
         <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>78</v>
@@ -9774,19 +9783,23 @@
         <v>78</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>104</v>
+        <v>148</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>105</v>
+        <v>345</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>346</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>78</v>
       </c>
@@ -9834,25 +9847,25 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>107</v>
+        <v>349</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>78</v>
+        <v>350</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>108</v>
+        <v>351</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>78</v>
@@ -9863,21 +9876,21 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>398</v>
+        <v>352</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>317</v>
+        <v>353</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>78</v>
@@ -9889,17 +9902,15 @@
         <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>78</v>
@@ -9936,37 +9947,37 @@
         <v>78</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>78</v>
@@ -9977,14 +9988,14 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>399</v>
+        <v>354</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>319</v>
+        <v>355</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10000,23 +10011,21 @@
         <v>78</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>320</v>
+        <v>112</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>321</v>
+        <v>113</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>323</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>78</v>
       </c>
@@ -10052,19 +10061,19 @@
         <v>78</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>324</v>
+        <v>118</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10076,13 +10085,13 @@
         <v>100</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>325</v>
+        <v>78</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>326</v>
+        <v>102</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>78</v>
@@ -10093,10 +10102,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>400</v>
+        <v>356</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>328</v>
+        <v>357</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10116,19 +10125,23 @@
         <v>78</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>105</v>
+        <v>358</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
+        <v>359</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>78</v>
       </c>
@@ -10137,7 +10150,7 @@
         <v>78</v>
       </c>
       <c r="S69" t="s" s="2">
-        <v>78</v>
+        <v>362</v>
       </c>
       <c r="T69" t="s" s="2">
         <v>78</v>
@@ -10176,7 +10189,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>107</v>
+        <v>363</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10185,16 +10198,16 @@
         <v>88</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>78</v>
+        <v>364</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>108</v>
+        <v>365</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>78</v>
@@ -10205,21 +10218,21 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>401</v>
+        <v>366</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>330</v>
+        <v>367</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>78</v>
@@ -10228,19 +10241,19 @@
         <v>78</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>112</v>
+        <v>368</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>113</v>
+        <v>369</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>114</v>
+        <v>370</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10278,37 +10291,37 @@
         <v>78</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>118</v>
+        <v>371</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>78</v>
+        <v>372</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>102</v>
+        <v>373</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>78</v>
@@ -10319,10 +10332,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>402</v>
+        <v>374</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>332</v>
+        <v>375</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10345,19 +10358,19 @@
         <v>89</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>132</v>
+        <v>172</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>333</v>
+        <v>376</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>334</v>
+        <v>377</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>335</v>
+        <v>378</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>336</v>
+        <v>379</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -10367,7 +10380,7 @@
         <v>78</v>
       </c>
       <c r="S71" t="s" s="2">
-        <v>337</v>
+        <v>78</v>
       </c>
       <c r="T71" t="s" s="2">
         <v>78</v>
@@ -10406,7 +10419,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>338</v>
+        <v>380</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10421,10 +10434,10 @@
         <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>339</v>
+        <v>381</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>78</v>
@@ -10435,10 +10448,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>403</v>
+        <v>383</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>342</v>
+        <v>384</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10464,15 +10477,17 @@
         <v>104</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>343</v>
+        <v>385</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>344</v>
+        <v>386</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="O72" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>387</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>78</v>
       </c>
@@ -10520,7 +10535,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>346</v>
+        <v>388</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10535,10 +10550,10 @@
         <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>347</v>
+        <v>389</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>348</v>
+        <v>390</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>78</v>
@@ -10549,10 +10564,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>404</v>
+        <v>391</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>350</v>
+        <v>392</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10575,19 +10590,19 @@
         <v>89</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>172</v>
+        <v>393</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>352</v>
+        <v>395</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>353</v>
+        <v>396</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>354</v>
+        <v>397</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>78</v>
@@ -10636,7 +10651,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>355</v>
+        <v>398</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10651,10 +10666,10 @@
         <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>356</v>
+        <v>399</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>357</v>
+        <v>400</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>78</v>
@@ -10665,10 +10680,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>359</v>
+        <v>402</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10694,16 +10709,16 @@
         <v>104</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>360</v>
+        <v>403</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>361</v>
+        <v>404</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>353</v>
+        <v>405</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>362</v>
+        <v>406</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>78</v>
@@ -10752,7 +10767,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>363</v>
+        <v>407</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10767,10 +10782,10 @@
         <v>101</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>364</v>
+        <v>408</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>365</v>
+        <v>409</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>78</v>
@@ -10781,10 +10796,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>367</v>
+        <v>249</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10807,19 +10822,19 @@
         <v>89</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>368</v>
+        <v>132</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>369</v>
+        <v>250</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>370</v>
+        <v>251</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>371</v>
+        <v>252</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>372</v>
+        <v>253</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>78</v>
@@ -10829,10 +10844,10 @@
         <v>78</v>
       </c>
       <c r="S75" t="s" s="2">
-        <v>78</v>
+        <v>411</v>
       </c>
       <c r="T75" t="s" s="2">
-        <v>78</v>
+        <v>254</v>
       </c>
       <c r="U75" t="s" s="2">
         <v>78</v>
@@ -10868,7 +10883,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>373</v>
+        <v>255</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10883,13 +10898,13 @@
         <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>374</v>
+        <v>256</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>375</v>
+        <v>257</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>78</v>
+        <v>258</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>78</v>
@@ -10897,10 +10912,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>377</v>
+        <v>259</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10926,17 +10941,15 @@
         <v>104</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>378</v>
+        <v>260</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>379</v>
+        <v>261</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>381</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>78</v>
       </c>
@@ -10948,7 +10961,7 @@
         <v>78</v>
       </c>
       <c r="T76" t="s" s="2">
-        <v>78</v>
+        <v>263</v>
       </c>
       <c r="U76" t="s" s="2">
         <v>78</v>
@@ -10984,7 +10997,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>382</v>
+        <v>264</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -10999,13 +11012,13 @@
         <v>101</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>383</v>
+        <v>265</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>384</v>
+        <v>266</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>78</v>
+        <v>267</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>78</v>
@@ -11013,10 +11026,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>249</v>
+        <v>268</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11039,20 +11052,18 @@
         <v>89</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>132</v>
+        <v>269</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>78</v>
       </c>
@@ -11061,10 +11072,10 @@
         <v>78</v>
       </c>
       <c r="S77" t="s" s="2">
-        <v>410</v>
+        <v>78</v>
       </c>
       <c r="T77" t="s" s="2">
-        <v>254</v>
+        <v>78</v>
       </c>
       <c r="U77" t="s" s="2">
         <v>78</v>
@@ -11100,7 +11111,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11112,16 +11123,16 @@
         <v>100</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>101</v>
+        <v>274</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>78</v>
@@ -11129,10 +11140,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>259</v>
+        <v>278</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11155,16 +11166,16 @@
         <v>89</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>104</v>
+        <v>279</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11178,7 +11189,7 @@
         <v>78</v>
       </c>
       <c r="T78" t="s" s="2">
-        <v>263</v>
+        <v>78</v>
       </c>
       <c r="U78" t="s" s="2">
         <v>78</v>
@@ -11214,7 +11225,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11226,16 +11237,16 @@
         <v>100</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>101</v>
+        <v>284</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>266</v>
+        <v>286</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>78</v>
@@ -11243,12 +11254,14 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="C79" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="C79" t="s" s="2">
+        <v>416</v>
+      </c>
       <c r="D79" t="s" s="2">
         <v>78</v>
       </c>
@@ -11257,7 +11270,7 @@
         <v>79</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>78</v>
@@ -11269,18 +11282,18 @@
         <v>89</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>269</v>
+        <v>218</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>270</v>
+        <v>417</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O79" s="2"/>
+        <v>220</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>78</v>
       </c>
@@ -11328,39 +11341,39 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>273</v>
+        <v>217</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>100</v>
+        <v>224</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>274</v>
+        <v>101</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>275</v>
+        <v>225</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>276</v>
+        <v>226</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>277</v>
+        <v>227</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>78</v>
+        <v>228</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>278</v>
+        <v>229</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11380,20 +11393,18 @@
         <v>78</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>279</v>
+        <v>104</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>280</v>
+        <v>105</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>78</v>
@@ -11442,7 +11453,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>283</v>
+        <v>107</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11451,19 +11462,19 @@
         <v>88</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>284</v>
+        <v>78</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>285</v>
+        <v>78</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>286</v>
+        <v>108</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>287</v>
+        <v>78</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>78</v>
@@ -11471,16 +11482,14 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="C81" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11496,21 +11505,21 @@
         <v>78</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>218</v>
+        <v>111</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>416</v>
+        <v>112</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" t="s" s="2">
-        <v>221</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>78</v>
       </c>
@@ -11546,19 +11555,19 @@
         <v>78</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>217</v>
+        <v>118</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11567,30 +11576,30 @@
         <v>80</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>224</v>
+        <v>100</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>225</v>
+        <v>78</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>226</v>
+        <v>102</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>227</v>
+        <v>78</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>228</v>
+        <v>78</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11607,22 +11616,26 @@
         <v>78</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>104</v>
+        <v>172</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>105</v>
+        <v>232</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>235</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>78</v>
       </c>
@@ -11646,13 +11659,13 @@
         <v>78</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>78</v>
+        <v>236</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>78</v>
+        <v>295</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>78</v>
+        <v>296</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>78</v>
@@ -11670,7 +11683,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>107</v>
+        <v>238</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -11679,16 +11692,16 @@
         <v>88</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>108</v>
+        <v>239</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>78</v>
@@ -11699,21 +11712,21 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>78</v>
@@ -11722,21 +11735,23 @@
         <v>78</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>111</v>
+        <v>241</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>112</v>
+        <v>242</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>113</v>
+        <v>243</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O83" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>78</v>
       </c>
@@ -11745,7 +11760,7 @@
         <v>78</v>
       </c>
       <c r="S83" t="s" s="2">
-        <v>78</v>
+        <v>422</v>
       </c>
       <c r="T83" t="s" s="2">
         <v>78</v>
@@ -11760,49 +11775,49 @@
         <v>78</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>78</v>
+        <v>152</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>78</v>
+        <v>299</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>78</v>
+        <v>300</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>118</v>
+        <v>247</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>78</v>
+        <v>248</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>102</v>
+        <v>239</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>78</v>
@@ -11813,10 +11828,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11833,25 +11848,25 @@
         <v>78</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J84" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>172</v>
+        <v>132</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>78</v>
@@ -11861,10 +11876,10 @@
         <v>78</v>
       </c>
       <c r="S84" t="s" s="2">
-        <v>78</v>
+        <v>424</v>
       </c>
       <c r="T84" t="s" s="2">
-        <v>78</v>
+        <v>254</v>
       </c>
       <c r="U84" t="s" s="2">
         <v>78</v>
@@ -11876,13 +11891,13 @@
         <v>78</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>236</v>
+        <v>78</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>295</v>
+        <v>78</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>296</v>
+        <v>78</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>78</v>
@@ -11900,7 +11915,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -11915,13 +11930,13 @@
         <v>101</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>102</v>
+        <v>256</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>78</v>
+        <v>258</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>78</v>
@@ -11929,10 +11944,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11955,20 +11970,18 @@
         <v>89</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>241</v>
+        <v>104</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>78</v>
       </c>
@@ -11977,10 +11990,10 @@
         <v>78</v>
       </c>
       <c r="S85" t="s" s="2">
-        <v>421</v>
+        <v>78</v>
       </c>
       <c r="T85" t="s" s="2">
-        <v>78</v>
+        <v>263</v>
       </c>
       <c r="U85" t="s" s="2">
         <v>78</v>
@@ -11992,13 +12005,13 @@
         <v>78</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>152</v>
+        <v>78</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>299</v>
+        <v>78</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>300</v>
+        <v>78</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>78</v>
@@ -12016,7 +12029,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -12031,13 +12044,13 @@
         <v>101</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>239</v>
+        <v>266</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>78</v>
+        <v>267</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>78</v>
@@ -12045,10 +12058,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>249</v>
+        <v>268</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12071,20 +12084,18 @@
         <v>89</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>132</v>
+        <v>269</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>78</v>
       </c>
@@ -12093,10 +12104,10 @@
         <v>78</v>
       </c>
       <c r="S86" t="s" s="2">
-        <v>423</v>
+        <v>78</v>
       </c>
       <c r="T86" t="s" s="2">
-        <v>254</v>
+        <v>78</v>
       </c>
       <c r="U86" t="s" s="2">
         <v>78</v>
@@ -12132,7 +12143,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12144,16 +12155,16 @@
         <v>100</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>101</v>
+        <v>274</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>78</v>
@@ -12161,10 +12172,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>259</v>
+        <v>278</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12187,16 +12198,16 @@
         <v>89</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>104</v>
+        <v>279</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12210,7 +12221,7 @@
         <v>78</v>
       </c>
       <c r="T87" t="s" s="2">
-        <v>263</v>
+        <v>78</v>
       </c>
       <c r="U87" t="s" s="2">
         <v>78</v>
@@ -12246,7 +12257,7 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12258,16 +12269,16 @@
         <v>100</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>101</v>
+        <v>284</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>266</v>
+        <v>286</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>78</v>
@@ -12275,12 +12286,14 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="C88" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="C88" t="s" s="2">
+        <v>429</v>
+      </c>
       <c r="D88" t="s" s="2">
         <v>78</v>
       </c>
@@ -12289,7 +12302,7 @@
         <v>79</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>78</v>
@@ -12301,18 +12314,18 @@
         <v>89</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>269</v>
+        <v>218</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>270</v>
+        <v>430</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O88" s="2"/>
+        <v>220</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="P88" t="s" s="2">
         <v>78</v>
       </c>
@@ -12360,39 +12373,39 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>273</v>
+        <v>217</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>100</v>
+        <v>224</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>274</v>
+        <v>101</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>275</v>
+        <v>225</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>276</v>
+        <v>226</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>277</v>
+        <v>227</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>78</v>
+        <v>228</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>278</v>
+        <v>229</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12412,20 +12425,18 @@
         <v>78</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>279</v>
+        <v>104</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>280</v>
+        <v>105</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>78</v>
@@ -12474,7 +12485,7 @@
         <v>78</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>283</v>
+        <v>107</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12483,19 +12494,19 @@
         <v>88</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>284</v>
+        <v>78</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>285</v>
+        <v>78</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>286</v>
+        <v>108</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>287</v>
+        <v>78</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>78</v>
@@ -12503,16 +12514,14 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="C90" t="s" s="2">
-        <v>428</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -12528,21 +12537,21 @@
         <v>78</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>218</v>
+        <v>111</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>429</v>
+        <v>112</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N90" s="2"/>
-      <c r="O90" t="s" s="2">
-        <v>221</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>78</v>
       </c>
@@ -12578,19 +12587,19 @@
         <v>78</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>217</v>
+        <v>118</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -12599,30 +12608,30 @@
         <v>80</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>224</v>
+        <v>100</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>225</v>
+        <v>78</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>226</v>
+        <v>102</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>227</v>
+        <v>78</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>228</v>
+        <v>78</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12639,22 +12648,26 @@
         <v>78</v>
       </c>
       <c r="I91" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>104</v>
+        <v>172</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>105</v>
+        <v>232</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>235</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>78</v>
       </c>
@@ -12678,13 +12691,13 @@
         <v>78</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>78</v>
+        <v>236</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>78</v>
+        <v>295</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>78</v>
+        <v>296</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>78</v>
@@ -12702,7 +12715,7 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>107</v>
+        <v>238</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -12711,16 +12724,16 @@
         <v>88</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>108</v>
+        <v>239</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>78</v>
@@ -12731,21 +12744,21 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>78</v>
@@ -12754,21 +12767,23 @@
         <v>78</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>111</v>
+        <v>241</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>112</v>
+        <v>242</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>113</v>
+        <v>243</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O92" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="P92" t="s" s="2">
         <v>78</v>
       </c>
@@ -12777,7 +12792,7 @@
         <v>78</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>78</v>
+        <v>422</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>78</v>
@@ -12792,49 +12807,49 @@
         <v>78</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>78</v>
+        <v>152</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>78</v>
+        <v>299</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>78</v>
+        <v>300</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC92" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>118</v>
+        <v>247</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>78</v>
+        <v>248</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>102</v>
+        <v>239</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>78</v>
@@ -12845,10 +12860,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12865,25 +12880,25 @@
         <v>78</v>
       </c>
       <c r="I93" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J93" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>172</v>
+        <v>132</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>78</v>
@@ -12893,10 +12908,10 @@
         <v>78</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>78</v>
+        <v>436</v>
       </c>
       <c r="T93" t="s" s="2">
-        <v>78</v>
+        <v>254</v>
       </c>
       <c r="U93" t="s" s="2">
         <v>78</v>
@@ -12908,13 +12923,13 @@
         <v>78</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>236</v>
+        <v>78</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>295</v>
+        <v>78</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>296</v>
+        <v>78</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>78</v>
@@ -12932,7 +12947,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -12947,13 +12962,13 @@
         <v>101</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>102</v>
+        <v>256</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>78</v>
+        <v>258</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>78</v>
@@ -12961,10 +12976,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12987,20 +13002,18 @@
         <v>89</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>241</v>
+        <v>104</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>78</v>
       </c>
@@ -13009,10 +13022,10 @@
         <v>78</v>
       </c>
       <c r="S94" t="s" s="2">
-        <v>421</v>
+        <v>78</v>
       </c>
       <c r="T94" t="s" s="2">
-        <v>78</v>
+        <v>263</v>
       </c>
       <c r="U94" t="s" s="2">
         <v>78</v>
@@ -13024,13 +13037,13 @@
         <v>78</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>152</v>
+        <v>78</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>299</v>
+        <v>78</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>300</v>
+        <v>78</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>78</v>
@@ -13048,7 +13061,7 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13063,13 +13076,13 @@
         <v>101</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>239</v>
+        <v>266</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>78</v>
+        <v>267</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>78</v>
@@ -13077,10 +13090,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>249</v>
+        <v>268</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13103,20 +13116,18 @@
         <v>89</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>132</v>
+        <v>269</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>78</v>
       </c>
@@ -13125,10 +13136,10 @@
         <v>78</v>
       </c>
       <c r="S95" t="s" s="2">
-        <v>435</v>
+        <v>78</v>
       </c>
       <c r="T95" t="s" s="2">
-        <v>254</v>
+        <v>78</v>
       </c>
       <c r="U95" t="s" s="2">
         <v>78</v>
@@ -13164,7 +13175,7 @@
         <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13176,16 +13187,16 @@
         <v>100</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>101</v>
+        <v>274</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>78</v>
@@ -13193,10 +13204,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>259</v>
+        <v>278</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13219,16 +13230,16 @@
         <v>89</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>104</v>
+        <v>279</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13242,7 +13253,7 @@
         <v>78</v>
       </c>
       <c r="T96" t="s" s="2">
-        <v>263</v>
+        <v>78</v>
       </c>
       <c r="U96" t="s" s="2">
         <v>78</v>
@@ -13278,7 +13289,7 @@
         <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13290,16 +13301,16 @@
         <v>100</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>101</v>
+        <v>284</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>266</v>
+        <v>286</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>78</v>
@@ -13307,10 +13318,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>268</v>
+        <v>440</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13327,28 +13338,32 @@
         <v>78</v>
       </c>
       <c r="I97" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J97" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>269</v>
+        <v>393</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>270</v>
+        <v>441</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>271</v>
+        <v>442</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O97" s="2"/>
+        <v>443</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>444</v>
+      </c>
       <c r="P97" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q97" s="2"/>
+      <c r="Q97" t="s" s="2">
+        <v>445</v>
+      </c>
       <c r="R97" t="s" s="2">
         <v>78</v>
       </c>
@@ -13392,7 +13407,7 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>273</v>
+        <v>440</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13404,27 +13419,27 @@
         <v>100</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>274</v>
+        <v>101</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>275</v>
+        <v>446</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>276</v>
+        <v>447</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>277</v>
+        <v>448</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>78</v>
+        <v>449</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>278</v>
+        <v>450</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13435,7 +13450,7 @@
         <v>79</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>78</v>
@@ -13447,18 +13462,20 @@
         <v>89</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>279</v>
+        <v>241</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>280</v>
+        <v>451</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>281</v>
+        <v>452</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="O98" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>454</v>
+      </c>
       <c r="P98" t="s" s="2">
         <v>78</v>
       </c>
@@ -13482,65 +13499,65 @@
         <v>78</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>78</v>
+        <v>162</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>78</v>
+        <v>455</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>78</v>
+        <v>456</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="AC98" s="2"/>
       <c r="AD98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>283</v>
+        <v>450</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>284</v>
+        <v>101</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>285</v>
+        <v>458</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>286</v>
+        <v>459</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>287</v>
+        <v>108</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>78</v>
+        <v>460</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>439</v>
+        <v>461</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="C99" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="C99" t="s" s="2">
+        <v>462</v>
+      </c>
       <c r="D99" t="s" s="2">
         <v>78</v>
       </c>
@@ -13555,32 +13572,30 @@
         <v>78</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J99" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>368</v>
+        <v>241</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q99" t="s" s="2">
-        <v>444</v>
-      </c>
+      <c r="Q99" s="2"/>
       <c r="R99" t="s" s="2">
         <v>78</v>
       </c>
@@ -13600,13 +13615,11 @@
         <v>78</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="Y99" s="2"/>
       <c r="Z99" t="s" s="2">
-        <v>78</v>
+        <v>463</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>78</v>
@@ -13624,13 +13637,13 @@
         <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>100</v>
@@ -13639,24 +13652,24 @@
         <v>101</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>445</v>
+        <v>458</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>447</v>
+        <v>108</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>448</v>
+        <v>460</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>449</v>
+        <v>464</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>449</v>
+        <v>465</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13667,7 +13680,7 @@
         <v>79</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>78</v>
@@ -13676,23 +13689,19 @@
         <v>78</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>241</v>
+        <v>104</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>450</v>
+        <v>105</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>453</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N100" s="2"/>
+      <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>78</v>
       </c>
@@ -13716,74 +13725,74 @@
         <v>78</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>162</v>
+        <v>78</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>454</v>
+        <v>78</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>455</v>
+        <v>78</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB100" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="AC100" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>449</v>
+        <v>107</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>457</v>
+        <v>78</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>458</v>
+        <v>108</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>459</v>
+        <v>78</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="C101" t="s" s="2">
-        <v>461</v>
-      </c>
+        <v>467</v>
+      </c>
+      <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>78</v>
@@ -13792,23 +13801,21 @@
         <v>78</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>241</v>
+        <v>111</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>450</v>
+        <v>112</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>451</v>
+        <v>113</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>453</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>78</v>
       </c>
@@ -13832,29 +13839,31 @@
         <v>78</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="Y101" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z101" t="s" s="2">
-        <v>462</v>
+        <v>78</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD101" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>449</v>
+        <v>118</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -13866,27 +13875,27 @@
         <v>100</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>457</v>
+        <v>78</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>458</v>
+        <v>102</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>459</v>
+        <v>78</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13894,7 +13903,7 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>88</v>
@@ -13906,19 +13915,23 @@
         <v>78</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>104</v>
+        <v>148</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>105</v>
+        <v>345</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N102" s="2"/>
-      <c r="O102" s="2"/>
+        <v>346</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="O102" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="P102" t="s" s="2">
         <v>78</v>
       </c>
@@ -13966,25 +13979,25 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>107</v>
+        <v>349</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>78</v>
+        <v>350</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>108</v>
+        <v>351</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>78</v>
@@ -13995,21 +14008,21 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>78</v>
@@ -14021,17 +14034,15 @@
         <v>78</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N103" s="2"/>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>78</v>
@@ -14068,37 +14079,37 @@
         <v>78</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC103" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>78</v>
@@ -14109,21 +14120,21 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>78</v>
@@ -14132,23 +14143,21 @@
         <v>78</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>320</v>
+        <v>112</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>321</v>
+        <v>113</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>323</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>78</v>
       </c>
@@ -14184,19 +14193,19 @@
         <v>78</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC104" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>324</v>
+        <v>118</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14208,13 +14217,13 @@
         <v>100</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>325</v>
+        <v>78</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>326</v>
+        <v>102</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>78</v>
@@ -14225,10 +14234,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14236,7 +14245,7 @@
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G105" t="s" s="2">
         <v>88</v>
@@ -14248,19 +14257,23 @@
         <v>78</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>105</v>
+        <v>358</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N105" s="2"/>
-      <c r="O105" s="2"/>
+        <v>359</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="P105" t="s" s="2">
         <v>78</v>
       </c>
@@ -14308,7 +14321,7 @@
         <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>107</v>
+        <v>363</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -14317,16 +14330,16 @@
         <v>88</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>78</v>
+        <v>364</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>108</v>
+        <v>365</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>78</v>
@@ -14337,21 +14350,21 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>78</v>
@@ -14360,19 +14373,19 @@
         <v>78</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>112</v>
+        <v>368</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>113</v>
+        <v>369</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>114</v>
+        <v>370</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -14410,37 +14423,37 @@
         <v>78</v>
       </c>
       <c r="AB106" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC106" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>118</v>
+        <v>371</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>78</v>
+        <v>372</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>102</v>
+        <v>373</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>78</v>
@@ -14451,10 +14464,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14462,7 +14475,7 @@
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G107" t="s" s="2">
         <v>88</v>
@@ -14477,19 +14490,19 @@
         <v>89</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>132</v>
+        <v>172</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>333</v>
+        <v>480</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>334</v>
+        <v>377</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>335</v>
+        <v>378</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>336</v>
+        <v>379</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>78</v>
@@ -14538,7 +14551,7 @@
         <v>78</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>338</v>
+        <v>380</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -14553,10 +14566,10 @@
         <v>101</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>339</v>
+        <v>381</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>78</v>
@@ -14567,10 +14580,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14596,15 +14609,17 @@
         <v>104</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>343</v>
+        <v>385</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>344</v>
+        <v>386</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="O108" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="O108" t="s" s="2">
+        <v>387</v>
+      </c>
       <c r="P108" t="s" s="2">
         <v>78</v>
       </c>
@@ -14652,7 +14667,7 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>346</v>
+        <v>388</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -14667,10 +14682,10 @@
         <v>101</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>347</v>
+        <v>389</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>348</v>
+        <v>390</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>78</v>
@@ -14681,10 +14696,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14707,19 +14722,19 @@
         <v>89</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>172</v>
+        <v>393</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>479</v>
+        <v>394</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>352</v>
+        <v>395</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>353</v>
+        <v>396</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>354</v>
+        <v>397</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>78</v>
@@ -14768,7 +14783,7 @@
         <v>78</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>355</v>
+        <v>398</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -14783,10 +14798,10 @@
         <v>101</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>356</v>
+        <v>399</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>357</v>
+        <v>400</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>78</v>
@@ -14797,10 +14812,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14826,16 +14841,16 @@
         <v>104</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>360</v>
+        <v>403</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>361</v>
+        <v>404</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>353</v>
+        <v>405</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>362</v>
+        <v>406</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>78</v>
@@ -14884,7 +14899,7 @@
         <v>78</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>363</v>
+        <v>407</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -14899,10 +14914,10 @@
         <v>101</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>364</v>
+        <v>408</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>365</v>
+        <v>409</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>78</v>
@@ -14913,12 +14928,14 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="C111" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="C111" t="s" s="2">
+        <v>488</v>
+      </c>
       <c r="D111" t="s" s="2">
         <v>78</v>
       </c>
@@ -14939,19 +14956,19 @@
         <v>89</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>368</v>
+        <v>241</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>369</v>
+        <v>489</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>370</v>
+        <v>452</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>371</v>
+        <v>453</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>372</v>
+        <v>454</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>78</v>
@@ -14976,13 +14993,11 @@
         <v>78</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y111" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
-        <v>78</v>
+        <v>490</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>78</v>
@@ -15000,13 +15015,13 @@
         <v>78</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>373</v>
+        <v>450</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>100</v>
@@ -15015,24 +15030,24 @@
         <v>101</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>374</v>
+        <v>458</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>375</v>
+        <v>459</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>78</v>
+        <v>460</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>485</v>
+        <v>465</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15052,23 +15067,19 @@
         <v>78</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K112" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>378</v>
+        <v>105</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>381</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N112" s="2"/>
+      <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>78</v>
       </c>
@@ -15116,7 +15127,7 @@
         <v>78</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>382</v>
+        <v>107</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -15125,16 +15136,16 @@
         <v>88</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>383</v>
+        <v>78</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>384</v>
+        <v>108</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>78</v>
@@ -15145,23 +15156,21 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="C113" t="s" s="2">
-        <v>487</v>
-      </c>
+        <v>467</v>
+      </c>
+      <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>78</v>
@@ -15170,23 +15179,21 @@
         <v>78</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>241</v>
+        <v>111</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>488</v>
+        <v>112</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>451</v>
+        <v>113</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>453</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>78</v>
       </c>
@@ -15210,29 +15217,31 @@
         <v>78</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="Y113" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z113" t="s" s="2">
-        <v>489</v>
+        <v>78</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB113" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC113" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD113" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE113" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>449</v>
+        <v>118</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -15244,27 +15253,27 @@
         <v>100</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>457</v>
+        <v>78</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>458</v>
+        <v>102</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>459</v>
+        <v>78</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15272,7 +15281,7 @@
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G114" t="s" s="2">
         <v>88</v>
@@ -15284,19 +15293,23 @@
         <v>78</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>104</v>
+        <v>148</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>105</v>
+        <v>345</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N114" s="2"/>
-      <c r="O114" s="2"/>
+        <v>346</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="O114" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="P114" t="s" s="2">
         <v>78</v>
       </c>
@@ -15344,25 +15357,25 @@
         <v>78</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>107</v>
+        <v>349</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>78</v>
+        <v>350</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>108</v>
+        <v>351</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>78</v>
@@ -15373,21 +15386,21 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>78</v>
@@ -15399,17 +15412,15 @@
         <v>78</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N115" s="2"/>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>78</v>
@@ -15446,37 +15457,37 @@
         <v>78</v>
       </c>
       <c r="AB115" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC115" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD115" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE115" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>78</v>
@@ -15487,21 +15498,21 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>78</v>
@@ -15510,23 +15521,21 @@
         <v>78</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>320</v>
+        <v>112</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>321</v>
+        <v>113</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>323</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>78</v>
       </c>
@@ -15562,19 +15571,19 @@
         <v>78</v>
       </c>
       <c r="AB116" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC116" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD116" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE116" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>324</v>
+        <v>118</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -15586,13 +15595,13 @@
         <v>100</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>325</v>
+        <v>78</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>326</v>
+        <v>102</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>78</v>
@@ -15603,10 +15612,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15614,7 +15623,7 @@
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G117" t="s" s="2">
         <v>88</v>
@@ -15626,19 +15635,23 @@
         <v>78</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>105</v>
+        <v>358</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N117" s="2"/>
-      <c r="O117" s="2"/>
+        <v>359</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="O117" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="P117" t="s" s="2">
         <v>78</v>
       </c>
@@ -15686,7 +15699,7 @@
         <v>78</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>107</v>
+        <v>363</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
@@ -15695,16 +15708,16 @@
         <v>88</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>78</v>
+        <v>364</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>108</v>
+        <v>365</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>78</v>
@@ -15715,21 +15728,21 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>78</v>
@@ -15738,19 +15751,19 @@
         <v>78</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>112</v>
+        <v>368</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>113</v>
+        <v>369</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>114</v>
+        <v>370</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -15788,37 +15801,37 @@
         <v>78</v>
       </c>
       <c r="AB118" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC118" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD118" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE118" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>118</v>
+        <v>371</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>78</v>
+        <v>372</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>102</v>
+        <v>373</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>78</v>
@@ -15829,10 +15842,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15840,7 +15853,7 @@
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G119" t="s" s="2">
         <v>88</v>
@@ -15855,19 +15868,19 @@
         <v>89</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>132</v>
+        <v>172</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>333</v>
+        <v>480</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>334</v>
+        <v>377</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>335</v>
+        <v>378</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>336</v>
+        <v>379</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>78</v>
@@ -15916,7 +15929,7 @@
         <v>78</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>338</v>
+        <v>380</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -15931,10 +15944,10 @@
         <v>101</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>339</v>
+        <v>381</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>78</v>
@@ -15945,10 +15958,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15974,15 +15987,17 @@
         <v>104</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>343</v>
+        <v>385</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>344</v>
+        <v>386</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="O120" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="O120" t="s" s="2">
+        <v>387</v>
+      </c>
       <c r="P120" t="s" s="2">
         <v>78</v>
       </c>
@@ -16030,7 +16045,7 @@
         <v>78</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>346</v>
+        <v>388</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -16045,10 +16060,10 @@
         <v>101</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>347</v>
+        <v>389</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>348</v>
+        <v>390</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>78</v>
@@ -16059,10 +16074,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16085,19 +16100,19 @@
         <v>89</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>172</v>
+        <v>393</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>479</v>
+        <v>394</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>352</v>
+        <v>395</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>353</v>
+        <v>396</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>354</v>
+        <v>397</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>78</v>
@@ -16146,7 +16161,7 @@
         <v>78</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>355</v>
+        <v>398</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -16161,10 +16176,10 @@
         <v>101</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>356</v>
+        <v>399</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>357</v>
+        <v>400</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>78</v>
@@ -16175,10 +16190,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16204,16 +16219,16 @@
         <v>104</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>360</v>
+        <v>403</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>361</v>
+        <v>404</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>353</v>
+        <v>405</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>362</v>
+        <v>406</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>78</v>
@@ -16262,7 +16277,7 @@
         <v>78</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>363</v>
+        <v>407</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -16277,10 +16292,10 @@
         <v>101</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>364</v>
+        <v>408</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>365</v>
+        <v>409</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>78</v>
@@ -16291,12 +16306,14 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="C123" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="C123" t="s" s="2">
+        <v>503</v>
+      </c>
       <c r="D123" t="s" s="2">
         <v>78</v>
       </c>
@@ -16317,19 +16334,19 @@
         <v>89</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>368</v>
+        <v>241</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>369</v>
+        <v>504</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>370</v>
+        <v>452</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>371</v>
+        <v>453</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>372</v>
+        <v>454</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>78</v>
@@ -16354,13 +16371,11 @@
         <v>78</v>
       </c>
       <c r="X123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y123" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="Y123" s="2"/>
       <c r="Z123" t="s" s="2">
-        <v>78</v>
+        <v>505</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>78</v>
@@ -16378,13 +16393,13 @@
         <v>78</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>373</v>
+        <v>450</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>100</v>
@@ -16393,24 +16408,24 @@
         <v>101</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>374</v>
+        <v>458</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>375</v>
+        <v>459</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>78</v>
+        <v>460</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>485</v>
+        <v>465</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16430,23 +16445,19 @@
         <v>78</v>
       </c>
       <c r="J124" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K124" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>378</v>
+        <v>105</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="O124" t="s" s="2">
-        <v>381</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N124" s="2"/>
+      <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
         <v>78</v>
       </c>
@@ -16494,7 +16505,7 @@
         <v>78</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>382</v>
+        <v>107</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -16503,16 +16514,16 @@
         <v>88</v>
       </c>
       <c r="AI124" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>383</v>
+        <v>78</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>384</v>
+        <v>108</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>78</v>
@@ -16523,23 +16534,21 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="C125" t="s" s="2">
-        <v>502</v>
-      </c>
+        <v>467</v>
+      </c>
+      <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>78</v>
@@ -16548,23 +16557,21 @@
         <v>78</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>241</v>
+        <v>111</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>503</v>
+        <v>112</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>451</v>
+        <v>113</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>453</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
         <v>78</v>
       </c>
@@ -16588,29 +16595,31 @@
         <v>78</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="Y125" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z125" t="s" s="2">
-        <v>504</v>
+        <v>78</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB125" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC125" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD125" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE125" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>449</v>
+        <v>118</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -16622,27 +16631,27 @@
         <v>100</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>457</v>
+        <v>78</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>458</v>
+        <v>102</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>459</v>
+        <v>78</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16650,7 +16659,7 @@
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G126" t="s" s="2">
         <v>88</v>
@@ -16662,19 +16671,23 @@
         <v>78</v>
       </c>
       <c r="J126" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>104</v>
+        <v>148</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>105</v>
+        <v>345</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N126" s="2"/>
-      <c r="O126" s="2"/>
+        <v>346</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="O126" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="P126" t="s" s="2">
         <v>78</v>
       </c>
@@ -16722,25 +16735,25 @@
         <v>78</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>107</v>
+        <v>349</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>78</v>
+        <v>350</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>108</v>
+        <v>351</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>78</v>
@@ -16751,21 +16764,21 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H127" t="s" s="2">
         <v>78</v>
@@ -16777,17 +16790,15 @@
         <v>78</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N127" s="2"/>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>78</v>
@@ -16824,37 +16835,37 @@
         <v>78</v>
       </c>
       <c r="AB127" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC127" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD127" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE127" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK127" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>78</v>
@@ -16865,21 +16876,21 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>78</v>
@@ -16888,23 +16899,21 @@
         <v>78</v>
       </c>
       <c r="J128" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>320</v>
+        <v>112</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>321</v>
+        <v>113</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>323</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
         <v>78</v>
       </c>
@@ -16940,19 +16949,19 @@
         <v>78</v>
       </c>
       <c r="AB128" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC128" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD128" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE128" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>324</v>
+        <v>118</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -16964,13 +16973,13 @@
         <v>100</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>325</v>
+        <v>78</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>326</v>
+        <v>102</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>78</v>
@@ -16981,10 +16990,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -16992,7 +17001,7 @@
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G129" t="s" s="2">
         <v>88</v>
@@ -17004,19 +17013,23 @@
         <v>78</v>
       </c>
       <c r="J129" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>105</v>
+        <v>358</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N129" s="2"/>
-      <c r="O129" s="2"/>
+        <v>359</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="O129" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="P129" t="s" s="2">
         <v>78</v>
       </c>
@@ -17064,7 +17077,7 @@
         <v>78</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>107</v>
+        <v>363</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
@@ -17073,16 +17086,16 @@
         <v>88</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>78</v>
+        <v>364</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>108</v>
+        <v>365</v>
       </c>
       <c r="AM129" t="s" s="2">
         <v>78</v>
@@ -17093,21 +17106,21 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>78</v>
@@ -17116,19 +17129,19 @@
         <v>78</v>
       </c>
       <c r="J130" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>112</v>
+        <v>368</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>113</v>
+        <v>369</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>114</v>
+        <v>370</v>
       </c>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
@@ -17166,37 +17179,37 @@
         <v>78</v>
       </c>
       <c r="AB130" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC130" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD130" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE130" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>118</v>
+        <v>371</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>78</v>
+        <v>372</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>102</v>
+        <v>373</v>
       </c>
       <c r="AM130" t="s" s="2">
         <v>78</v>
@@ -17207,10 +17220,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17218,7 +17231,7 @@
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G131" t="s" s="2">
         <v>88</v>
@@ -17233,19 +17246,19 @@
         <v>89</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>132</v>
+        <v>172</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>333</v>
+        <v>480</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>334</v>
+        <v>377</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>335</v>
+        <v>378</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>336</v>
+        <v>379</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>78</v>
@@ -17294,7 +17307,7 @@
         <v>78</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>338</v>
+        <v>380</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
@@ -17309,10 +17322,10 @@
         <v>101</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>339</v>
+        <v>381</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="AM131" t="s" s="2">
         <v>78</v>
@@ -17323,10 +17336,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17352,15 +17365,17 @@
         <v>104</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>343</v>
+        <v>385</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>344</v>
+        <v>386</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="O132" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="O132" t="s" s="2">
+        <v>387</v>
+      </c>
       <c r="P132" t="s" s="2">
         <v>78</v>
       </c>
@@ -17408,7 +17423,7 @@
         <v>78</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>346</v>
+        <v>388</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
@@ -17423,10 +17438,10 @@
         <v>101</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>347</v>
+        <v>389</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>348</v>
+        <v>390</v>
       </c>
       <c r="AM132" t="s" s="2">
         <v>78</v>
@@ -17437,10 +17452,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17463,19 +17478,19 @@
         <v>89</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>172</v>
+        <v>393</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>479</v>
+        <v>394</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>352</v>
+        <v>395</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>353</v>
+        <v>396</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>354</v>
+        <v>397</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>78</v>
@@ -17524,7 +17539,7 @@
         <v>78</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>355</v>
+        <v>398</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -17539,10 +17554,10 @@
         <v>101</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>356</v>
+        <v>399</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>357</v>
+        <v>400</v>
       </c>
       <c r="AM133" t="s" s="2">
         <v>78</v>
@@ -17553,10 +17568,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17582,16 +17597,16 @@
         <v>104</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>360</v>
+        <v>403</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>361</v>
+        <v>404</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>353</v>
+        <v>405</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>362</v>
+        <v>406</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>78</v>
@@ -17640,7 +17655,7 @@
         <v>78</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>363</v>
+        <v>407</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -17655,10 +17670,10 @@
         <v>101</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>364</v>
+        <v>408</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>365</v>
+        <v>409</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>78</v>
@@ -17669,10 +17684,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>483</v>
+        <v>517</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17695,19 +17710,19 @@
         <v>89</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>368</v>
+        <v>104</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>369</v>
+        <v>518</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>370</v>
+        <v>519</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>371</v>
+        <v>520</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>372</v>
+        <v>521</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>78</v>
@@ -17756,7 +17771,7 @@
         <v>78</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>373</v>
+        <v>517</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -17765,19 +17780,19 @@
         <v>88</v>
       </c>
       <c r="AI135" t="s" s="2">
-        <v>100</v>
+        <v>224</v>
       </c>
       <c r="AJ135" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>374</v>
+        <v>522</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>375</v>
+        <v>523</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>78</v>
+        <v>524</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>78</v>
@@ -17785,10 +17800,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>515</v>
+        <v>525</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>485</v>
+        <v>525</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17799,7 +17814,7 @@
         <v>79</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H136" t="s" s="2">
         <v>78</v>
@@ -17808,22 +17823,22 @@
         <v>78</v>
       </c>
       <c r="J136" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K136" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>378</v>
+        <v>526</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>379</v>
+        <v>527</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>380</v>
+        <v>528</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>381</v>
+        <v>529</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>78</v>
@@ -17872,13 +17887,13 @@
         <v>78</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>382</v>
+        <v>525</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH136" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI136" t="s" s="2">
         <v>100</v>
@@ -17887,10 +17902,10 @@
         <v>101</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>383</v>
+        <v>78</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>384</v>
+        <v>523</v>
       </c>
       <c r="AM136" t="s" s="2">
         <v>78</v>
@@ -17901,10 +17916,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>516</v>
+        <v>530</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>516</v>
+        <v>530</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17915,7 +17930,7 @@
         <v>79</v>
       </c>
       <c r="G137" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H137" t="s" s="2">
         <v>78</v>
@@ -17924,22 +17939,22 @@
         <v>78</v>
       </c>
       <c r="J137" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>104</v>
+        <v>531</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>517</v>
+        <v>532</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>518</v>
+        <v>533</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>519</v>
+        <v>534</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>520</v>
+        <v>535</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>78</v>
@@ -17988,28 +18003,28 @@
         <v>78</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>516</v>
+        <v>530</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI137" t="s" s="2">
-        <v>224</v>
+        <v>100</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>101</v>
+        <v>536</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>521</v>
+        <v>537</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>522</v>
+        <v>538</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>523</v>
+        <v>539</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>78</v>
@@ -18017,10 +18032,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>524</v>
+        <v>540</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>524</v>
+        <v>540</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18043,19 +18058,19 @@
         <v>78</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>104</v>
+        <v>541</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>525</v>
+        <v>542</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>526</v>
+        <v>543</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>527</v>
+        <v>544</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>528</v>
+        <v>545</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>78</v>
@@ -18104,7 +18119,7 @@
         <v>78</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>524</v>
+        <v>540</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>79</v>
@@ -18116,16 +18131,16 @@
         <v>100</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>101</v>
+        <v>546</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>78</v>
+        <v>547</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>522</v>
+        <v>548</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>78</v>
+        <v>549</v>
       </c>
       <c r="AN138" t="s" s="2">
         <v>78</v>
@@ -18133,10 +18148,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>529</v>
+        <v>550</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>529</v>
+        <v>550</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18147,7 +18162,7 @@
         <v>79</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H139" t="s" s="2">
         <v>78</v>
@@ -18156,22 +18171,22 @@
         <v>78</v>
       </c>
       <c r="J139" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>530</v>
+        <v>551</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>531</v>
+        <v>552</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>532</v>
+        <v>553</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>533</v>
+        <v>554</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>534</v>
+        <v>555</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>78</v>
@@ -18220,28 +18235,28 @@
         <v>78</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>529</v>
+        <v>550</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH139" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI139" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>535</v>
+        <v>284</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>536</v>
+        <v>446</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>537</v>
+        <v>556</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>538</v>
+        <v>108</v>
       </c>
       <c r="AN139" t="s" s="2">
         <v>78</v>
@@ -18249,10 +18264,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>539</v>
+        <v>557</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>539</v>
+        <v>557</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18263,7 +18278,7 @@
         <v>79</v>
       </c>
       <c r="G140" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H140" t="s" s="2">
         <v>78</v>
@@ -18275,20 +18290,16 @@
         <v>78</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>540</v>
+        <v>104</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>541</v>
+        <v>105</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="N140" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="O140" t="s" s="2">
-        <v>544</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N140" s="2"/>
+      <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
         <v>78</v>
       </c>
@@ -18336,28 +18347,28 @@
         <v>78</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>539</v>
+        <v>107</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI140" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>545</v>
+        <v>78</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>546</v>
+        <v>78</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>547</v>
+        <v>108</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>548</v>
+        <v>78</v>
       </c>
       <c r="AN140" t="s" s="2">
         <v>78</v>
@@ -18365,21 +18376,21 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G141" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H141" t="s" s="2">
         <v>78</v>
@@ -18388,23 +18399,21 @@
         <v>78</v>
       </c>
       <c r="J141" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>550</v>
+        <v>111</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>551</v>
+        <v>112</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>552</v>
+        <v>113</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="O141" t="s" s="2">
-        <v>554</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>78</v>
       </c>
@@ -18440,40 +18449,40 @@
         <v>78</v>
       </c>
       <c r="AB141" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC141" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD141" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE141" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>549</v>
+        <v>118</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH141" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI141" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>284</v>
+        <v>119</v>
       </c>
       <c r="AK141" t="s" s="2">
-        <v>445</v>
+        <v>78</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>555</v>
+        <v>102</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>78</v>
@@ -18481,10 +18490,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18504,18 +18513,20 @@
         <v>78</v>
       </c>
       <c r="J142" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K142" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>105</v>
+        <v>560</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N142" s="2"/>
+        <v>561</v>
+      </c>
+      <c r="N142" t="s" s="2">
+        <v>562</v>
+      </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
         <v>78</v>
@@ -18564,7 +18575,7 @@
         <v>78</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>107</v>
+        <v>563</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
@@ -18573,16 +18584,16 @@
         <v>88</v>
       </c>
       <c r="AI142" t="s" s="2">
-        <v>78</v>
+        <v>564</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK142" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="AM142" t="s" s="2">
         <v>78</v>
@@ -18593,21 +18604,21 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H143" t="s" s="2">
         <v>78</v>
@@ -18616,19 +18627,19 @@
         <v>78</v>
       </c>
       <c r="J143" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>112</v>
+        <v>566</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>113</v>
+        <v>567</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>114</v>
+        <v>568</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
@@ -18654,43 +18665,41 @@
         <v>78</v>
       </c>
       <c r="X143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y143" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="Y143" s="2"/>
       <c r="Z143" t="s" s="2">
-        <v>78</v>
+        <v>463</v>
       </c>
       <c r="AA143" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB143" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC143" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD143" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE143" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>118</v>
+        <v>569</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH143" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI143" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ143" t="s" s="2">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="AK143" t="s" s="2">
         <v>78</v>
@@ -18707,10 +18716,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18733,16 +18742,16 @@
         <v>89</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>104</v>
+        <v>218</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -18792,7 +18801,7 @@
         <v>78</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>79</v>
@@ -18801,19 +18810,19 @@
         <v>88</v>
       </c>
       <c r="AI144" t="s" s="2">
-        <v>563</v>
+        <v>100</v>
       </c>
       <c r="AJ144" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK144" t="s" s="2">
-        <v>78</v>
+        <v>575</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>102</v>
+        <v>576</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>78</v>
+        <v>577</v>
       </c>
       <c r="AN144" t="s" s="2">
         <v>78</v>
@@ -18821,10 +18830,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>564</v>
+        <v>578</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>564</v>
+        <v>578</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -18847,16 +18856,16 @@
         <v>89</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>565</v>
+        <v>579</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>566</v>
+        <v>580</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>567</v>
+        <v>581</v>
       </c>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
@@ -18882,11 +18891,13 @@
         <v>78</v>
       </c>
       <c r="X145" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="Y145" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y145" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z145" t="s" s="2">
-        <v>462</v>
+        <v>78</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>78</v>
@@ -18904,7 +18915,7 @@
         <v>78</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>568</v>
+        <v>582</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>79</v>
@@ -18933,10 +18944,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>569</v>
+        <v>583</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>569</v>
+        <v>583</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -18947,7 +18958,7 @@
         <v>79</v>
       </c>
       <c r="G146" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H146" t="s" s="2">
         <v>78</v>
@@ -18956,21 +18967,23 @@
         <v>78</v>
       </c>
       <c r="J146" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>218</v>
+        <v>584</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>570</v>
+        <v>585</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>571</v>
+        <v>586</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="O146" s="2"/>
+        <v>587</v>
+      </c>
+      <c r="O146" t="s" s="2">
+        <v>588</v>
+      </c>
       <c r="P146" t="s" s="2">
         <v>78</v>
       </c>
@@ -19018,13 +19031,13 @@
         <v>78</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>573</v>
+        <v>583</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH146" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI146" t="s" s="2">
         <v>100</v>
@@ -19033,13 +19046,13 @@
         <v>101</v>
       </c>
       <c r="AK146" t="s" s="2">
-        <v>574</v>
+        <v>78</v>
       </c>
       <c r="AL146" t="s" s="2">
-        <v>575</v>
+        <v>589</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>576</v>
+        <v>78</v>
       </c>
       <c r="AN146" t="s" s="2">
         <v>78</v>
@@ -19047,10 +19060,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>577</v>
+        <v>590</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>577</v>
+        <v>590</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19070,20 +19083,18 @@
         <v>78</v>
       </c>
       <c r="J147" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K147" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>578</v>
+        <v>105</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="N147" t="s" s="2">
-        <v>580</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N147" s="2"/>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
         <v>78</v>
@@ -19132,7 +19143,7 @@
         <v>78</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>581</v>
+        <v>107</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>79</v>
@@ -19141,16 +19152,16 @@
         <v>88</v>
       </c>
       <c r="AI147" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK147" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="AM147" t="s" s="2">
         <v>78</v>
@@ -19161,14 +19172,14 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>582</v>
+        <v>591</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>582</v>
+        <v>591</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
@@ -19187,20 +19198,18 @@
         <v>78</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>583</v>
+        <v>111</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>584</v>
+        <v>112</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>585</v>
+        <v>113</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="O148" t="s" s="2">
-        <v>587</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
         <v>78</v>
       </c>
@@ -19236,19 +19245,19 @@
         <v>78</v>
       </c>
       <c r="AB148" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC148" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD148" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE148" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>582</v>
+        <v>118</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -19260,13 +19269,13 @@
         <v>100</v>
       </c>
       <c r="AJ148" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK148" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>588</v>
+        <v>102</v>
       </c>
       <c r="AM148" t="s" s="2">
         <v>78</v>
@@ -19277,42 +19286,46 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
-        <v>78</v>
+        <v>593</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G149" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H149" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I149" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J149" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>105</v>
+        <v>594</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N149" s="2"/>
-      <c r="O149" s="2"/>
+        <v>595</v>
+      </c>
+      <c r="N149" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O149" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="P149" t="s" s="2">
         <v>78</v>
       </c>
@@ -19360,25 +19373,25 @@
         <v>78</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>107</v>
+        <v>596</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH149" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI149" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ149" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK149" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="AM149" t="s" s="2">
         <v>78</v>
@@ -19389,21 +19402,21 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G150" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H150" t="s" s="2">
         <v>78</v>
@@ -19415,18 +19428,20 @@
         <v>78</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>111</v>
+        <v>241</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>112</v>
+        <v>598</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>113</v>
+        <v>599</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O150" s="2"/>
+        <v>600</v>
+      </c>
+      <c r="O150" t="s" s="2">
+        <v>601</v>
+      </c>
       <c r="P150" t="s" s="2">
         <v>78</v>
       </c>
@@ -19450,49 +19465,49 @@
         <v>78</v>
       </c>
       <c r="X150" t="s" s="2">
-        <v>78</v>
+        <v>152</v>
       </c>
       <c r="Y150" t="s" s="2">
-        <v>78</v>
+        <v>602</v>
       </c>
       <c r="Z150" t="s" s="2">
-        <v>78</v>
+        <v>603</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB150" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC150" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD150" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE150" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>118</v>
+        <v>597</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH150" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI150" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ150" t="s" s="2">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>78</v>
+        <v>604</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>102</v>
+        <v>605</v>
       </c>
       <c r="AM150" t="s" s="2">
         <v>78</v>
@@ -19503,45 +19518,45 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>591</v>
+        <v>606</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>591</v>
+        <v>606</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
-        <v>592</v>
+        <v>78</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G151" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H151" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I151" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J151" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>111</v>
+        <v>607</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>593</v>
+        <v>608</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>594</v>
+        <v>609</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>114</v>
+        <v>610</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>215</v>
+        <v>611</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>78</v>
@@ -19590,28 +19605,28 @@
         <v>78</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>595</v>
+        <v>606</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH151" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI151" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ151" t="s" s="2">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>78</v>
+        <v>612</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>102</v>
+        <v>613</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>78</v>
+        <v>614</v>
       </c>
       <c r="AN151" t="s" s="2">
         <v>78</v>
@@ -19619,10 +19634,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>596</v>
+        <v>615</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>596</v>
+        <v>615</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -19633,7 +19648,7 @@
         <v>79</v>
       </c>
       <c r="G152" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H152" t="s" s="2">
         <v>78</v>
@@ -19645,19 +19660,17 @@
         <v>78</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>241</v>
+        <v>531</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>597</v>
+        <v>532</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="N152" t="s" s="2">
-        <v>599</v>
-      </c>
+        <v>533</v>
+      </c>
+      <c r="N152" s="2"/>
       <c r="O152" t="s" s="2">
-        <v>600</v>
+        <v>616</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>78</v>
@@ -19682,13 +19695,13 @@
         <v>78</v>
       </c>
       <c r="X152" t="s" s="2">
-        <v>152</v>
+        <v>78</v>
       </c>
       <c r="Y152" t="s" s="2">
-        <v>601</v>
+        <v>78</v>
       </c>
       <c r="Z152" t="s" s="2">
-        <v>602</v>
+        <v>78</v>
       </c>
       <c r="AA152" t="s" s="2">
         <v>78</v>
@@ -19706,28 +19719,28 @@
         <v>78</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>596</v>
+        <v>615</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH152" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI152" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ152" t="s" s="2">
-        <v>101</v>
+        <v>617</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>603</v>
+        <v>537</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>604</v>
+        <v>538</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>78</v>
+        <v>539</v>
       </c>
       <c r="AN152" t="s" s="2">
         <v>78</v>
@@ -19735,10 +19748,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>605</v>
+        <v>618</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>605</v>
+        <v>618</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -19761,19 +19774,19 @@
         <v>78</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>606</v>
+        <v>541</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>607</v>
+        <v>542</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>608</v>
+        <v>543</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>609</v>
+        <v>544</v>
       </c>
       <c r="O153" t="s" s="2">
-        <v>610</v>
+        <v>619</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>78</v>
@@ -19822,7 +19835,7 @@
         <v>78</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>605</v>
+        <v>618</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>79</v>
@@ -19837,13 +19850,13 @@
         <v>101</v>
       </c>
       <c r="AK153" t="s" s="2">
-        <v>611</v>
+        <v>547</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>612</v>
+        <v>548</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>613</v>
+        <v>549</v>
       </c>
       <c r="AN153" t="s" s="2">
         <v>78</v>
@@ -19851,10 +19864,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -19877,17 +19890,19 @@
         <v>78</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>530</v>
+        <v>621</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>531</v>
+        <v>622</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="N154" s="2"/>
+        <v>623</v>
+      </c>
+      <c r="N154" t="s" s="2">
+        <v>554</v>
+      </c>
       <c r="O154" t="s" s="2">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>78</v>
@@ -19936,7 +19951,7 @@
         <v>78</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>79</v>
@@ -19948,250 +19963,18 @@
         <v>100</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>616</v>
+        <v>284</v>
       </c>
       <c r="AK154" t="s" s="2">
-        <v>536</v>
+        <v>78</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>537</v>
+        <v>625</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>538</v>
+        <v>78</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="B155" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="C155" s="2"/>
-      <c r="D155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E155" s="2"/>
-      <c r="F155" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G155" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K155" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="L155" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="M155" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="N155" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="O155" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="P155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q155" s="2"/>
-      <c r="R155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF155" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="AG155" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH155" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI155" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ155" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK155" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="AL155" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="AM155" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="AN155" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="B156" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="C156" s="2"/>
-      <c r="D156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E156" s="2"/>
-      <c r="F156" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G156" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K156" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="L156" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="M156" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="N156" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="O156" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="P156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q156" s="2"/>
-      <c r="R156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF156" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="AG156" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH156" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI156" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ156" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="AK156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL156" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="AM156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN156" t="s" s="2">
         <v>78</v>
       </c>
     </row>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:05:52+00:00</t>
+    <t>2024-05-23T12:32:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -709,8 +709,8 @@
     <t>Organizations are known by a variety of ids. Some institutions maintain several, and most collect identifiers for exchange with other organizations concerning the organization.</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:system}
-</t>
+    <t>pattern:system}
+pattern:type}</t>
   </si>
   <si>
     <t>Slice based on the identifier.system pattern</t>
@@ -6333,7 +6333,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>88</v>
@@ -7365,7 +7365,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>88</v>
@@ -8397,7 +8397,7 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>88</v>
@@ -11723,7 +11723,7 @@
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G83" t="s" s="2">
         <v>88</v>
@@ -12755,7 +12755,7 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G92" t="s" s="2">
         <v>88</v>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:32:02+00:00</t>
+    <t>2024-05-23T14:35:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T14:35:00+00:00</t>
+    <t>2024-06-11T15:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:12+00:00</t>
+    <t>2024-06-11T15:33:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:34+00:00</t>
+    <t>2024-07-02T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Interop'Santé (http://interopsante.org/)</t>
   </si>
   <si>
-    <t>InteropSanté (fhir@interopsante.org(WORK))</t>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -1446,7 +1446,7 @@
     <t>http://hl7.org/fhir/ValueSet/organization-type</t>
   </si>
   <si>
-    <t xml:space="preserve">value:coding.system}
+    <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-08T11:39:28+00:00</t>
+    <t>2024-07-17T12:13:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T12:13:27+00:00</t>
+    <t>2024-07-17T14:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.1</t>
+    <t>2.1.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T14:21:13+00:00</t>
+    <t>2024-07-17T15:15:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T15:15:49+00:00</t>
+    <t>2024-07-17T15:35:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T07:11:02+00:00</t>
+    <t>2024-07-25T15:28:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:28:42+00:00</t>
+    <t>2024-07-25T15:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:29:18+00:00</t>
+    <t>2024-07-25T15:44:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:44:10+00:00</t>
+    <t>2024-08-01T13:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0-ballot</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-03T15:38:30+00:00</t>
+    <t>2024-09-04T07:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T07:28:39+00:00</t>
+    <t>2024-09-04T07:33:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-06T12:53:53+00:00</t>
+    <t>2024-10-28T08:07:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -424,7 +424,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -444,7 +444,7 @@
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -1688,7 +1688,7 @@
     <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats).  This data type may be used to convey addresses for use in delivering mail as well as for visiting locations which might not be valid for mail delivery.  There are a variety of postal address formats defined around the world.</t>
   </si>
   <si>
-    <t>Note: address is intended to describe postal addresses for administrative purposes, not to describe absolute geographical coordinates.  Postal addresses are often used as proxies for physical locations (also see the [Location](location.html#) resource).</t>
+    <t>Note: address is intended to describe postal addresses for administrative purposes, not to describe absolute geographical coordinates.  Postal addresses are often used as proxies for physical locations (also see the [Location](http://hl7.org/fhir/R4/location.html#) resource).</t>
   </si>
   <si>
     <t>May need to keep track of the organization's addresses for contacting, billing or reporting requirements.</t>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>88</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>88</v>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>88</v>
@@ -6395,7 +6395,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>88</v>
@@ -6511,7 +6511,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>88</v>
@@ -7425,7 +7425,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>88</v>
@@ -8455,7 +8455,7 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>88</v>
@@ -10743,7 +10743,7 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>88</v>
@@ -11773,7 +11773,7 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G84" t="s" s="2">
         <v>88</v>
@@ -12803,7 +12803,7 @@
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G93" t="s" s="2">
         <v>88</v>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:07:18+00:00</t>
+    <t>2024-10-28T08:08:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5612" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5286" uniqueCount="599">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:08:30+00:00</t>
+    <t>2024-10-29T10:42:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1288,25 +1288,25 @@
     <t>Organization.identifier:finess.assigner</t>
   </si>
   <si>
-    <t>Organization.identifier:adeliRang</t>
-  </si>
-  <si>
-    <t>adeliRang</t>
-  </si>
-  <si>
-    <t>Identifiant ADELI rang (9 chiffres ADELI + 2 chiffres RANG)</t>
-  </si>
-  <si>
-    <t>Organization.identifier:adeliRang.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier:adeliRang.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier:adeliRang.use</t>
-  </si>
-  <si>
-    <t>Organization.identifier:adeliRang.type</t>
+    <t>Organization.identifier:rppsRang</t>
+  </si>
+  <si>
+    <t>rppsRang</t>
+  </si>
+  <si>
+    <t>RPPS rang (11 chiffres RPPS + 2 chiffres RANG)</t>
+  </si>
+  <si>
+    <t>Organization.identifier:rppsRang.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier:rppsRang.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier:rppsRang.use</t>
+  </si>
+  <si>
+    <t>Organization.identifier:rppsRang.type</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -1315,42 +1315,6 @@
     &lt;code value="INTRN"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>Organization.identifier:adeliRang.system</t>
-  </si>
-  <si>
-    <t>https://adelirang.esante.gouv.fr</t>
-  </si>
-  <si>
-    <t>Organization.identifier:adeliRang.value</t>
-  </si>
-  <si>
-    <t>Organization.identifier:adeliRang.period</t>
-  </si>
-  <si>
-    <t>Organization.identifier:adeliRang.assigner</t>
-  </si>
-  <si>
-    <t>Organization.identifier:rppsRang</t>
-  </si>
-  <si>
-    <t>rppsRang</t>
-  </si>
-  <si>
-    <t>RPPS rang (11 chiffres RPPS + 2 chiffres RANG)</t>
-  </si>
-  <si>
-    <t>Organization.identifier:rppsRang.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier:rppsRang.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier:rppsRang.use</t>
-  </si>
-  <si>
-    <t>Organization.identifier:rppsRang.type</t>
   </si>
   <si>
     <t>Organization.identifier:rppsRang.system</t>
@@ -2230,7 +2194,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN154"/>
+  <dimension ref="A1:AN145"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="63.859375" customWidth="true" bestFit="true"/>
@@ -12221,11 +12185,9 @@
         <v>421</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="C88" t="s" s="2">
-        <v>422</v>
-      </c>
+        <v>421</v>
+      </c>
+      <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
         <v>78</v>
       </c>
@@ -12234,34 +12196,38 @@
         <v>79</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J88" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>215</v>
+        <v>386</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="M88" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N88" s="2"/>
+      <c r="N88" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="O88" t="s" s="2">
-        <v>218</v>
+        <v>425</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q88" s="2"/>
+      <c r="Q88" t="s" s="2">
+        <v>426</v>
+      </c>
       <c r="R88" t="s" s="2">
         <v>78</v>
       </c>
@@ -12305,39 +12271,39 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>214</v>
+        <v>421</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>221</v>
+        <v>78</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>222</v>
+        <v>427</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>223</v>
+        <v>428</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>224</v>
+        <v>429</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>225</v>
+        <v>430</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>226</v>
+        <v>431</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12348,7 +12314,7 @@
         <v>79</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>78</v>
@@ -12357,19 +12323,23 @@
         <v>78</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>102</v>
+        <v>238</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>103</v>
+        <v>432</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
+        <v>433</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>435</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>78</v>
       </c>
@@ -12393,74 +12363,74 @@
         <v>78</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>78</v>
+        <v>158</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>78</v>
+        <v>436</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>78</v>
+        <v>437</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>438</v>
+      </c>
+      <c r="AC89" s="2"/>
       <c r="AD89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>105</v>
+        <v>431</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>78</v>
+        <v>439</v>
       </c>
       <c r="AL89" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AM89" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="AM89" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AN89" t="s" s="2">
-        <v>78</v>
+        <v>441</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="C90" s="2"/>
+        <v>431</v>
+      </c>
+      <c r="C90" t="s" s="2">
+        <v>443</v>
+      </c>
       <c r="D90" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>78</v>
@@ -12469,21 +12439,23 @@
         <v>78</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>109</v>
+        <v>238</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>110</v>
+        <v>432</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>111</v>
+        <v>433</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O90" s="2"/>
+        <v>434</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>435</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>78</v>
       </c>
@@ -12507,31 +12479,29 @@
         <v>78</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
-        <v>78</v>
+        <v>444</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>116</v>
+        <v>431</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -12543,27 +12513,27 @@
         <v>78</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>78</v>
+        <v>439</v>
       </c>
       <c r="AL90" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AM90" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="AM90" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AN90" t="s" s="2">
-        <v>78</v>
+        <v>441</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>426</v>
+        <v>445</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>228</v>
+        <v>446</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12580,26 +12550,22 @@
         <v>78</v>
       </c>
       <c r="I91" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>168</v>
+        <v>102</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>229</v>
+        <v>103</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>232</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>78</v>
       </c>
@@ -12623,13 +12589,13 @@
         <v>78</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>233</v>
+        <v>78</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>289</v>
+        <v>78</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>290</v>
+        <v>78</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>78</v>
@@ -12647,7 +12613,7 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>235</v>
+        <v>105</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -12659,13 +12625,13 @@
         <v>78</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>191</v>
+        <v>78</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>236</v>
+        <v>106</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>78</v>
@@ -12676,21 +12642,21 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>427</v>
+        <v>447</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>237</v>
+        <v>448</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>78</v>
@@ -12699,23 +12665,21 @@
         <v>78</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>238</v>
+        <v>109</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>239</v>
+        <v>110</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>240</v>
+        <v>111</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>78</v>
       </c>
@@ -12724,7 +12688,7 @@
         <v>78</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>415</v>
+        <v>78</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>78</v>
@@ -12739,49 +12703,49 @@
         <v>78</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>293</v>
+        <v>78</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>294</v>
+        <v>78</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC92" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>244</v>
+        <v>116</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>245</v>
+        <v>78</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>236</v>
+        <v>106</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>78</v>
@@ -12792,10 +12756,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>428</v>
+        <v>449</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>246</v>
+        <v>450</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12818,19 +12782,19 @@
         <v>89</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>247</v>
+        <v>339</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>248</v>
+        <v>340</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>249</v>
+        <v>341</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>250</v>
+        <v>342</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>78</v>
@@ -12840,10 +12804,10 @@
         <v>78</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>429</v>
+        <v>78</v>
       </c>
       <c r="T93" t="s" s="2">
-        <v>251</v>
+        <v>78</v>
       </c>
       <c r="U93" t="s" s="2">
         <v>78</v>
@@ -12879,13 +12843,13 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>252</v>
+        <v>343</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>78</v>
@@ -12894,13 +12858,13 @@
         <v>100</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>253</v>
+        <v>344</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>254</v>
+        <v>345</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>255</v>
+        <v>78</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>78</v>
@@ -12908,10 +12872,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>430</v>
+        <v>451</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>256</v>
+        <v>452</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12931,20 +12895,18 @@
         <v>78</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K94" t="s" s="2">
         <v>102</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>257</v>
+        <v>103</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N94" s="2"/>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>78</v>
@@ -12957,7 +12919,7 @@
         <v>78</v>
       </c>
       <c r="T94" t="s" s="2">
-        <v>260</v>
+        <v>78</v>
       </c>
       <c r="U94" t="s" s="2">
         <v>78</v>
@@ -12993,7 +12955,7 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>261</v>
+        <v>105</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13005,16 +12967,16 @@
         <v>78</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>262</v>
+        <v>78</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>263</v>
+        <v>106</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>264</v>
+        <v>78</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>78</v>
@@ -13022,21 +12984,21 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>431</v>
+        <v>453</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>265</v>
+        <v>454</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>78</v>
@@ -13045,18 +13007,20 @@
         <v>78</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>266</v>
+        <v>109</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>267</v>
+        <v>110</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N95" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>78</v>
@@ -13093,40 +13057,40 @@
         <v>78</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC95" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>269</v>
+        <v>116</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>270</v>
+        <v>78</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>271</v>
+        <v>106</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>272</v>
+        <v>78</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>78</v>
@@ -13134,10 +13098,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>432</v>
+        <v>455</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>273</v>
+        <v>456</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13145,7 +13109,7 @@
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G96" t="s" s="2">
         <v>88</v>
@@ -13160,18 +13124,20 @@
         <v>89</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>274</v>
+        <v>130</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>275</v>
+        <v>352</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>276</v>
+        <v>353</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="O96" s="2"/>
+        <v>354</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>78</v>
       </c>
@@ -13219,7 +13185,7 @@
         <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>278</v>
+        <v>357</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13234,13 +13200,13 @@
         <v>100</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>279</v>
+        <v>358</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>280</v>
+        <v>359</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>281</v>
+        <v>78</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>78</v>
@@ -13248,10 +13214,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>433</v>
+        <v>457</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>433</v>
+        <v>458</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13268,32 +13234,28 @@
         <v>78</v>
       </c>
       <c r="I97" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J97" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>386</v>
+        <v>102</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>434</v>
+        <v>362</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>435</v>
+        <v>363</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>437</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q97" t="s" s="2">
-        <v>438</v>
-      </c>
+      <c r="Q97" s="2"/>
       <c r="R97" t="s" s="2">
         <v>78</v>
       </c>
@@ -13337,7 +13299,7 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>433</v>
+        <v>365</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13352,24 +13314,24 @@
         <v>100</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>439</v>
+        <v>366</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>440</v>
+        <v>367</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>441</v>
+        <v>78</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>442</v>
+        <v>78</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>443</v>
+        <v>459</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>443</v>
+        <v>460</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13380,7 +13342,7 @@
         <v>79</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>78</v>
@@ -13392,19 +13354,17 @@
         <v>89</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>238</v>
+        <v>168</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>444</v>
+        <v>461</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>446</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>447</v>
+        <v>372</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>78</v>
@@ -13429,35 +13389,37 @@
         <v>78</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>158</v>
+        <v>78</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>448</v>
+        <v>78</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>449</v>
+        <v>78</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AC98" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>443</v>
+        <v>373</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>78</v>
@@ -13466,28 +13428,26 @@
         <v>100</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>451</v>
+        <v>374</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>452</v>
+        <v>375</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>453</v>
+        <v>78</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="C99" t="s" s="2">
-        <v>455</v>
-      </c>
+        <v>463</v>
+      </c>
+      <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
         <v>78</v>
       </c>
@@ -13508,19 +13468,17 @@
         <v>89</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>238</v>
+        <v>102</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>444</v>
+        <v>378</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>446</v>
-      </c>
+        <v>379</v>
+      </c>
+      <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>447</v>
+        <v>380</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>78</v>
@@ -13545,11 +13503,13 @@
         <v>78</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="Y99" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z99" t="s" s="2">
-        <v>456</v>
+        <v>78</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>78</v>
@@ -13567,13 +13527,13 @@
         <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>443</v>
+        <v>381</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>78</v>
@@ -13582,24 +13542,24 @@
         <v>100</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>451</v>
+        <v>382</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>452</v>
+        <v>383</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>453</v>
+        <v>78</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13619,19 +13579,23 @@
         <v>78</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>102</v>
+        <v>386</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>103</v>
+        <v>387</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N100" s="2"/>
-      <c r="O100" s="2"/>
+        <v>388</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>390</v>
+      </c>
       <c r="P100" t="s" s="2">
         <v>78</v>
       </c>
@@ -13679,7 +13643,7 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>105</v>
+        <v>391</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -13691,13 +13655,13 @@
         <v>78</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>78</v>
+        <v>392</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>106</v>
+        <v>393</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>78</v>
@@ -13708,21 +13672,21 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>78</v>
@@ -13731,21 +13695,23 @@
         <v>78</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>110</v>
+        <v>396</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>111</v>
+        <v>397</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O101" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="O101" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="P101" t="s" s="2">
         <v>78</v>
       </c>
@@ -13781,37 +13747,37 @@
         <v>78</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD101" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>116</v>
+        <v>400</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>78</v>
+        <v>401</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>106</v>
+        <v>402</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>78</v>
@@ -13822,18 +13788,20 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="C102" s="2"/>
+        <v>431</v>
+      </c>
+      <c r="C102" t="s" s="2">
+        <v>469</v>
+      </c>
       <c r="D102" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>88</v>
@@ -13848,19 +13816,19 @@
         <v>89</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>146</v>
+        <v>238</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>339</v>
+        <v>470</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>340</v>
+        <v>433</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>341</v>
+        <v>434</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>342</v>
+        <v>435</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>78</v>
@@ -13885,13 +13853,11 @@
         <v>78</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y102" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="Y102" s="2"/>
       <c r="Z102" t="s" s="2">
-        <v>78</v>
+        <v>471</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>78</v>
@@ -13909,7 +13875,7 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>343</v>
+        <v>431</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -13924,24 +13890,24 @@
         <v>100</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>344</v>
+        <v>439</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>345</v>
+        <v>440</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>78</v>
+        <v>441</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>464</v>
+        <v>446</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14050,10 +14016,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>466</v>
+        <v>448</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14164,10 +14130,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>468</v>
+        <v>450</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14190,19 +14156,19 @@
         <v>89</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>78</v>
@@ -14251,13 +14217,13 @@
         <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>357</v>
+        <v>343</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>78</v>
@@ -14266,10 +14232,10 @@
         <v>100</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>358</v>
+        <v>344</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>359</v>
+        <v>345</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>78</v>
@@ -14280,10 +14246,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>470</v>
+        <v>452</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14303,20 +14269,18 @@
         <v>78</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K106" t="s" s="2">
         <v>102</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>362</v>
+        <v>103</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>364</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N106" s="2"/>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>78</v>
@@ -14365,7 +14329,7 @@
         <v>78</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>365</v>
+        <v>105</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -14377,13 +14341,13 @@
         <v>78</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>366</v>
+        <v>78</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>367</v>
+        <v>106</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>78</v>
@@ -14394,21 +14358,21 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>472</v>
+        <v>454</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>78</v>
@@ -14417,21 +14381,21 @@
         <v>78</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>473</v>
+        <v>110</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N107" s="2"/>
-      <c r="O107" t="s" s="2">
-        <v>372</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>78</v>
       </c>
@@ -14467,37 +14431,37 @@
         <v>78</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC107" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD107" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>373</v>
+        <v>116</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>374</v>
+        <v>78</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>375</v>
+        <v>106</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>78</v>
@@ -14508,10 +14472,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>475</v>
+        <v>456</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14519,7 +14483,7 @@
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G108" t="s" s="2">
         <v>88</v>
@@ -14534,17 +14498,19 @@
         <v>89</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>378</v>
+        <v>352</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N108" s="2"/>
+        <v>353</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>354</v>
+      </c>
       <c r="O108" t="s" s="2">
-        <v>380</v>
+        <v>355</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>78</v>
@@ -14593,7 +14559,7 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>381</v>
+        <v>357</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -14608,10 +14574,10 @@
         <v>100</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>382</v>
+        <v>358</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>78</v>
@@ -14622,10 +14588,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>477</v>
+        <v>458</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14648,20 +14614,18 @@
         <v>89</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>386</v>
+        <v>102</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>387</v>
+        <v>362</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>388</v>
+        <v>363</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>390</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>78</v>
       </c>
@@ -14709,7 +14673,7 @@
         <v>78</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>391</v>
+        <v>365</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -14724,10 +14688,10 @@
         <v>100</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>392</v>
+        <v>366</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>393</v>
+        <v>367</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>78</v>
@@ -14738,10 +14702,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>479</v>
+        <v>460</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14764,19 +14728,17 @@
         <v>89</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>102</v>
+        <v>168</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>396</v>
+        <v>461</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="N110" s="2"/>
       <c r="O110" t="s" s="2">
-        <v>399</v>
+        <v>372</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>78</v>
@@ -14825,7 +14787,7 @@
         <v>78</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>400</v>
+        <v>373</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -14840,10 +14802,10 @@
         <v>100</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>401</v>
+        <v>374</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>402</v>
+        <v>375</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>78</v>
@@ -14857,11 +14819,9 @@
         <v>480</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="C111" t="s" s="2">
-        <v>481</v>
-      </c>
+        <v>463</v>
+      </c>
+      <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
         <v>78</v>
       </c>
@@ -14882,19 +14842,17 @@
         <v>89</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>238</v>
+        <v>102</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>482</v>
+        <v>378</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>446</v>
-      </c>
+        <v>379</v>
+      </c>
+      <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>447</v>
+        <v>380</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>78</v>
@@ -14919,11 +14877,13 @@
         <v>78</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="Y111" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z111" t="s" s="2">
-        <v>483</v>
+        <v>78</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>78</v>
@@ -14941,13 +14901,13 @@
         <v>78</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>443</v>
+        <v>381</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>78</v>
@@ -14956,24 +14916,24 @@
         <v>100</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>451</v>
+        <v>382</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>452</v>
+        <v>383</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>453</v>
+        <v>78</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14993,19 +14953,23 @@
         <v>78</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>102</v>
+        <v>386</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>103</v>
+        <v>387</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N112" s="2"/>
-      <c r="O112" s="2"/>
+        <v>388</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="O112" t="s" s="2">
+        <v>390</v>
+      </c>
       <c r="P112" t="s" s="2">
         <v>78</v>
       </c>
@@ -15053,7 +15017,7 @@
         <v>78</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>105</v>
+        <v>391</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -15065,13 +15029,13 @@
         <v>78</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>78</v>
+        <v>392</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>106</v>
+        <v>393</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>78</v>
@@ -15082,21 +15046,21 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>78</v>
@@ -15105,21 +15069,23 @@
         <v>78</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>110</v>
+        <v>396</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>111</v>
+        <v>397</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O113" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="O113" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="P113" t="s" s="2">
         <v>78</v>
       </c>
@@ -15155,37 +15121,37 @@
         <v>78</v>
       </c>
       <c r="AB113" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC113" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD113" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE113" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>116</v>
+        <v>400</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>78</v>
+        <v>401</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>106</v>
+        <v>402</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>78</v>
@@ -15196,18 +15162,20 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="C114" s="2"/>
+        <v>431</v>
+      </c>
+      <c r="C114" t="s" s="2">
+        <v>484</v>
+      </c>
       <c r="D114" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G114" t="s" s="2">
         <v>88</v>
@@ -15222,19 +15190,19 @@
         <v>89</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>146</v>
+        <v>238</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>339</v>
+        <v>485</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>340</v>
+        <v>433</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>341</v>
+        <v>434</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>342</v>
+        <v>435</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>78</v>
@@ -15259,13 +15227,11 @@
         <v>78</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y114" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="Y114" s="2"/>
       <c r="Z114" t="s" s="2">
-        <v>78</v>
+        <v>486</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>78</v>
@@ -15283,7 +15249,7 @@
         <v>78</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>343</v>
+        <v>431</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
@@ -15298,16 +15264,16 @@
         <v>100</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>344</v>
+        <v>439</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>345</v>
+        <v>440</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>78</v>
+        <v>441</v>
       </c>
     </row>
     <row r="115">
@@ -15315,7 +15281,7 @@
         <v>487</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>464</v>
+        <v>446</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15427,7 +15393,7 @@
         <v>488</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>466</v>
+        <v>448</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15541,7 +15507,7 @@
         <v>489</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>468</v>
+        <v>450</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15564,19 +15530,19 @@
         <v>89</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>78</v>
@@ -15625,13 +15591,13 @@
         <v>78</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>357</v>
+        <v>343</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>78</v>
@@ -15640,10 +15606,10 @@
         <v>100</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>358</v>
+        <v>344</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>359</v>
+        <v>345</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>78</v>
@@ -15657,7 +15623,7 @@
         <v>490</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>470</v>
+        <v>452</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15677,20 +15643,18 @@
         <v>78</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K118" t="s" s="2">
         <v>102</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>362</v>
+        <v>103</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>364</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N118" s="2"/>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>78</v>
@@ -15739,7 +15703,7 @@
         <v>78</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>365</v>
+        <v>105</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -15751,13 +15715,13 @@
         <v>78</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>366</v>
+        <v>78</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>367</v>
+        <v>106</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>78</v>
@@ -15771,18 +15735,18 @@
         <v>491</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>472</v>
+        <v>454</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>78</v>
@@ -15791,21 +15755,21 @@
         <v>78</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>473</v>
+        <v>110</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N119" s="2"/>
-      <c r="O119" t="s" s="2">
-        <v>372</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>78</v>
       </c>
@@ -15841,37 +15805,37 @@
         <v>78</v>
       </c>
       <c r="AB119" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC119" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD119" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE119" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>373</v>
+        <v>116</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>374</v>
+        <v>78</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>375</v>
+        <v>106</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>78</v>
@@ -15885,7 +15849,7 @@
         <v>492</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>475</v>
+        <v>456</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15893,7 +15857,7 @@
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G120" t="s" s="2">
         <v>88</v>
@@ -15908,17 +15872,19 @@
         <v>89</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>378</v>
+        <v>352</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N120" s="2"/>
+        <v>353</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>354</v>
+      </c>
       <c r="O120" t="s" s="2">
-        <v>380</v>
+        <v>355</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>78</v>
@@ -15967,7 +15933,7 @@
         <v>78</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>381</v>
+        <v>357</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -15982,10 +15948,10 @@
         <v>100</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>382</v>
+        <v>358</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>78</v>
@@ -15999,7 +15965,7 @@
         <v>493</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>477</v>
+        <v>458</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16022,20 +15988,18 @@
         <v>89</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>386</v>
+        <v>102</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>387</v>
+        <v>362</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>388</v>
+        <v>363</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="O121" t="s" s="2">
-        <v>390</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
         <v>78</v>
       </c>
@@ -16083,7 +16047,7 @@
         <v>78</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>391</v>
+        <v>365</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -16098,10 +16062,10 @@
         <v>100</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>392</v>
+        <v>366</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>393</v>
+        <v>367</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>78</v>
@@ -16115,7 +16079,7 @@
         <v>494</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>479</v>
+        <v>460</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16138,19 +16102,17 @@
         <v>89</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>102</v>
+        <v>168</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>396</v>
+        <v>461</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>399</v>
+        <v>372</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>78</v>
@@ -16199,7 +16161,7 @@
         <v>78</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>400</v>
+        <v>373</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -16214,10 +16176,10 @@
         <v>100</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>401</v>
+        <v>374</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>402</v>
+        <v>375</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>78</v>
@@ -16231,11 +16193,9 @@
         <v>495</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="C123" t="s" s="2">
-        <v>496</v>
-      </c>
+        <v>463</v>
+      </c>
+      <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
         <v>78</v>
       </c>
@@ -16256,19 +16216,17 @@
         <v>89</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>238</v>
+        <v>102</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>497</v>
+        <v>378</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>446</v>
-      </c>
+        <v>379</v>
+      </c>
+      <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>447</v>
+        <v>380</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>78</v>
@@ -16293,11 +16251,13 @@
         <v>78</v>
       </c>
       <c r="X123" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="Y123" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y123" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z123" t="s" s="2">
-        <v>498</v>
+        <v>78</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>78</v>
@@ -16315,13 +16275,13 @@
         <v>78</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>443</v>
+        <v>381</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>78</v>
@@ -16330,24 +16290,24 @@
         <v>100</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>451</v>
+        <v>382</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>452</v>
+        <v>383</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>453</v>
+        <v>78</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16367,19 +16327,23 @@
         <v>78</v>
       </c>
       <c r="J124" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>102</v>
+        <v>386</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>103</v>
+        <v>387</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N124" s="2"/>
-      <c r="O124" s="2"/>
+        <v>388</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="O124" t="s" s="2">
+        <v>390</v>
+      </c>
       <c r="P124" t="s" s="2">
         <v>78</v>
       </c>
@@ -16427,7 +16391,7 @@
         <v>78</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>105</v>
+        <v>391</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -16439,13 +16403,13 @@
         <v>78</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>78</v>
+        <v>392</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>106</v>
+        <v>393</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>78</v>
@@ -16456,21 +16420,21 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>78</v>
@@ -16479,21 +16443,23 @@
         <v>78</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>110</v>
+        <v>396</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>111</v>
+        <v>397</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O125" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="O125" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="P125" t="s" s="2">
         <v>78</v>
       </c>
@@ -16529,37 +16495,37 @@
         <v>78</v>
       </c>
       <c r="AB125" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC125" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD125" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE125" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>116</v>
+        <v>400</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>78</v>
+        <v>401</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>106</v>
+        <v>402</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>78</v>
@@ -16570,10 +16536,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>462</v>
+        <v>498</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16581,7 +16547,7 @@
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G126" t="s" s="2">
         <v>88</v>
@@ -16596,19 +16562,19 @@
         <v>89</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>146</v>
+        <v>102</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>339</v>
+        <v>499</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>340</v>
+        <v>500</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>341</v>
+        <v>501</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>342</v>
+        <v>502</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>78</v>
@@ -16657,28 +16623,28 @@
         <v>78</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>343</v>
+        <v>498</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>78</v>
+        <v>221</v>
       </c>
       <c r="AJ126" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>344</v>
+        <v>503</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>345</v>
+        <v>504</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>78</v>
+        <v>505</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>78</v>
@@ -16686,10 +16652,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>464</v>
+        <v>506</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16700,7 +16666,7 @@
         <v>79</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H127" t="s" s="2">
         <v>78</v>
@@ -16715,13 +16681,17 @@
         <v>102</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>103</v>
+        <v>507</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N127" s="2"/>
-      <c r="O127" s="2"/>
+        <v>508</v>
+      </c>
+      <c r="N127" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="O127" t="s" s="2">
+        <v>510</v>
+      </c>
       <c r="P127" t="s" s="2">
         <v>78</v>
       </c>
@@ -16769,25 +16739,25 @@
         <v>78</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>105</v>
+        <v>506</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI127" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK127" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>106</v>
+        <v>504</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>78</v>
@@ -16798,14 +16768,14 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>466</v>
+        <v>511</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -16824,18 +16794,20 @@
         <v>78</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>109</v>
+        <v>512</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>110</v>
+        <v>513</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>111</v>
+        <v>514</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O128" s="2"/>
+        <v>515</v>
+      </c>
+      <c r="O128" t="s" s="2">
+        <v>516</v>
+      </c>
       <c r="P128" t="s" s="2">
         <v>78</v>
       </c>
@@ -16871,19 +16843,19 @@
         <v>78</v>
       </c>
       <c r="AB128" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC128" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD128" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE128" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>116</v>
+        <v>511</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -16892,19 +16864,19 @@
         <v>80</v>
       </c>
       <c r="AI128" t="s" s="2">
-        <v>78</v>
+        <v>200</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>117</v>
+        <v>517</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>78</v>
+        <v>518</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>106</v>
+        <v>519</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>78</v>
+        <v>520</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>78</v>
@@ -16912,10 +16884,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>504</v>
+        <v>521</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>468</v>
+        <v>521</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -16923,10 +16895,10 @@
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>78</v>
@@ -16935,22 +16907,22 @@
         <v>78</v>
       </c>
       <c r="J129" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>130</v>
+        <v>522</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>352</v>
+        <v>523</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>353</v>
+        <v>524</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>354</v>
+        <v>525</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>355</v>
+        <v>526</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>78</v>
@@ -16999,28 +16971,28 @@
         <v>78</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>357</v>
+        <v>521</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>78</v>
+        <v>200</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>100</v>
+        <v>527</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>358</v>
+        <v>528</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>359</v>
+        <v>529</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>78</v>
+        <v>530</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>78</v>
@@ -17028,10 +17000,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>505</v>
+        <v>531</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>470</v>
+        <v>531</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17054,18 +17026,18 @@
         <v>89</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>102</v>
+        <v>532</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>362</v>
+        <v>533</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="O130" s="2"/>
+        <v>534</v>
+      </c>
+      <c r="N130" s="2"/>
+      <c r="O130" t="s" s="2">
+        <v>535</v>
+      </c>
       <c r="P130" t="s" s="2">
         <v>78</v>
       </c>
@@ -17113,7 +17085,7 @@
         <v>78</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>365</v>
+        <v>531</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
@@ -17128,13 +17100,13 @@
         <v>100</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>366</v>
+        <v>427</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>367</v>
+        <v>536</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="AN130" t="s" s="2">
         <v>78</v>
@@ -17142,10 +17114,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>506</v>
+        <v>537</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>472</v>
+        <v>537</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17165,21 +17137,19 @@
         <v>78</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>168</v>
+        <v>102</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>473</v>
+        <v>103</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>371</v>
+        <v>104</v>
       </c>
       <c r="N131" s="2"/>
-      <c r="O131" t="s" s="2">
-        <v>372</v>
-      </c>
+      <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>78</v>
       </c>
@@ -17227,7 +17197,7 @@
         <v>78</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>373</v>
+        <v>105</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
@@ -17239,13 +17209,13 @@
         <v>78</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>374</v>
+        <v>78</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>375</v>
+        <v>106</v>
       </c>
       <c r="AM131" t="s" s="2">
         <v>78</v>
@@ -17256,21 +17226,21 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>507</v>
+        <v>538</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>475</v>
+        <v>538</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>78</v>
@@ -17279,21 +17249,21 @@
         <v>78</v>
       </c>
       <c r="J132" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>378</v>
+        <v>110</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N132" s="2"/>
-      <c r="O132" t="s" s="2">
-        <v>380</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="N132" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
         <v>78</v>
       </c>
@@ -17329,37 +17299,37 @@
         <v>78</v>
       </c>
       <c r="AB132" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC132" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD132" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE132" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>381</v>
+        <v>116</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI132" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>382</v>
+        <v>78</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>383</v>
+        <v>106</v>
       </c>
       <c r="AM132" t="s" s="2">
         <v>78</v>
@@ -17370,10 +17340,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>508</v>
+        <v>539</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>477</v>
+        <v>539</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17396,20 +17366,18 @@
         <v>89</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>386</v>
+        <v>102</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>387</v>
+        <v>540</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>388</v>
+        <v>541</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>390</v>
-      </c>
+        <v>542</v>
+      </c>
+      <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
         <v>78</v>
       </c>
@@ -17457,7 +17425,7 @@
         <v>78</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>391</v>
+        <v>543</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -17466,16 +17434,16 @@
         <v>88</v>
       </c>
       <c r="AI133" t="s" s="2">
-        <v>78</v>
+        <v>544</v>
       </c>
       <c r="AJ133" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>392</v>
+        <v>78</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>393</v>
+        <v>191</v>
       </c>
       <c r="AM133" t="s" s="2">
         <v>78</v>
@@ -17486,10 +17454,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>509</v>
+        <v>545</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>479</v>
+        <v>545</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17512,20 +17480,18 @@
         <v>89</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>396</v>
+        <v>546</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>397</v>
+        <v>547</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>548</v>
+      </c>
+      <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>78</v>
       </c>
@@ -17549,13 +17515,11 @@
         <v>78</v>
       </c>
       <c r="X134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y134" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="Y134" s="2"/>
       <c r="Z134" t="s" s="2">
-        <v>78</v>
+        <v>444</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>78</v>
@@ -17573,7 +17537,7 @@
         <v>78</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>400</v>
+        <v>549</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -17588,10 +17552,10 @@
         <v>100</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>401</v>
+        <v>78</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>402</v>
+        <v>191</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>78</v>
@@ -17602,10 +17566,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>510</v>
+        <v>550</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>510</v>
+        <v>550</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17628,20 +17592,18 @@
         <v>89</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>102</v>
+        <v>215</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>511</v>
+        <v>551</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>512</v>
+        <v>552</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>514</v>
-      </c>
+        <v>553</v>
+      </c>
+      <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
         <v>78</v>
       </c>
@@ -17689,7 +17651,7 @@
         <v>78</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>510</v>
+        <v>554</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -17698,19 +17660,19 @@
         <v>88</v>
       </c>
       <c r="AI135" t="s" s="2">
-        <v>221</v>
+        <v>78</v>
       </c>
       <c r="AJ135" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>515</v>
+        <v>78</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>516</v>
+        <v>555</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>517</v>
+        <v>78</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>78</v>
@@ -17718,10 +17680,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>518</v>
+        <v>556</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>518</v>
+        <v>556</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17732,7 +17694,7 @@
         <v>79</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H136" t="s" s="2">
         <v>78</v>
@@ -17741,23 +17703,21 @@
         <v>78</v>
       </c>
       <c r="J136" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K136" t="s" s="2">
         <v>102</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>519</v>
+        <v>557</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>520</v>
+        <v>558</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="O136" t="s" s="2">
-        <v>522</v>
-      </c>
+        <v>559</v>
+      </c>
+      <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
         <v>78</v>
       </c>
@@ -17805,13 +17765,13 @@
         <v>78</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>518</v>
+        <v>560</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH136" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI136" t="s" s="2">
         <v>78</v>
@@ -17823,7 +17783,7 @@
         <v>78</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>516</v>
+        <v>191</v>
       </c>
       <c r="AM136" t="s" s="2">
         <v>78</v>
@@ -17834,10 +17794,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>523</v>
+        <v>561</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>523</v>
+        <v>561</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17860,19 +17820,19 @@
         <v>78</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>524</v>
+        <v>562</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>525</v>
+        <v>563</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>526</v>
+        <v>564</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>527</v>
+        <v>565</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>528</v>
+        <v>566</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>78</v>
@@ -17921,7 +17881,7 @@
         <v>78</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>523</v>
+        <v>561</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
@@ -17930,19 +17890,19 @@
         <v>80</v>
       </c>
       <c r="AI137" t="s" s="2">
-        <v>200</v>
+        <v>78</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>529</v>
+        <v>100</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>530</v>
+        <v>78</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>531</v>
+        <v>567</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>532</v>
+        <v>78</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>78</v>
@@ -17950,10 +17910,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>533</v>
+        <v>568</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>533</v>
+        <v>568</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -17964,7 +17924,7 @@
         <v>79</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H138" t="s" s="2">
         <v>78</v>
@@ -17976,20 +17936,16 @@
         <v>78</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>534</v>
+        <v>102</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>535</v>
+        <v>103</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="O138" t="s" s="2">
-        <v>538</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N138" s="2"/>
+      <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
         <v>78</v>
       </c>
@@ -18037,28 +17993,28 @@
         <v>78</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>533</v>
+        <v>105</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI138" t="s" s="2">
-        <v>200</v>
+        <v>78</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>539</v>
+        <v>78</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>540</v>
+        <v>78</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>541</v>
+        <v>106</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>542</v>
+        <v>78</v>
       </c>
       <c r="AN138" t="s" s="2">
         <v>78</v>
@@ -18066,21 +18022,21 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>543</v>
+        <v>569</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>543</v>
+        <v>569</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H139" t="s" s="2">
         <v>78</v>
@@ -18089,21 +18045,21 @@
         <v>78</v>
       </c>
       <c r="J139" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>544</v>
+        <v>109</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>545</v>
+        <v>110</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="N139" s="2"/>
-      <c r="O139" t="s" s="2">
-        <v>547</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="N139" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
         <v>78</v>
       </c>
@@ -18151,28 +18107,28 @@
         <v>78</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>543</v>
+        <v>116</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH139" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI139" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>439</v>
+        <v>78</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>548</v>
+        <v>106</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="AN139" t="s" s="2">
         <v>78</v>
@@ -18180,42 +18136,46 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>549</v>
+        <v>570</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>549</v>
+        <v>570</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>78</v>
+        <v>571</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G140" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H140" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I140" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J140" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>103</v>
+        <v>572</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N140" s="2"/>
-      <c r="O140" s="2"/>
+        <v>573</v>
+      </c>
+      <c r="N140" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O140" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P140" t="s" s="2">
         <v>78</v>
       </c>
@@ -18263,25 +18223,25 @@
         <v>78</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>105</v>
+        <v>574</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI140" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AK140" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>106</v>
+        <v>191</v>
       </c>
       <c r="AM140" t="s" s="2">
         <v>78</v>
@@ -18292,21 +18252,21 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>550</v>
+        <v>575</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>550</v>
+        <v>575</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G141" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H141" t="s" s="2">
         <v>78</v>
@@ -18318,18 +18278,18 @@
         <v>78</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>109</v>
+        <v>238</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>110</v>
+        <v>576</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O141" s="2"/>
+        <v>577</v>
+      </c>
+      <c r="N141" s="2"/>
+      <c r="O141" t="s" s="2">
+        <v>578</v>
+      </c>
       <c r="P141" t="s" s="2">
         <v>78</v>
       </c>
@@ -18353,49 +18313,49 @@
         <v>78</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>78</v>
+        <v>579</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>78</v>
+        <v>580</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB141" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC141" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD141" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE141" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>116</v>
+        <v>575</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH141" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI141" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="AK141" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>106</v>
+        <v>581</v>
       </c>
       <c r="AM141" t="s" s="2">
         <v>78</v>
@@ -18406,10 +18366,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>551</v>
+        <v>582</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>551</v>
+        <v>582</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18429,21 +18389,21 @@
         <v>78</v>
       </c>
       <c r="J142" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>102</v>
+        <v>583</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>552</v>
+        <v>584</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="N142" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="O142" s="2"/>
+        <v>585</v>
+      </c>
+      <c r="N142" s="2"/>
+      <c r="O142" t="s" s="2">
+        <v>586</v>
+      </c>
       <c r="P142" t="s" s="2">
         <v>78</v>
       </c>
@@ -18491,7 +18451,7 @@
         <v>78</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>555</v>
+        <v>582</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
@@ -18500,16 +18460,16 @@
         <v>88</v>
       </c>
       <c r="AI142" t="s" s="2">
-        <v>556</v>
+        <v>78</v>
       </c>
       <c r="AJ142" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>78</v>
+        <v>587</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>191</v>
+        <v>588</v>
       </c>
       <c r="AM142" t="s" s="2">
         <v>78</v>
@@ -18520,10 +18480,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>557</v>
+        <v>589</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>557</v>
+        <v>589</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18534,7 +18494,7 @@
         <v>79</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H143" t="s" s="2">
         <v>78</v>
@@ -18543,21 +18503,21 @@
         <v>78</v>
       </c>
       <c r="J143" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>130</v>
+        <v>512</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>558</v>
+        <v>513</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="O143" s="2"/>
+        <v>514</v>
+      </c>
+      <c r="N143" s="2"/>
+      <c r="O143" t="s" s="2">
+        <v>590</v>
+      </c>
       <c r="P143" t="s" s="2">
         <v>78</v>
       </c>
@@ -18581,11 +18541,13 @@
         <v>78</v>
       </c>
       <c r="X143" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y143" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y143" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z143" t="s" s="2">
-        <v>456</v>
+        <v>78</v>
       </c>
       <c r="AA143" t="s" s="2">
         <v>78</v>
@@ -18603,28 +18565,28 @@
         <v>78</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>561</v>
+        <v>589</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH143" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI143" t="s" s="2">
-        <v>78</v>
+        <v>200</v>
       </c>
       <c r="AJ143" t="s" s="2">
-        <v>100</v>
+        <v>591</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>78</v>
+        <v>518</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>191</v>
+        <v>519</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>78</v>
+        <v>520</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>78</v>
@@ -18632,10 +18594,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>562</v>
+        <v>592</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>562</v>
+        <v>592</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18655,21 +18617,23 @@
         <v>78</v>
       </c>
       <c r="J144" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>215</v>
+        <v>522</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>563</v>
+        <v>523</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>564</v>
+        <v>524</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="O144" s="2"/>
+        <v>525</v>
+      </c>
+      <c r="O144" t="s" s="2">
+        <v>593</v>
+      </c>
       <c r="P144" t="s" s="2">
         <v>78</v>
       </c>
@@ -18717,7 +18681,7 @@
         <v>78</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>566</v>
+        <v>592</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>79</v>
@@ -18726,19 +18690,19 @@
         <v>88</v>
       </c>
       <c r="AI144" t="s" s="2">
-        <v>78</v>
+        <v>200</v>
       </c>
       <c r="AJ144" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK144" t="s" s="2">
-        <v>78</v>
+        <v>528</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>567</v>
+        <v>529</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>78</v>
+        <v>530</v>
       </c>
       <c r="AN144" t="s" s="2">
         <v>78</v>
@@ -18746,10 +18710,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>568</v>
+        <v>594</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>568</v>
+        <v>594</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -18760,7 +18724,7 @@
         <v>79</v>
       </c>
       <c r="G145" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H145" t="s" s="2">
         <v>78</v>
@@ -18769,21 +18733,21 @@
         <v>78</v>
       </c>
       <c r="J145" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>102</v>
+        <v>595</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>569</v>
+        <v>596</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="N145" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="O145" s="2"/>
+        <v>597</v>
+      </c>
+      <c r="N145" s="2"/>
+      <c r="O145" t="s" s="2">
+        <v>598</v>
+      </c>
       <c r="P145" t="s" s="2">
         <v>78</v>
       </c>
@@ -18831,13 +18795,13 @@
         <v>78</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>572</v>
+        <v>594</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH145" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI145" t="s" s="2">
         <v>78</v>
@@ -18849,1042 +18813,12 @@
         <v>78</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>191</v>
+        <v>106</v>
       </c>
       <c r="AM145" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="B146" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="C146" s="2"/>
-      <c r="D146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E146" s="2"/>
-      <c r="F146" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K146" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="L146" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="M146" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="N146" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="O146" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="P146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q146" s="2"/>
-      <c r="R146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF146" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="AG146" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ146" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL146" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="AM146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN146" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="B147" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="C147" s="2"/>
-      <c r="D147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E147" s="2"/>
-      <c r="F147" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G147" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K147" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L147" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="M147" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N147" s="2"/>
-      <c r="O147" s="2"/>
-      <c r="P147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q147" s="2"/>
-      <c r="R147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF147" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AG147" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH147" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL147" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AM147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN147" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="B148" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="C148" s="2"/>
-      <c r="D148" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="E148" s="2"/>
-      <c r="F148" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K148" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L148" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="M148" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N148" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O148" s="2"/>
-      <c r="P148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q148" s="2"/>
-      <c r="R148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF148" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AG148" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ148" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AK148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL148" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AM148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN148" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="B149" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="C149" s="2"/>
-      <c r="D149" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="E149" s="2"/>
-      <c r="F149" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I149" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="J149" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K149" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L149" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="M149" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="N149" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O149" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="P149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q149" s="2"/>
-      <c r="R149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF149" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="AG149" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ149" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AK149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL149" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AM149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN149" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="B150" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="C150" s="2"/>
-      <c r="D150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E150" s="2"/>
-      <c r="F150" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G150" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K150" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="L150" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="M150" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="N150" s="2"/>
-      <c r="O150" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="P150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q150" s="2"/>
-      <c r="R150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X150" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y150" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="Z150" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="AA150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF150" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="AG150" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH150" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ150" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL150" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="AM150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN150" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="B151" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="C151" s="2"/>
-      <c r="D151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E151" s="2"/>
-      <c r="F151" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G151" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K151" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="L151" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="M151" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="N151" s="2"/>
-      <c r="O151" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="P151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q151" s="2"/>
-      <c r="R151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF151" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="AG151" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH151" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ151" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK151" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="AL151" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="AM151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN151" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="B152" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="C152" s="2"/>
-      <c r="D152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E152" s="2"/>
-      <c r="F152" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K152" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="L152" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="M152" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="N152" s="2"/>
-      <c r="O152" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="P152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q152" s="2"/>
-      <c r="R152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF152" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="AG152" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI152" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AJ152" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="AK152" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="AL152" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="AM152" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="AN152" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="B153" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="C153" s="2"/>
-      <c r="D153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E153" s="2"/>
-      <c r="F153" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G153" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K153" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="L153" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="M153" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="O153" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="P153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q153" s="2"/>
-      <c r="R153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF153" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="AG153" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH153" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI153" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AJ153" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK153" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="AL153" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="AM153" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="AN153" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="B154" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="C154" s="2"/>
-      <c r="D154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E154" s="2"/>
-      <c r="F154" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G154" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K154" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="L154" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="M154" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="N154" s="2"/>
-      <c r="O154" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="P154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q154" s="2"/>
-      <c r="R154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF154" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="AG154" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH154" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ154" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL154" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AM154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN154" t="s" s="2">
         <v>78</v>
       </c>
     </row>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:05:50+00:00</t>
+    <t>2025-01-28T09:07:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:07:36+00:00</t>
+    <t>2025-02-04T08:51:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T08:51:44+00:00</t>
+    <t>2025-02-04T09:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5285" uniqueCount="608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5276" uniqueCount="606">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T09:30:35+00:00</t>
+    <t>2025-02-19T13:47:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -913,12 +913,6 @@
   </si>
   <si>
     <t>official</t>
-  </si>
-  <si>
-    <t>Identifies the purpose for this identifier, if known .</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
   </si>
   <si>
     <t>Organization.identifier:idNatSt.type</t>
@@ -932,12 +926,6 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
-  </si>
-  <si>
     <t>Organization.identifier:idNatSt.system</t>
   </si>
   <si>
@@ -1060,6 +1048,12 @@
   </si>
   <si>
     <t>Organization.identifier:finess.type</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
   </si>
   <si>
     <t>Organization.identifier:finess.type.id</t>
@@ -6209,11 +6203,9 @@
       <c r="X35" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="Y35" t="s" s="2">
-        <v>289</v>
-      </c>
+      <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>290</v>
+        <v>234</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>78</v>
@@ -6260,7 +6252,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>237</v>
@@ -6308,7 +6300,7 @@
         <v>78</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>78</v>
@@ -6325,11 +6317,9 @@
       <c r="X36" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="Y36" t="s" s="2">
-        <v>293</v>
-      </c>
+      <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>294</v>
+        <v>243</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>78</v>
@@ -6376,7 +6366,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>246</v>
@@ -6424,7 +6414,7 @@
         <v>78</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>251</v>
@@ -6492,7 +6482,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>256</v>
@@ -6521,7 +6511,7 @@
         <v>102</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="M38" t="s" s="2">
         <v>258</v>
@@ -6606,7 +6596,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>265</v>
@@ -6718,7 +6708,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>273</v>
@@ -6832,13 +6822,13 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>214</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>78</v>
@@ -6863,7 +6853,7 @@
         <v>215</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="M41" t="s" s="2">
         <v>217</v>
@@ -6948,7 +6938,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>226</v>
@@ -7060,7 +7050,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>227</v>
@@ -7174,7 +7164,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>228</v>
@@ -7239,11 +7229,9 @@
       <c r="X44" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="Y44" t="s" s="2">
-        <v>289</v>
-      </c>
+      <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>290</v>
+        <v>234</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>78</v>
@@ -7290,7 +7278,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>237</v>
@@ -7338,7 +7326,7 @@
         <v>78</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>78</v>
@@ -7355,11 +7343,9 @@
       <c r="X45" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="Y45" t="s" s="2">
-        <v>293</v>
-      </c>
+      <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>294</v>
+        <v>243</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>78</v>
@@ -7406,7 +7392,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>246</v>
@@ -7454,7 +7440,7 @@
         <v>78</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="T46" t="s" s="2">
         <v>251</v>
@@ -7522,7 +7508,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>256</v>
@@ -7636,7 +7622,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>265</v>
@@ -7748,7 +7734,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>273</v>
@@ -7862,13 +7848,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>214</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>78</v>
@@ -7893,7 +7879,7 @@
         <v>215</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="M50" t="s" s="2">
         <v>217</v>
@@ -7978,7 +7964,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>226</v>
@@ -8090,7 +8076,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>227</v>
@@ -8204,7 +8190,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>228</v>
@@ -8269,11 +8255,9 @@
       <c r="X53" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="Y53" t="s" s="2">
-        <v>289</v>
-      </c>
+      <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>290</v>
+        <v>234</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>78</v>
@@ -8320,7 +8304,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>237</v>
@@ -8368,7 +8352,7 @@
         <v>78</v>
       </c>
       <c r="S54" t="s" s="2">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="T54" t="s" s="2">
         <v>78</v>
@@ -8385,11 +8369,9 @@
       <c r="X54" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="Y54" t="s" s="2">
-        <v>293</v>
-      </c>
+      <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>294</v>
+        <v>243</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>78</v>
@@ -8436,7 +8418,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>246</v>
@@ -8484,7 +8466,7 @@
         <v>78</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>251</v>
@@ -8552,7 +8534,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>256</v>
@@ -8666,7 +8648,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>265</v>
@@ -8778,7 +8760,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>273</v>
@@ -8892,13 +8874,13 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>214</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>78</v>
@@ -8923,7 +8905,7 @@
         <v>215</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="M59" t="s" s="2">
         <v>217</v>
@@ -9008,7 +8990,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>226</v>
@@ -9120,7 +9102,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>227</v>
@@ -9234,7 +9216,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>228</v>
@@ -9299,11 +9281,9 @@
       <c r="X62" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="Y62" t="s" s="2">
-        <v>289</v>
-      </c>
+      <c r="Y62" s="2"/>
       <c r="Z62" t="s" s="2">
-        <v>290</v>
+        <v>234</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>78</v>
@@ -9350,7 +9330,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>237</v>
@@ -9416,10 +9396,10 @@
         <v>150</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>293</v>
+        <v>329</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>294</v>
+        <v>330</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>78</v>
@@ -9466,10 +9446,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9578,10 +9558,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9692,10 +9672,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9721,16 +9701,16 @@
         <v>146</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="N66" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="O66" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>78</v>
@@ -9779,7 +9759,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9794,10 +9774,10 @@
         <v>100</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>78</v>
@@ -9808,10 +9788,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9920,10 +9900,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10034,10 +10014,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10063,16 +10043,16 @@
         <v>130</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="N69" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>78</v>
@@ -10082,7 +10062,7 @@
         <v>78</v>
       </c>
       <c r="S69" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="T69" t="s" s="2">
         <v>78</v>
@@ -10121,7 +10101,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10136,10 +10116,10 @@
         <v>100</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>78</v>
@@ -10150,10 +10130,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10179,13 +10159,13 @@
         <v>102</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="N70" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10235,7 +10215,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10250,10 +10230,10 @@
         <v>100</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>78</v>
@@ -10264,10 +10244,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10293,14 +10273,14 @@
         <v>168</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -10349,7 +10329,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10364,10 +10344,10 @@
         <v>100</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>78</v>
@@ -10378,10 +10358,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10407,14 +10387,14 @@
         <v>102</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>78</v>
@@ -10463,7 +10443,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10478,10 +10458,10 @@
         <v>100</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>78</v>
@@ -10492,10 +10472,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10518,19 +10498,19 @@
         <v>89</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="O73" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>78</v>
@@ -10579,7 +10559,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10594,10 +10574,10 @@
         <v>100</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>78</v>
@@ -10608,10 +10588,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10637,16 +10617,16 @@
         <v>102</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="N74" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>78</v>
@@ -10695,7 +10675,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10710,10 +10690,10 @@
         <v>100</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>78</v>
@@ -10724,7 +10704,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>246</v>
@@ -10772,7 +10752,7 @@
         <v>78</v>
       </c>
       <c r="S75" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="T75" t="s" s="2">
         <v>251</v>
@@ -10840,7 +10820,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>256</v>
@@ -10954,7 +10934,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>265</v>
@@ -11066,7 +11046,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>273</v>
@@ -11180,13 +11160,13 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>214</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>78</v>
@@ -11211,7 +11191,7 @@
         <v>215</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="M79" t="s" s="2">
         <v>217</v>
@@ -11296,7 +11276,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>226</v>
@@ -11408,7 +11388,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>227</v>
@@ -11522,7 +11502,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>228</v>
@@ -11587,11 +11567,9 @@
       <c r="X82" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="Y82" t="s" s="2">
-        <v>289</v>
-      </c>
+      <c r="Y82" s="2"/>
       <c r="Z82" t="s" s="2">
-        <v>290</v>
+        <v>234</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>78</v>
@@ -11638,7 +11616,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>237</v>
@@ -11686,7 +11664,7 @@
         <v>78</v>
       </c>
       <c r="S83" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="T83" t="s" s="2">
         <v>78</v>
@@ -11703,11 +11681,9 @@
       <c r="X83" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="Y83" t="s" s="2">
-        <v>293</v>
-      </c>
+      <c r="Y83" s="2"/>
       <c r="Z83" t="s" s="2">
-        <v>294</v>
+        <v>243</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>78</v>
@@ -11754,7 +11730,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>246</v>
@@ -11802,7 +11778,7 @@
         <v>78</v>
       </c>
       <c r="S84" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="T84" t="s" s="2">
         <v>251</v>
@@ -11870,7 +11846,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>256</v>
@@ -11984,7 +11960,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>265</v>
@@ -12096,7 +12072,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>273</v>
@@ -12210,10 +12186,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12236,26 +12212,26 @@
         <v>89</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="N88" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="O88" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="N88" t="s" s="2">
+      <c r="P88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q88" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="O88" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="P88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q88" t="s" s="2">
-        <v>426</v>
-      </c>
       <c r="R88" t="s" s="2">
         <v>78</v>
       </c>
@@ -12299,7 +12275,7 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12314,24 +12290,24 @@
         <v>100</v>
       </c>
       <c r="AK88" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AM88" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="AL88" t="s" s="2">
+      <c r="AN88" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>430</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12357,16 +12333,16 @@
         <v>238</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="N89" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="M89" t="s" s="2">
+      <c r="O89" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>78</v>
@@ -12394,16 +12370,16 @@
         <v>158</v>
       </c>
       <c r="Y89" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB89" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="Z89" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="AA89" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB89" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="AC89" s="2"/>
       <c r="AD89" t="s" s="2">
@@ -12413,7 +12389,7 @@
         <v>115</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12428,27 +12404,27 @@
         <v>100</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D90" t="s" s="2">
         <v>78</v>
@@ -12473,16 +12449,16 @@
         <v>238</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="N90" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="O90" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>78</v>
@@ -12511,7 +12487,7 @@
       </c>
       <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>78</v>
@@ -12529,7 +12505,7 @@
         <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -12544,24 +12520,24 @@
         <v>100</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12670,10 +12646,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12784,10 +12760,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12813,16 +12789,16 @@
         <v>146</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="N93" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="O93" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>78</v>
@@ -12871,7 +12847,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -12886,10 +12862,10 @@
         <v>100</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>78</v>
@@ -12900,10 +12876,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13012,10 +12988,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13126,10 +13102,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13155,16 +13131,16 @@
         <v>130</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="N96" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="O96" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>78</v>
@@ -13213,7 +13189,7 @@
         <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13228,10 +13204,10 @@
         <v>100</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>78</v>
@@ -13242,10 +13218,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13271,13 +13247,13 @@
         <v>102</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="N97" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13327,7 +13303,7 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13342,10 +13318,10 @@
         <v>100</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>78</v>
@@ -13356,10 +13332,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13385,14 +13361,14 @@
         <v>168</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>78</v>
@@ -13441,7 +13417,7 @@
         <v>78</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -13456,10 +13432,10 @@
         <v>100</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>78</v>
@@ -13470,10 +13446,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13499,14 +13475,14 @@
         <v>102</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>78</v>
@@ -13555,7 +13531,7 @@
         <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -13570,10 +13546,10 @@
         <v>100</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>78</v>
@@ -13584,10 +13560,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13610,19 +13586,19 @@
         <v>89</v>
       </c>
       <c r="K100" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="L100" t="s" s="2">
+      <c r="N100" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="O100" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>78</v>
@@ -13671,7 +13647,7 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -13686,10 +13662,10 @@
         <v>100</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>78</v>
@@ -13700,10 +13676,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13729,16 +13705,16 @@
         <v>102</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="N101" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="O101" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>78</v>
@@ -13787,7 +13763,7 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -13802,10 +13778,10 @@
         <v>100</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>78</v>
@@ -13816,13 +13792,13 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D102" t="s" s="2">
         <v>78</v>
@@ -13847,16 +13823,16 @@
         <v>238</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="M102" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="O102" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>78</v>
@@ -13885,7 +13861,7 @@
       </c>
       <c r="Y102" s="2"/>
       <c r="Z102" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>78</v>
@@ -13903,7 +13879,7 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -13918,24 +13894,24 @@
         <v>100</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14044,10 +14020,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14158,10 +14134,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14187,16 +14163,16 @@
         <v>146</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="N105" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="M105" t="s" s="2">
+      <c r="O105" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>78</v>
@@ -14245,7 +14221,7 @@
         <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -14260,10 +14236,10 @@
         <v>100</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>78</v>
@@ -14274,10 +14250,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14386,10 +14362,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14500,10 +14476,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14529,16 +14505,16 @@
         <v>130</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="N108" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="M108" t="s" s="2">
+      <c r="O108" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>78</v>
@@ -14587,7 +14563,7 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -14602,10 +14578,10 @@
         <v>100</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>78</v>
@@ -14616,10 +14592,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14645,13 +14621,13 @@
         <v>102</v>
       </c>
       <c r="L109" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="N109" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -14701,7 +14677,7 @@
         <v>78</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -14716,10 +14692,10 @@
         <v>100</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>78</v>
@@ -14730,10 +14706,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14759,14 +14735,14 @@
         <v>168</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>78</v>
@@ -14815,7 +14791,7 @@
         <v>78</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -14830,10 +14806,10 @@
         <v>100</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>78</v>
@@ -14844,10 +14820,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14873,14 +14849,14 @@
         <v>102</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>78</v>
@@ -14929,7 +14905,7 @@
         <v>78</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -14944,10 +14920,10 @@
         <v>100</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>78</v>
@@ -14958,10 +14934,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14984,19 +14960,19 @@
         <v>89</v>
       </c>
       <c r="K112" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="L112" t="s" s="2">
+      <c r="N112" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="M112" t="s" s="2">
+      <c r="O112" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>78</v>
@@ -15045,7 +15021,7 @@
         <v>78</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -15060,10 +15036,10 @@
         <v>100</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>78</v>
@@ -15074,10 +15050,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15103,16 +15079,16 @@
         <v>102</v>
       </c>
       <c r="L113" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="N113" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M113" t="s" s="2">
+      <c r="O113" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>78</v>
@@ -15161,7 +15137,7 @@
         <v>78</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -15176,10 +15152,10 @@
         <v>100</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>78</v>
@@ -15190,13 +15166,13 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="D114" t="s" s="2">
         <v>78</v>
@@ -15221,16 +15197,16 @@
         <v>238</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="M114" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="O114" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>78</v>
@@ -15259,7 +15235,7 @@
       </c>
       <c r="Y114" s="2"/>
       <c r="Z114" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>78</v>
@@ -15277,7 +15253,7 @@
         <v>78</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
@@ -15292,24 +15268,24 @@
         <v>100</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15418,10 +15394,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15532,10 +15508,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15561,16 +15537,16 @@
         <v>146</v>
       </c>
       <c r="L117" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="N117" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="M117" t="s" s="2">
+      <c r="O117" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="O117" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>78</v>
@@ -15619,7 +15595,7 @@
         <v>78</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
@@ -15634,10 +15610,10 @@
         <v>100</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>78</v>
@@ -15648,10 +15624,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15760,10 +15736,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15874,10 +15850,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15903,16 +15879,16 @@
         <v>130</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="N120" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="M120" t="s" s="2">
+      <c r="O120" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>78</v>
@@ -15961,7 +15937,7 @@
         <v>78</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -15976,10 +15952,10 @@
         <v>100</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>78</v>
@@ -15990,10 +15966,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16019,13 +15995,13 @@
         <v>102</v>
       </c>
       <c r="L121" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="M121" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="N121" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -16075,7 +16051,7 @@
         <v>78</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -16090,10 +16066,10 @@
         <v>100</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>78</v>
@@ -16104,10 +16080,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16133,14 +16109,14 @@
         <v>168</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>78</v>
@@ -16189,7 +16165,7 @@
         <v>78</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -16204,10 +16180,10 @@
         <v>100</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>78</v>
@@ -16218,10 +16194,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16247,14 +16223,14 @@
         <v>102</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>78</v>
@@ -16303,7 +16279,7 @@
         <v>78</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -16318,10 +16294,10 @@
         <v>100</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>78</v>
@@ -16332,10 +16308,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16358,19 +16334,19 @@
         <v>89</v>
       </c>
       <c r="K124" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="L124" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="L124" t="s" s="2">
+      <c r="N124" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="M124" t="s" s="2">
+      <c r="O124" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="O124" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>78</v>
@@ -16419,7 +16395,7 @@
         <v>78</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -16434,10 +16410,10 @@
         <v>100</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>78</v>
@@ -16448,10 +16424,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16477,16 +16453,16 @@
         <v>102</v>
       </c>
       <c r="L125" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M125" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="N125" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M125" t="s" s="2">
+      <c r="O125" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>78</v>
@@ -16535,7 +16511,7 @@
         <v>78</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -16550,10 +16526,10 @@
         <v>100</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>78</v>
@@ -16564,10 +16540,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16593,16 +16569,16 @@
         <v>102</v>
       </c>
       <c r="L126" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M126" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="N126" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="M126" t="s" s="2">
+      <c r="O126" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="O126" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>78</v>
@@ -16651,7 +16627,7 @@
         <v>78</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -16666,13 +16642,13 @@
         <v>100</v>
       </c>
       <c r="AK126" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AL126" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AM126" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="AL126" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="AM126" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>78</v>
@@ -16680,10 +16656,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16709,16 +16685,16 @@
         <v>102</v>
       </c>
       <c r="L127" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M127" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="N127" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="M127" t="s" s="2">
+      <c r="O127" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>78</v>
@@ -16767,7 +16743,7 @@
         <v>78</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -16785,7 +16761,7 @@
         <v>78</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>78</v>
@@ -16796,10 +16772,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -16822,19 +16798,19 @@
         <v>78</v>
       </c>
       <c r="K128" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="L128" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="M128" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="L128" t="s" s="2">
+      <c r="N128" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="M128" t="s" s="2">
+      <c r="O128" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>78</v>
@@ -16883,7 +16859,7 @@
         <v>78</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -16892,19 +16868,19 @@
         <v>80</v>
       </c>
       <c r="AI128" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AJ128" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="AK128" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="AJ128" t="s" s="2">
+      <c r="AL128" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="AK128" t="s" s="2">
+      <c r="AM128" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="AL128" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="AM128" t="s" s="2">
-        <v>521</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>78</v>
@@ -16912,10 +16888,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -16938,19 +16914,19 @@
         <v>78</v>
       </c>
       <c r="K129" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="L129" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="M129" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="L129" t="s" s="2">
+      <c r="N129" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="M129" t="s" s="2">
+      <c r="O129" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="O129" t="s" s="2">
-        <v>527</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>78</v>
@@ -16999,7 +16975,7 @@
         <v>78</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
@@ -17008,19 +16984,19 @@
         <v>80</v>
       </c>
       <c r="AI129" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AJ129" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="AK129" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="AJ129" t="s" s="2">
+      <c r="AL129" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="AK129" t="s" s="2">
+      <c r="AM129" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="AL129" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="AM129" t="s" s="2">
-        <v>532</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>78</v>
@@ -17028,10 +17004,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17054,17 +17030,17 @@
         <v>89</v>
       </c>
       <c r="K130" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="L130" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="M130" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="L130" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>78</v>
@@ -17113,7 +17089,7 @@
         <v>78</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
@@ -17128,10 +17104,10 @@
         <v>100</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="AM130" t="s" s="2">
         <v>106</v>
@@ -17142,10 +17118,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17254,10 +17230,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17368,10 +17344,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17397,13 +17373,13 @@
         <v>102</v>
       </c>
       <c r="L133" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="M133" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="N133" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -17453,7 +17429,7 @@
         <v>78</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -17462,7 +17438,7 @@
         <v>88</v>
       </c>
       <c r="AI133" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="AJ133" t="s" s="2">
         <v>100</v>
@@ -17482,10 +17458,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17511,13 +17487,13 @@
         <v>130</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="M134" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="N134" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>550</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -17547,7 +17523,7 @@
       </c>
       <c r="Y134" s="2"/>
       <c r="Z134" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>78</v>
@@ -17565,7 +17541,7 @@
         <v>78</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -17594,10 +17570,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17623,13 +17599,13 @@
         <v>215</v>
       </c>
       <c r="L135" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M135" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="N135" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="M135" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -17679,7 +17655,7 @@
         <v>78</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -17697,7 +17673,7 @@
         <v>78</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>78</v>
@@ -17708,10 +17684,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17737,13 +17713,13 @@
         <v>102</v>
       </c>
       <c r="L136" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="M136" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="N136" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="M136" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -17793,7 +17769,7 @@
         <v>78</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -17822,10 +17798,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17848,19 +17824,19 @@
         <v>78</v>
       </c>
       <c r="K137" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="L137" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="M137" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="L137" t="s" s="2">
+      <c r="N137" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="M137" t="s" s="2">
+      <c r="O137" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="N137" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="O137" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>78</v>
@@ -17909,7 +17885,7 @@
         <v>78</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
@@ -17927,7 +17903,7 @@
         <v>78</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="AM137" t="s" s="2">
         <v>78</v>
@@ -17938,10 +17914,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18050,10 +18026,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18164,14 +18140,14 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
@@ -18193,10 +18169,10 @@
         <v>109</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="N140" t="s" s="2">
         <v>112</v>
@@ -18251,7 +18227,7 @@
         <v>78</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
@@ -18280,10 +18256,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18309,14 +18285,14 @@
         <v>238</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>78</v>
@@ -18344,10 +18320,10 @@
         <v>150</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>78</v>
@@ -18365,7 +18341,7 @@
         <v>78</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
@@ -18383,7 +18359,7 @@
         <v>78</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="AM141" t="s" s="2">
         <v>78</v>
@@ -18394,10 +18370,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18420,17 +18396,17 @@
         <v>78</v>
       </c>
       <c r="K142" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="L142" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="M142" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="L142" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="M142" t="s" s="2">
-        <v>587</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>78</v>
@@ -18479,7 +18455,7 @@
         <v>78</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
@@ -18494,10 +18470,10 @@
         <v>100</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="AM142" t="s" s="2">
         <v>78</v>
@@ -18508,10 +18484,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18534,17 +18510,17 @@
         <v>78</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>78</v>
@@ -18593,7 +18569,7 @@
         <v>78</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -18608,10 +18584,10 @@
         <v>100</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="AM143" t="s" s="2">
         <v>78</v>
@@ -18622,10 +18598,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18648,17 +18624,17 @@
         <v>78</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" t="s" s="2">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>78</v>
@@ -18707,7 +18683,7 @@
         <v>78</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>79</v>
@@ -18722,10 +18698,10 @@
         <v>100</v>
       </c>
       <c r="AK144" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="AM144" t="s" s="2">
         <v>78</v>
@@ -18736,10 +18712,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -18762,17 +18738,17 @@
         <v>78</v>
       </c>
       <c r="K145" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="L145" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="M145" t="s" s="2">
         <v>604</v>
-      </c>
-      <c r="L145" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="M145" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" t="s" s="2">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>78</v>
@@ -18821,7 +18797,7 @@
         <v>78</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>79</v>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:47:59+00:00</t>
+    <t>2025-02-19T13:52:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5276" uniqueCount="606">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5276" uniqueCount="607">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:52:01+00:00</t>
+    <t>2025-02-19T13:53:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -900,7 +900,7 @@
     <t>idNatSt</t>
   </si>
   <si>
-    <t>Identifiant idNat_Struct délivré par une autorité d'enregistrement tel que défini dans l'Annexe Transverse Source des données métier pour les professionnels et les structures.</t>
+    <t>Identifiant national de structure unique délivré par une autorité d'enregistrement tel que défini dans l'Annexe Transverse Source des données métier pour les professionnels et les structures.</t>
   </si>
   <si>
     <t>Organization.identifier:idNatSt.id</t>
@@ -935,7 +935,10 @@
     <t>Organization.identifier:idNatSt.value</t>
   </si>
   <si>
-    <t>Identification nationale de la structure préfixé : 0 + ADELI rang, 1 + Numéro FINESS Etablissement, 2 + Numéro SIREN, 3 + Numéro SIRET, 4 + RPPS rang ou identifiant technique de la structure.</t>
+    <t>Identifiant national de la structure. Cet identifiant ne doit pas être construit ni interprété, la donnée peut être trouvée dans l'annuaire santé.</t>
+  </si>
+  <si>
+    <t>L'idNatStruct est construit, selon le cas, de cette manière : 0 + ADELI rang, 1 + Numéro FINESS Etablissement, 2 + Numéro SIREN, 3 + Numéro SIRET, 4 + RPPS rang ou identifiant technique de la structure</t>
   </si>
   <si>
     <t>Organization.identifier:idNatSt.period</t>
@@ -6514,7 +6517,7 @@
         <v>294</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>258</v>
+        <v>295</v>
       </c>
       <c r="N38" t="s" s="2">
         <v>259</v>
@@ -6596,7 +6599,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>265</v>
@@ -6708,7 +6711,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>273</v>
@@ -6822,13 +6825,13 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>214</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>78</v>
@@ -6853,7 +6856,7 @@
         <v>215</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M41" t="s" s="2">
         <v>217</v>
@@ -6938,7 +6941,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>226</v>
@@ -7050,7 +7053,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>227</v>
@@ -7164,7 +7167,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>228</v>
@@ -7278,7 +7281,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>237</v>
@@ -7326,7 +7329,7 @@
         <v>78</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>78</v>
@@ -7392,7 +7395,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>246</v>
@@ -7440,7 +7443,7 @@
         <v>78</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="T46" t="s" s="2">
         <v>251</v>
@@ -7508,7 +7511,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>256</v>
@@ -7622,7 +7625,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>265</v>
@@ -7734,7 +7737,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>273</v>
@@ -7848,13 +7851,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>214</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>78</v>
@@ -7879,7 +7882,7 @@
         <v>215</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M50" t="s" s="2">
         <v>217</v>
@@ -7964,7 +7967,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>226</v>
@@ -8076,7 +8079,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>227</v>
@@ -8190,7 +8193,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>228</v>
@@ -8304,7 +8307,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>237</v>
@@ -8352,7 +8355,7 @@
         <v>78</v>
       </c>
       <c r="S54" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="T54" t="s" s="2">
         <v>78</v>
@@ -8418,7 +8421,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>246</v>
@@ -8466,7 +8469,7 @@
         <v>78</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>251</v>
@@ -8534,7 +8537,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>256</v>
@@ -8648,7 +8651,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>265</v>
@@ -8760,7 +8763,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>273</v>
@@ -8874,13 +8877,13 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>214</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>78</v>
@@ -8905,7 +8908,7 @@
         <v>215</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M59" t="s" s="2">
         <v>217</v>
@@ -8990,7 +8993,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>226</v>
@@ -9102,7 +9105,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>227</v>
@@ -9216,7 +9219,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>228</v>
@@ -9330,7 +9333,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>237</v>
@@ -9396,10 +9399,10 @@
         <v>150</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>78</v>
@@ -9446,10 +9449,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9558,10 +9561,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9672,10 +9675,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9701,16 +9704,16 @@
         <v>146</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>78</v>
@@ -9759,7 +9762,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9774,10 +9777,10 @@
         <v>100</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>78</v>
@@ -9788,10 +9791,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9900,10 +9903,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10014,10 +10017,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10043,16 +10046,16 @@
         <v>130</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>78</v>
@@ -10062,7 +10065,7 @@
         <v>78</v>
       </c>
       <c r="S69" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="T69" t="s" s="2">
         <v>78</v>
@@ -10101,7 +10104,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10116,10 +10119,10 @@
         <v>100</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>78</v>
@@ -10130,10 +10133,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10159,13 +10162,13 @@
         <v>102</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10215,7 +10218,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10230,10 +10233,10 @@
         <v>100</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>78</v>
@@ -10244,10 +10247,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10273,14 +10276,14 @@
         <v>168</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -10329,7 +10332,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10344,10 +10347,10 @@
         <v>100</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>78</v>
@@ -10358,10 +10361,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10387,14 +10390,14 @@
         <v>102</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>78</v>
@@ -10443,7 +10446,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10458,10 +10461,10 @@
         <v>100</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>78</v>
@@ -10472,10 +10475,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10498,19 +10501,19 @@
         <v>89</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>78</v>
@@ -10559,7 +10562,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10574,10 +10577,10 @@
         <v>100</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>78</v>
@@ -10588,10 +10591,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10617,16 +10620,16 @@
         <v>102</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>78</v>
@@ -10675,7 +10678,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10690,10 +10693,10 @@
         <v>100</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>78</v>
@@ -10704,7 +10707,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>246</v>
@@ -10752,7 +10755,7 @@
         <v>78</v>
       </c>
       <c r="S75" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="T75" t="s" s="2">
         <v>251</v>
@@ -10820,7 +10823,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>256</v>
@@ -10934,7 +10937,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>265</v>
@@ -11046,7 +11049,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>273</v>
@@ -11160,13 +11163,13 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>214</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>78</v>
@@ -11191,7 +11194,7 @@
         <v>215</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M79" t="s" s="2">
         <v>217</v>
@@ -11276,7 +11279,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>226</v>
@@ -11388,7 +11391,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>227</v>
@@ -11502,7 +11505,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>228</v>
@@ -11616,7 +11619,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>237</v>
@@ -11664,7 +11667,7 @@
         <v>78</v>
       </c>
       <c r="S83" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="T83" t="s" s="2">
         <v>78</v>
@@ -11730,7 +11733,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>246</v>
@@ -11778,7 +11781,7 @@
         <v>78</v>
       </c>
       <c r="S84" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="T84" t="s" s="2">
         <v>251</v>
@@ -11846,7 +11849,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>256</v>
@@ -11960,7 +11963,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>265</v>
@@ -12072,7 +12075,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>273</v>
@@ -12186,10 +12189,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12212,70 +12215,70 @@
         <v>89</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="P88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q88" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="R88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF88" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="P88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q88" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="R88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12290,24 +12293,24 @@
         <v>100</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12333,16 +12336,16 @@
         <v>238</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>78</v>
@@ -12370,16 +12373,16 @@
         <v>158</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AC89" s="2"/>
       <c r="AD89" t="s" s="2">
@@ -12389,7 +12392,7 @@
         <v>115</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12404,27 +12407,27 @@
         <v>100</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D90" t="s" s="2">
         <v>78</v>
@@ -12449,16 +12452,16 @@
         <v>238</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>78</v>
@@ -12487,7 +12490,7 @@
       </c>
       <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>78</v>
@@ -12505,7 +12508,7 @@
         <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -12520,24 +12523,24 @@
         <v>100</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12646,10 +12649,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12760,10 +12763,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12789,16 +12792,16 @@
         <v>146</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>78</v>
@@ -12847,7 +12850,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -12862,10 +12865,10 @@
         <v>100</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>78</v>
@@ -12876,10 +12879,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12988,10 +12991,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13102,10 +13105,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13131,16 +13134,16 @@
         <v>130</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>78</v>
@@ -13189,7 +13192,7 @@
         <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13204,10 +13207,10 @@
         <v>100</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>78</v>
@@ -13218,10 +13221,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13247,13 +13250,13 @@
         <v>102</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13303,7 +13306,7 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13318,10 +13321,10 @@
         <v>100</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>78</v>
@@ -13332,10 +13335,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13361,14 +13364,14 @@
         <v>168</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>78</v>
@@ -13417,7 +13420,7 @@
         <v>78</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -13432,10 +13435,10 @@
         <v>100</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>78</v>
@@ -13446,10 +13449,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13475,14 +13478,14 @@
         <v>102</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>78</v>
@@ -13531,7 +13534,7 @@
         <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -13546,10 +13549,10 @@
         <v>100</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>78</v>
@@ -13560,10 +13563,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13586,19 +13589,19 @@
         <v>89</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>78</v>
@@ -13647,7 +13650,7 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -13662,10 +13665,10 @@
         <v>100</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>78</v>
@@ -13676,10 +13679,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13705,16 +13708,16 @@
         <v>102</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>78</v>
@@ -13763,7 +13766,7 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -13778,10 +13781,10 @@
         <v>100</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>78</v>
@@ -13792,13 +13795,13 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D102" t="s" s="2">
         <v>78</v>
@@ -13823,16 +13826,16 @@
         <v>238</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>78</v>
@@ -13861,7 +13864,7 @@
       </c>
       <c r="Y102" s="2"/>
       <c r="Z102" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>78</v>
@@ -13879,7 +13882,7 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -13894,24 +13897,24 @@
         <v>100</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14020,10 +14023,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14134,10 +14137,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14163,16 +14166,16 @@
         <v>146</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>78</v>
@@ -14221,7 +14224,7 @@
         <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -14236,10 +14239,10 @@
         <v>100</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>78</v>
@@ -14250,10 +14253,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14362,10 +14365,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14476,10 +14479,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14505,16 +14508,16 @@
         <v>130</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>78</v>
@@ -14563,7 +14566,7 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -14578,10 +14581,10 @@
         <v>100</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>78</v>
@@ -14592,10 +14595,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14621,13 +14624,13 @@
         <v>102</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -14677,7 +14680,7 @@
         <v>78</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -14692,10 +14695,10 @@
         <v>100</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>78</v>
@@ -14706,10 +14709,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14735,14 +14738,14 @@
         <v>168</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>78</v>
@@ -14791,7 +14794,7 @@
         <v>78</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -14806,10 +14809,10 @@
         <v>100</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>78</v>
@@ -14820,10 +14823,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14849,14 +14852,14 @@
         <v>102</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>78</v>
@@ -14905,7 +14908,7 @@
         <v>78</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -14920,10 +14923,10 @@
         <v>100</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>78</v>
@@ -14934,10 +14937,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14960,19 +14963,19 @@
         <v>89</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>78</v>
@@ -15021,7 +15024,7 @@
         <v>78</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -15036,10 +15039,10 @@
         <v>100</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>78</v>
@@ -15050,10 +15053,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15079,16 +15082,16 @@
         <v>102</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>78</v>
@@ -15137,7 +15140,7 @@
         <v>78</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -15152,10 +15155,10 @@
         <v>100</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>78</v>
@@ -15166,13 +15169,13 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D114" t="s" s="2">
         <v>78</v>
@@ -15197,16 +15200,16 @@
         <v>238</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>78</v>
@@ -15235,7 +15238,7 @@
       </c>
       <c r="Y114" s="2"/>
       <c r="Z114" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>78</v>
@@ -15253,7 +15256,7 @@
         <v>78</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
@@ -15268,24 +15271,24 @@
         <v>100</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15394,10 +15397,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15508,10 +15511,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15537,16 +15540,16 @@
         <v>146</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>78</v>
@@ -15595,7 +15598,7 @@
         <v>78</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
@@ -15610,10 +15613,10 @@
         <v>100</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>78</v>
@@ -15624,10 +15627,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15736,10 +15739,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15850,10 +15853,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15879,16 +15882,16 @@
         <v>130</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>78</v>
@@ -15937,7 +15940,7 @@
         <v>78</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -15952,10 +15955,10 @@
         <v>100</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>78</v>
@@ -15966,10 +15969,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15995,13 +15998,13 @@
         <v>102</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -16051,7 +16054,7 @@
         <v>78</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -16066,10 +16069,10 @@
         <v>100</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>78</v>
@@ -16080,10 +16083,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16109,14 +16112,14 @@
         <v>168</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>78</v>
@@ -16165,7 +16168,7 @@
         <v>78</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -16180,10 +16183,10 @@
         <v>100</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>78</v>
@@ -16194,10 +16197,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16223,14 +16226,14 @@
         <v>102</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>78</v>
@@ -16279,7 +16282,7 @@
         <v>78</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -16294,10 +16297,10 @@
         <v>100</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>78</v>
@@ -16308,10 +16311,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16334,19 +16337,19 @@
         <v>89</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>78</v>
@@ -16395,7 +16398,7 @@
         <v>78</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -16410,10 +16413,10 @@
         <v>100</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>78</v>
@@ -16424,10 +16427,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16453,16 +16456,16 @@
         <v>102</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>78</v>
@@ -16511,7 +16514,7 @@
         <v>78</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -16526,10 +16529,10 @@
         <v>100</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>78</v>
@@ -16540,10 +16543,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16569,16 +16572,16 @@
         <v>102</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>78</v>
@@ -16627,7 +16630,7 @@
         <v>78</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -16642,13 +16645,13 @@
         <v>100</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>78</v>
@@ -16656,10 +16659,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16685,16 +16688,16 @@
         <v>102</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>78</v>
@@ -16743,7 +16746,7 @@
         <v>78</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -16761,7 +16764,7 @@
         <v>78</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>78</v>
@@ -16772,10 +16775,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -16798,19 +16801,19 @@
         <v>78</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>78</v>
@@ -16859,7 +16862,7 @@
         <v>78</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -16868,19 +16871,19 @@
         <v>80</v>
       </c>
       <c r="AI128" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>78</v>
@@ -16888,10 +16891,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -16914,19 +16917,19 @@
         <v>78</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>78</v>
@@ -16975,7 +16978,7 @@
         <v>78</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
@@ -16984,19 +16987,19 @@
         <v>80</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>78</v>
@@ -17004,10 +17007,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17030,17 +17033,17 @@
         <v>89</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>78</v>
@@ -17089,7 +17092,7 @@
         <v>78</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
@@ -17104,10 +17107,10 @@
         <v>100</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AM130" t="s" s="2">
         <v>106</v>
@@ -17118,10 +17121,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17230,10 +17233,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17344,10 +17347,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17373,13 +17376,13 @@
         <v>102</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -17429,7 +17432,7 @@
         <v>78</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -17438,7 +17441,7 @@
         <v>88</v>
       </c>
       <c r="AI133" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AJ133" t="s" s="2">
         <v>100</v>
@@ -17458,10 +17461,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17487,13 +17490,13 @@
         <v>130</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -17523,7 +17526,7 @@
       </c>
       <c r="Y134" s="2"/>
       <c r="Z134" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>78</v>
@@ -17541,7 +17544,7 @@
         <v>78</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -17570,10 +17573,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17599,13 +17602,13 @@
         <v>215</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -17655,7 +17658,7 @@
         <v>78</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -17673,7 +17676,7 @@
         <v>78</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>78</v>
@@ -17684,10 +17687,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17713,13 +17716,13 @@
         <v>102</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -17769,7 +17772,7 @@
         <v>78</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -17798,10 +17801,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17824,19 +17827,19 @@
         <v>78</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>78</v>
@@ -17885,7 +17888,7 @@
         <v>78</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
@@ -17903,7 +17906,7 @@
         <v>78</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AM137" t="s" s="2">
         <v>78</v>
@@ -17914,10 +17917,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18026,10 +18029,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18140,14 +18143,14 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
@@ -18169,10 +18172,10 @@
         <v>109</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N140" t="s" s="2">
         <v>112</v>
@@ -18227,7 +18230,7 @@
         <v>78</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
@@ -18256,10 +18259,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18285,14 +18288,14 @@
         <v>238</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>78</v>
@@ -18320,10 +18323,10 @@
         <v>150</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>78</v>
@@ -18341,7 +18344,7 @@
         <v>78</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
@@ -18359,7 +18362,7 @@
         <v>78</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AM141" t="s" s="2">
         <v>78</v>
@@ -18370,10 +18373,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18396,17 +18399,17 @@
         <v>78</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>78</v>
@@ -18455,7 +18458,7 @@
         <v>78</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
@@ -18470,10 +18473,10 @@
         <v>100</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AM142" t="s" s="2">
         <v>78</v>
@@ -18484,10 +18487,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18510,17 +18513,17 @@
         <v>78</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>78</v>
@@ -18569,7 +18572,7 @@
         <v>78</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -18584,10 +18587,10 @@
         <v>100</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AM143" t="s" s="2">
         <v>78</v>
@@ -18598,10 +18601,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18624,17 +18627,17 @@
         <v>78</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>78</v>
@@ -18683,7 +18686,7 @@
         <v>78</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>79</v>
@@ -18698,10 +18701,10 @@
         <v>100</v>
       </c>
       <c r="AK144" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AM144" t="s" s="2">
         <v>78</v>
@@ -18712,10 +18715,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -18738,17 +18741,17 @@
         <v>78</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>78</v>
@@ -18797,7 +18800,7 @@
         <v>78</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>79</v>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5276" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5276" uniqueCount="609">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:53:58+00:00</t>
+    <t>2025-02-19T13:58:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -638,6 +638,11 @@
     <t>FR Core Organization Short Name Extension</t>
   </si>
   <si>
+    <t>Libellé court de l'organisation
++The Organization short name</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
@@ -653,6 +658,10 @@
   </si>
   <si>
     <t>FR Core Organization Description Extension</t>
+  </si>
+  <si>
+    <t>Description textuelle d'une organisation
+Organization description</t>
   </si>
   <si>
     <t>Organization.extension:usePeriod</t>
@@ -4351,7 +4360,7 @@
         <v>199</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4411,7 +4420,7 @@
         <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>117</v>
@@ -4431,13 +4440,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>78</v>
@@ -4459,13 +4468,13 @@
         <v>78</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4525,7 +4534,7 @@
         <v>80</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>117</v>
@@ -4545,13 +4554,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>78</v>
@@ -4573,13 +4582,13 @@
         <v>78</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>193</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4659,10 +4668,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4688,16 +4697,16 @@
         <v>109</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>78</v>
@@ -4746,7 +4755,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4775,10 +4784,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4801,17 +4810,17 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>78</v>
@@ -4848,10 +4857,10 @@
         <v>78</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>78</v>
@@ -4860,7 +4869,7 @@
         <v>115</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4869,30 +4878,30 @@
         <v>80</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5001,10 +5010,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5115,10 +5124,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5144,16 +5153,16 @@
         <v>168</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>78</v>
@@ -5178,11 +5187,11 @@
         <v>78</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>78</v>
@@ -5200,7 +5209,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5218,7 +5227,7 @@
         <v>191</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>78</v>
@@ -5229,10 +5238,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5255,19 +5264,19 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -5296,7 +5305,7 @@
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>78</v>
@@ -5314,7 +5323,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5329,10 +5338,10 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>78</v>
@@ -5343,10 +5352,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5372,16 +5381,16 @@
         <v>130</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>78</v>
@@ -5394,7 +5403,7 @@
         <v>78</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>78</v>
@@ -5430,7 +5439,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5445,13 +5454,13 @@
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>78</v>
@@ -5459,10 +5468,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5488,13 +5497,13 @@
         <v>102</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5508,7 +5517,7 @@
         <v>78</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="U29" t="s" s="2">
         <v>78</v>
@@ -5544,7 +5553,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5559,13 +5568,13 @@
         <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>78</v>
@@ -5573,10 +5582,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5599,13 +5608,13 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5656,7 +5665,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5671,13 +5680,13 @@
         <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>78</v>
@@ -5685,10 +5694,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5711,16 +5720,16 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5770,7 +5779,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5785,13 +5794,13 @@
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>78</v>
@@ -5799,13 +5808,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>78</v>
@@ -5827,17 +5836,17 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>78</v>
@@ -5886,7 +5895,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5895,30 +5904,30 @@
         <v>80</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6027,10 +6036,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6141,10 +6150,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6170,16 +6179,16 @@
         <v>168</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>78</v>
@@ -6189,7 +6198,7 @@
         <v>78</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>78</v>
@@ -6204,11 +6213,11 @@
         <v>78</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>78</v>
@@ -6226,7 +6235,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6244,7 +6253,7 @@
         <v>191</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>78</v>
@@ -6255,10 +6264,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6281,19 +6290,19 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -6303,7 +6312,7 @@
         <v>78</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>78</v>
@@ -6322,7 +6331,7 @@
       </c>
       <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>78</v>
@@ -6340,7 +6349,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6355,10 +6364,10 @@
         <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>78</v>
@@ -6369,10 +6378,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6398,16 +6407,16 @@
         <v>130</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -6417,10 +6426,10 @@
         <v>78</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>78</v>
@@ -6456,7 +6465,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6471,13 +6480,13 @@
         <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>78</v>
@@ -6485,10 +6494,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6514,13 +6523,13 @@
         <v>102</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6534,7 +6543,7 @@
         <v>78</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="U38" t="s" s="2">
         <v>78</v>
@@ -6570,7 +6579,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6585,13 +6594,13 @@
         <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>78</v>
@@ -6599,10 +6608,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6625,13 +6634,13 @@
         <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6682,7 +6691,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6697,13 +6706,13 @@
         <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>78</v>
@@ -6711,10 +6720,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6737,16 +6746,16 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6796,7 +6805,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6811,13 +6820,13 @@
         <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>78</v>
@@ -6825,13 +6834,13 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>78</v>
@@ -6853,17 +6862,17 @@
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>78</v>
@@ -6912,7 +6921,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6921,30 +6930,30 @@
         <v>80</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7053,10 +7062,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7167,10 +7176,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7196,16 +7205,16 @@
         <v>168</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>78</v>
@@ -7230,11 +7239,11 @@
         <v>78</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>78</v>
@@ -7252,7 +7261,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7270,7 +7279,7 @@
         <v>191</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>78</v>
@@ -7281,10 +7290,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7307,19 +7316,19 @@
         <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>78</v>
@@ -7329,7 +7338,7 @@
         <v>78</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>78</v>
@@ -7348,7 +7357,7 @@
       </c>
       <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>78</v>
@@ -7366,7 +7375,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7381,10 +7390,10 @@
         <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
@@ -7395,10 +7404,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7424,16 +7433,16 @@
         <v>130</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>78</v>
@@ -7443,10 +7452,10 @@
         <v>78</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>78</v>
@@ -7482,7 +7491,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7497,13 +7506,13 @@
         <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>78</v>
@@ -7511,10 +7520,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7540,13 +7549,13 @@
         <v>102</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7560,7 +7569,7 @@
         <v>78</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>78</v>
@@ -7596,7 +7605,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7611,13 +7620,13 @@
         <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>78</v>
@@ -7625,10 +7634,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7651,13 +7660,13 @@
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7708,7 +7717,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7723,13 +7732,13 @@
         <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>78</v>
@@ -7737,10 +7746,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7763,16 +7772,16 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7822,7 +7831,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7837,13 +7846,13 @@
         <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>78</v>
@@ -7851,13 +7860,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>78</v>
@@ -7879,17 +7888,17 @@
         <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -7938,7 +7947,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7947,30 +7956,30 @@
         <v>80</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8079,10 +8088,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8193,10 +8202,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8222,16 +8231,16 @@
         <v>168</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -8256,11 +8265,11 @@
         <v>78</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>78</v>
@@ -8278,7 +8287,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8296,7 +8305,7 @@
         <v>191</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>78</v>
@@ -8307,10 +8316,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8333,19 +8342,19 @@
         <v>89</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>78</v>
@@ -8355,7 +8364,7 @@
         <v>78</v>
       </c>
       <c r="S54" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="T54" t="s" s="2">
         <v>78</v>
@@ -8374,7 +8383,7 @@
       </c>
       <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>78</v>
@@ -8392,7 +8401,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8407,10 +8416,10 @@
         <v>100</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>78</v>
@@ -8421,10 +8430,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8450,16 +8459,16 @@
         <v>130</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
@@ -8469,10 +8478,10 @@
         <v>78</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>78</v>
@@ -8508,7 +8517,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8523,13 +8532,13 @@
         <v>100</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>78</v>
@@ -8537,10 +8546,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8566,13 +8575,13 @@
         <v>102</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8586,7 +8595,7 @@
         <v>78</v>
       </c>
       <c r="T56" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="U56" t="s" s="2">
         <v>78</v>
@@ -8622,7 +8631,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8637,13 +8646,13 @@
         <v>100</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>78</v>
@@ -8651,10 +8660,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8677,13 +8686,13 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8734,7 +8743,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8749,13 +8758,13 @@
         <v>100</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>78</v>
@@ -8763,10 +8772,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8789,16 +8798,16 @@
         <v>89</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8848,7 +8857,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8863,13 +8872,13 @@
         <v>100</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>78</v>
@@ -8877,13 +8886,13 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>78</v>
@@ -8905,17 +8914,17 @@
         <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>78</v>
@@ -8964,7 +8973,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8973,30 +8982,30 @@
         <v>80</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9105,10 +9114,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9219,10 +9228,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9248,16 +9257,16 @@
         <v>168</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>78</v>
@@ -9282,11 +9291,11 @@
         <v>78</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Y62" s="2"/>
       <c r="Z62" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>78</v>
@@ -9304,7 +9313,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9322,7 +9331,7 @@
         <v>191</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>78</v>
@@ -9333,10 +9342,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9359,19 +9368,19 @@
         <v>89</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>78</v>
@@ -9399,10 +9408,10 @@
         <v>150</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>78</v>
@@ -9420,7 +9429,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9435,10 +9444,10 @@
         <v>100</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>78</v>
@@ -9449,10 +9458,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9561,10 +9570,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9675,10 +9684,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9704,16 +9713,16 @@
         <v>146</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>78</v>
@@ -9762,7 +9771,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9777,10 +9786,10 @@
         <v>100</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>78</v>
@@ -9791,10 +9800,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9903,10 +9912,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10017,10 +10026,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10046,16 +10055,16 @@
         <v>130</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>78</v>
@@ -10065,7 +10074,7 @@
         <v>78</v>
       </c>
       <c r="S69" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="T69" t="s" s="2">
         <v>78</v>
@@ -10104,7 +10113,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10119,10 +10128,10 @@
         <v>100</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>78</v>
@@ -10133,10 +10142,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10162,13 +10171,13 @@
         <v>102</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10218,7 +10227,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10233,10 +10242,10 @@
         <v>100</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>78</v>
@@ -10247,10 +10256,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10276,14 +10285,14 @@
         <v>168</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -10332,7 +10341,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10347,10 +10356,10 @@
         <v>100</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>78</v>
@@ -10361,10 +10370,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10390,14 +10399,14 @@
         <v>102</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>78</v>
@@ -10446,7 +10455,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10461,10 +10470,10 @@
         <v>100</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>78</v>
@@ -10475,10 +10484,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10501,19 +10510,19 @@
         <v>89</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>78</v>
@@ -10562,7 +10571,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10577,10 +10586,10 @@
         <v>100</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>78</v>
@@ -10591,10 +10600,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10620,16 +10629,16 @@
         <v>102</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>78</v>
@@ -10678,7 +10687,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10693,10 +10702,10 @@
         <v>100</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>78</v>
@@ -10707,10 +10716,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10736,16 +10745,16 @@
         <v>130</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>78</v>
@@ -10755,10 +10764,10 @@
         <v>78</v>
       </c>
       <c r="S75" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="T75" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="U75" t="s" s="2">
         <v>78</v>
@@ -10794,7 +10803,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10809,13 +10818,13 @@
         <v>100</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>78</v>
@@ -10823,10 +10832,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10852,13 +10861,13 @@
         <v>102</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10872,7 +10881,7 @@
         <v>78</v>
       </c>
       <c r="T76" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="U76" t="s" s="2">
         <v>78</v>
@@ -10908,7 +10917,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -10923,13 +10932,13 @@
         <v>100</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>78</v>
@@ -10937,10 +10946,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10963,13 +10972,13 @@
         <v>89</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11020,7 +11029,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11035,13 +11044,13 @@
         <v>100</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>78</v>
@@ -11049,10 +11058,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11075,16 +11084,16 @@
         <v>89</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11134,7 +11143,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11149,13 +11158,13 @@
         <v>100</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>78</v>
@@ -11163,13 +11172,13 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>78</v>
@@ -11191,17 +11200,17 @@
         <v>89</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>78</v>
@@ -11250,7 +11259,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11259,30 +11268,30 @@
         <v>80</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11391,10 +11400,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11505,10 +11514,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11534,16 +11543,16 @@
         <v>168</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>78</v>
@@ -11568,11 +11577,11 @@
         <v>78</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Y82" s="2"/>
       <c r="Z82" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>78</v>
@@ -11590,7 +11599,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -11608,7 +11617,7 @@
         <v>191</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>78</v>
@@ -11619,10 +11628,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11645,19 +11654,19 @@
         <v>89</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>78</v>
@@ -11667,7 +11676,7 @@
         <v>78</v>
       </c>
       <c r="S83" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="T83" t="s" s="2">
         <v>78</v>
@@ -11686,7 +11695,7 @@
       </c>
       <c r="Y83" s="2"/>
       <c r="Z83" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>78</v>
@@ -11704,7 +11713,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -11719,10 +11728,10 @@
         <v>100</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>78</v>
@@ -11733,10 +11742,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11762,16 +11771,16 @@
         <v>130</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>78</v>
@@ -11781,10 +11790,10 @@
         <v>78</v>
       </c>
       <c r="S84" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="T84" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="U84" t="s" s="2">
         <v>78</v>
@@ -11820,7 +11829,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -11835,13 +11844,13 @@
         <v>100</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>78</v>
@@ -11849,10 +11858,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11878,13 +11887,13 @@
         <v>102</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -11898,7 +11907,7 @@
         <v>78</v>
       </c>
       <c r="T85" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="U85" t="s" s="2">
         <v>78</v>
@@ -11934,7 +11943,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -11949,13 +11958,13 @@
         <v>100</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>78</v>
@@ -11963,10 +11972,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11989,13 +11998,13 @@
         <v>89</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12046,7 +12055,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12061,13 +12070,13 @@
         <v>100</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>78</v>
@@ -12075,10 +12084,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12101,16 +12110,16 @@
         <v>89</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12160,7 +12169,7 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12175,13 +12184,13 @@
         <v>100</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>78</v>
@@ -12189,10 +12198,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12215,70 +12224,70 @@
         <v>89</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M88" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="P88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q88" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="R88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF88" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="P88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q88" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="R88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12293,24 +12302,24 @@
         <v>100</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12333,19 +12342,19 @@
         <v>89</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>78</v>
@@ -12373,16 +12382,16 @@
         <v>158</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AC89" s="2"/>
       <c r="AD89" t="s" s="2">
@@ -12392,7 +12401,7 @@
         <v>115</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12407,27 +12416,27 @@
         <v>100</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D90" t="s" s="2">
         <v>78</v>
@@ -12449,19 +12458,19 @@
         <v>89</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>78</v>
@@ -12486,11 +12495,11 @@
         <v>78</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>78</v>
@@ -12508,7 +12517,7 @@
         <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -12523,24 +12532,24 @@
         <v>100</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12649,10 +12658,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12763,10 +12772,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12792,16 +12801,16 @@
         <v>146</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>78</v>
@@ -12850,7 +12859,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -12865,10 +12874,10 @@
         <v>100</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>78</v>
@@ -12879,10 +12888,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12991,10 +13000,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13105,10 +13114,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13134,16 +13143,16 @@
         <v>130</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>78</v>
@@ -13192,7 +13201,7 @@
         <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13207,10 +13216,10 @@
         <v>100</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>78</v>
@@ -13221,10 +13230,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13250,13 +13259,13 @@
         <v>102</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13306,7 +13315,7 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13321,10 +13330,10 @@
         <v>100</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>78</v>
@@ -13335,10 +13344,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13364,14 +13373,14 @@
         <v>168</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>78</v>
@@ -13420,7 +13429,7 @@
         <v>78</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -13435,10 +13444,10 @@
         <v>100</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>78</v>
@@ -13449,10 +13458,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13478,14 +13487,14 @@
         <v>102</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>78</v>
@@ -13534,7 +13543,7 @@
         <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -13549,10 +13558,10 @@
         <v>100</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>78</v>
@@ -13563,10 +13572,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13589,19 +13598,19 @@
         <v>89</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>78</v>
@@ -13650,7 +13659,7 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -13665,10 +13674,10 @@
         <v>100</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>78</v>
@@ -13679,10 +13688,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13708,16 +13717,16 @@
         <v>102</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>78</v>
@@ -13766,7 +13775,7 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -13781,10 +13790,10 @@
         <v>100</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>78</v>
@@ -13795,13 +13804,13 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D102" t="s" s="2">
         <v>78</v>
@@ -13823,19 +13832,19 @@
         <v>89</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>78</v>
@@ -13860,11 +13869,11 @@
         <v>78</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Y102" s="2"/>
       <c r="Z102" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>78</v>
@@ -13882,7 +13891,7 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -13897,24 +13906,24 @@
         <v>100</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14023,10 +14032,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14137,10 +14146,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14166,16 +14175,16 @@
         <v>146</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>78</v>
@@ -14224,7 +14233,7 @@
         <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -14239,10 +14248,10 @@
         <v>100</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>78</v>
@@ -14253,10 +14262,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14365,10 +14374,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14479,10 +14488,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14508,16 +14517,16 @@
         <v>130</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>78</v>
@@ -14566,7 +14575,7 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -14581,10 +14590,10 @@
         <v>100</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>78</v>
@@ -14595,10 +14604,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14624,13 +14633,13 @@
         <v>102</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -14680,7 +14689,7 @@
         <v>78</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -14695,10 +14704,10 @@
         <v>100</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>78</v>
@@ -14709,10 +14718,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14738,14 +14747,14 @@
         <v>168</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>78</v>
@@ -14794,7 +14803,7 @@
         <v>78</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -14809,10 +14818,10 @@
         <v>100</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>78</v>
@@ -14823,10 +14832,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14852,14 +14861,14 @@
         <v>102</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>78</v>
@@ -14908,7 +14917,7 @@
         <v>78</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -14923,10 +14932,10 @@
         <v>100</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>78</v>
@@ -14937,10 +14946,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14963,19 +14972,19 @@
         <v>89</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>78</v>
@@ -15024,7 +15033,7 @@
         <v>78</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -15039,10 +15048,10 @@
         <v>100</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>78</v>
@@ -15053,10 +15062,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15082,16 +15091,16 @@
         <v>102</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>78</v>
@@ -15140,7 +15149,7 @@
         <v>78</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -15155,10 +15164,10 @@
         <v>100</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>78</v>
@@ -15169,13 +15178,13 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D114" t="s" s="2">
         <v>78</v>
@@ -15197,19 +15206,19 @@
         <v>89</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>78</v>
@@ -15234,11 +15243,11 @@
         <v>78</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Y114" s="2"/>
       <c r="Z114" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>78</v>
@@ -15256,7 +15265,7 @@
         <v>78</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
@@ -15271,24 +15280,24 @@
         <v>100</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15397,10 +15406,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15511,10 +15520,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15540,16 +15549,16 @@
         <v>146</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>78</v>
@@ -15598,7 +15607,7 @@
         <v>78</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
@@ -15613,10 +15622,10 @@
         <v>100</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>78</v>
@@ -15627,10 +15636,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15739,10 +15748,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15853,10 +15862,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15882,16 +15891,16 @@
         <v>130</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>78</v>
@@ -15940,7 +15949,7 @@
         <v>78</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -15955,10 +15964,10 @@
         <v>100</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>78</v>
@@ -15969,10 +15978,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15998,13 +16007,13 @@
         <v>102</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -16054,7 +16063,7 @@
         <v>78</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -16069,10 +16078,10 @@
         <v>100</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>78</v>
@@ -16083,10 +16092,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16112,14 +16121,14 @@
         <v>168</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>78</v>
@@ -16168,7 +16177,7 @@
         <v>78</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -16183,10 +16192,10 @@
         <v>100</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>78</v>
@@ -16197,10 +16206,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16226,14 +16235,14 @@
         <v>102</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>78</v>
@@ -16282,7 +16291,7 @@
         <v>78</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -16297,10 +16306,10 @@
         <v>100</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>78</v>
@@ -16311,10 +16320,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16337,19 +16346,19 @@
         <v>89</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>78</v>
@@ -16398,7 +16407,7 @@
         <v>78</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -16413,10 +16422,10 @@
         <v>100</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>78</v>
@@ -16427,10 +16436,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16456,16 +16465,16 @@
         <v>102</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>78</v>
@@ -16514,7 +16523,7 @@
         <v>78</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -16529,10 +16538,10 @@
         <v>100</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>78</v>
@@ -16543,10 +16552,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16572,16 +16581,16 @@
         <v>102</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>78</v>
@@ -16630,7 +16639,7 @@
         <v>78</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -16639,19 +16648,19 @@
         <v>88</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AJ126" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>78</v>
@@ -16659,10 +16668,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16688,16 +16697,16 @@
         <v>102</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>78</v>
@@ -16746,7 +16755,7 @@
         <v>78</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -16764,7 +16773,7 @@
         <v>78</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>78</v>
@@ -16775,10 +16784,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -16801,19 +16810,19 @@
         <v>78</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>78</v>
@@ -16862,7 +16871,7 @@
         <v>78</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -16871,19 +16880,19 @@
         <v>80</v>
       </c>
       <c r="AI128" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>78</v>
@@ -16891,10 +16900,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -16917,19 +16926,19 @@
         <v>78</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>78</v>
@@ -16978,7 +16987,7 @@
         <v>78</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
@@ -16987,19 +16996,19 @@
         <v>80</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>78</v>
@@ -17007,10 +17016,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17033,17 +17042,17 @@
         <v>89</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>78</v>
@@ -17092,7 +17101,7 @@
         <v>78</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
@@ -17107,10 +17116,10 @@
         <v>100</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AM130" t="s" s="2">
         <v>106</v>
@@ -17121,10 +17130,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17233,10 +17242,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17347,10 +17356,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17376,13 +17385,13 @@
         <v>102</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -17432,7 +17441,7 @@
         <v>78</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -17441,7 +17450,7 @@
         <v>88</v>
       </c>
       <c r="AI133" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ133" t="s" s="2">
         <v>100</v>
@@ -17461,10 +17470,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17490,13 +17499,13 @@
         <v>130</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -17526,7 +17535,7 @@
       </c>
       <c r="Y134" s="2"/>
       <c r="Z134" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>78</v>
@@ -17544,7 +17553,7 @@
         <v>78</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -17573,10 +17582,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17599,16 +17608,16 @@
         <v>89</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -17658,7 +17667,7 @@
         <v>78</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -17676,7 +17685,7 @@
         <v>78</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>78</v>
@@ -17687,10 +17696,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17716,13 +17725,13 @@
         <v>102</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -17772,7 +17781,7 @@
         <v>78</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -17801,10 +17810,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17827,19 +17836,19 @@
         <v>78</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>78</v>
@@ -17888,7 +17897,7 @@
         <v>78</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
@@ -17906,7 +17915,7 @@
         <v>78</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="AM137" t="s" s="2">
         <v>78</v>
@@ -17917,10 +17926,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18029,10 +18038,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18143,14 +18152,14 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
@@ -18172,16 +18181,16 @@
         <v>109</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="N140" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>78</v>
@@ -18230,7 +18239,7 @@
         <v>78</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
@@ -18259,10 +18268,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18285,17 +18294,17 @@
         <v>78</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>78</v>
@@ -18323,10 +18332,10 @@
         <v>150</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>78</v>
@@ -18344,7 +18353,7 @@
         <v>78</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
@@ -18362,7 +18371,7 @@
         <v>78</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AM141" t="s" s="2">
         <v>78</v>
@@ -18373,10 +18382,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18399,17 +18408,17 @@
         <v>78</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>78</v>
@@ -18458,7 +18467,7 @@
         <v>78</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
@@ -18473,10 +18482,10 @@
         <v>100</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AM142" t="s" s="2">
         <v>78</v>
@@ -18487,10 +18496,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18513,17 +18522,17 @@
         <v>78</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>78</v>
@@ -18572,7 +18581,7 @@
         <v>78</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -18587,10 +18596,10 @@
         <v>100</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="AM143" t="s" s="2">
         <v>78</v>
@@ -18601,10 +18610,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18627,17 +18636,17 @@
         <v>78</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>78</v>
@@ -18686,7 +18695,7 @@
         <v>78</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>79</v>
@@ -18701,10 +18710,10 @@
         <v>100</v>
       </c>
       <c r="AK144" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="AM144" t="s" s="2">
         <v>78</v>
@@ -18715,10 +18724,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -18741,17 +18750,17 @@
         <v>78</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>78</v>
@@ -18800,7 +18809,7 @@
         <v>78</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>79</v>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:58:46+00:00</t>
+    <t>2025-02-19T14:07:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T14:07:54+00:00</t>
+    <t>2025-02-19T14:26:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T08:11:18+00:00</t>
+    <t>2025-05-20T13:27:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:27:17+00:00</t>
+    <t>2025-05-20T13:29:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:29:42+00:00</t>
+    <t>2025-05-20T13:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5275" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5275" uniqueCount="606">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:48:39+00:00</t>
+    <t>2025-06-04T13:32:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -670,7 +670,7 @@
     <t>usePeriod</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {organization-period}
+    <t xml:space="preserve">Extension {organization-period|5.2.0}
 </t>
   </si>
   <si>
@@ -709,11 +709,11 @@
     <t>Organizations are known by a variety of ids. Some institutions maintain several, and most collect identifiers for exchange with other organizations concerning the organization.</t>
   </si>
   <si>
-    <t>pattern:system}
-pattern:type}</t>
-  </si>
-  <si>
-    <t>Slice based on the identifier.system pattern</t>
+    <t>value:system}
+value:type}</t>
+  </si>
+  <si>
+    <t>Slice based on the identifier.system #value</t>
   </si>
   <si>
     <t xml:space="preserve">org-1
@@ -1384,10 +1384,6 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/organization-type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
   </si>
   <si>
     <t>No equivalent in v2</t>
@@ -12383,7 +12379,7 @@
         <v>78</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>437</v>
+        <v>140</v>
       </c>
       <c r="AC89" s="2"/>
       <c r="AD89" t="s" s="2">
@@ -12408,27 +12404,27 @@
         <v>100</v>
       </c>
       <c r="AK89" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AL89" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="AL89" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>430</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D90" t="s" s="2">
         <v>78</v>
@@ -12491,7 +12487,7 @@
       </c>
       <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>78</v>
@@ -12524,24 +12520,24 @@
         <v>100</v>
       </c>
       <c r="AK90" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AL90" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="AL90" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="B91" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12650,10 +12646,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="B92" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12764,10 +12760,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="B93" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12880,10 +12876,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="B94" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12992,10 +12988,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="B95" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="B95" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13106,10 +13102,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="B96" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13222,10 +13218,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="B97" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13336,10 +13332,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="B98" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13365,7 +13361,7 @@
         <v>168</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="M98" t="s" s="2">
         <v>370</v>
@@ -13450,10 +13446,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="B99" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13564,10 +13560,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="B100" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13680,10 +13676,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="B101" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13796,13 +13792,13 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>430</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D102" t="s" s="2">
         <v>78</v>
@@ -13827,7 +13823,7 @@
         <v>240</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="M102" t="s" s="2">
         <v>432</v>
@@ -13865,7 +13861,7 @@
       </c>
       <c r="Y102" s="2"/>
       <c r="Z102" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>78</v>
@@ -13898,24 +13894,24 @@
         <v>100</v>
       </c>
       <c r="AK102" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AL102" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="AL102" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14024,10 +14020,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14138,10 +14134,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14254,10 +14250,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14366,10 +14362,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14480,10 +14476,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14596,10 +14592,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14710,10 +14706,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14739,7 +14735,7 @@
         <v>168</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="M110" t="s" s="2">
         <v>370</v>
@@ -14824,10 +14820,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14938,10 +14934,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15054,10 +15050,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15170,13 +15166,13 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>430</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D114" t="s" s="2">
         <v>78</v>
@@ -15201,7 +15197,7 @@
         <v>240</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="M114" t="s" s="2">
         <v>432</v>
@@ -15239,7 +15235,7 @@
       </c>
       <c r="Y114" s="2"/>
       <c r="Z114" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>78</v>
@@ -15272,24 +15268,24 @@
         <v>100</v>
       </c>
       <c r="AK114" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AL114" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="AL114" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15398,10 +15394,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15512,10 +15508,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15628,10 +15624,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15740,10 +15736,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15854,10 +15850,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15970,10 +15966,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16084,10 +16080,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16113,7 +16109,7 @@
         <v>168</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="M122" t="s" s="2">
         <v>370</v>
@@ -16198,10 +16194,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16312,10 +16308,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16428,10 +16424,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16544,10 +16540,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16573,16 +16569,16 @@
         <v>102</v>
       </c>
       <c r="L126" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M126" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="M126" t="s" s="2">
+      <c r="N126" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="N126" t="s" s="2">
+      <c r="O126" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="O126" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>78</v>
@@ -16631,7 +16627,7 @@
         <v>78</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -16646,13 +16642,13 @@
         <v>100</v>
       </c>
       <c r="AK126" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AL126" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="AL126" t="s" s="2">
+      <c r="AM126" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="AM126" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>78</v>
@@ -16660,10 +16656,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16689,16 +16685,16 @@
         <v>102</v>
       </c>
       <c r="L127" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M127" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="M127" t="s" s="2">
+      <c r="N127" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="N127" t="s" s="2">
+      <c r="O127" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>78</v>
@@ -16747,7 +16743,7 @@
         <v>78</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -16765,7 +16761,7 @@
         <v>78</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>78</v>
@@ -16776,10 +16772,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -16802,19 +16798,19 @@
         <v>78</v>
       </c>
       <c r="K128" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="L128" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="L128" t="s" s="2">
+      <c r="M128" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="M128" t="s" s="2">
+      <c r="N128" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="N128" t="s" s="2">
+      <c r="O128" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>78</v>
@@ -16863,7 +16859,7 @@
         <v>78</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -16872,19 +16868,19 @@
         <v>80</v>
       </c>
       <c r="AI128" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AJ128" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="AJ128" t="s" s="2">
+      <c r="AK128" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="AK128" t="s" s="2">
+      <c r="AL128" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="AL128" t="s" s="2">
+      <c r="AM128" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="AM128" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>78</v>
@@ -16892,10 +16888,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -16918,19 +16914,19 @@
         <v>78</v>
       </c>
       <c r="K129" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="L129" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="L129" t="s" s="2">
+      <c r="M129" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="M129" t="s" s="2">
+      <c r="N129" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="N129" t="s" s="2">
+      <c r="O129" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="O129" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>78</v>
@@ -16979,7 +16975,7 @@
         <v>78</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
@@ -16988,19 +16984,19 @@
         <v>80</v>
       </c>
       <c r="AI129" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AJ129" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="AJ129" t="s" s="2">
+      <c r="AK129" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="AK129" t="s" s="2">
+      <c r="AL129" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="AL129" t="s" s="2">
+      <c r="AM129" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="AM129" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>78</v>
@@ -17008,10 +17004,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17034,17 +17030,17 @@
         <v>89</v>
       </c>
       <c r="K130" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="L130" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="L130" t="s" s="2">
+      <c r="M130" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>535</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>78</v>
@@ -17093,7 +17089,7 @@
         <v>78</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
@@ -17111,7 +17107,7 @@
         <v>426</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="AM130" t="s" s="2">
         <v>106</v>
@@ -17122,10 +17118,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17234,10 +17230,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17348,10 +17344,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17377,13 +17373,13 @@
         <v>102</v>
       </c>
       <c r="L133" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="M133" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="M133" t="s" s="2">
+      <c r="N133" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -17433,16 +17429,16 @@
         <v>78</v>
       </c>
       <c r="AF133" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="AG133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH133" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI133" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="AG133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH133" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI133" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="AJ133" t="s" s="2">
         <v>100</v>
@@ -17462,10 +17458,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17491,13 +17487,13 @@
         <v>130</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="M134" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="M134" t="s" s="2">
+      <c r="N134" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>549</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -17527,7 +17523,7 @@
       </c>
       <c r="Y134" s="2"/>
       <c r="Z134" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>78</v>
@@ -17545,7 +17541,7 @@
         <v>78</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -17574,10 +17570,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17603,13 +17599,13 @@
         <v>217</v>
       </c>
       <c r="L135" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M135" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="M135" t="s" s="2">
+      <c r="N135" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -17659,7 +17655,7 @@
         <v>78</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -17677,7 +17673,7 @@
         <v>78</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>78</v>
@@ -17688,10 +17684,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17717,13 +17713,13 @@
         <v>102</v>
       </c>
       <c r="L136" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="M136" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="M136" t="s" s="2">
+      <c r="N136" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -17773,7 +17769,7 @@
         <v>78</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -17802,10 +17798,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17828,19 +17824,19 @@
         <v>78</v>
       </c>
       <c r="K137" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="L137" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="L137" t="s" s="2">
+      <c r="M137" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="M137" t="s" s="2">
+      <c r="N137" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="N137" t="s" s="2">
+      <c r="O137" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="O137" t="s" s="2">
-        <v>567</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>78</v>
@@ -17889,7 +17885,7 @@
         <v>78</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
@@ -17907,7 +17903,7 @@
         <v>78</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AM137" t="s" s="2">
         <v>78</v>
@@ -17918,10 +17914,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18030,10 +18026,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18144,14 +18140,14 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
@@ -18173,10 +18169,10 @@
         <v>109</v>
       </c>
       <c r="L140" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M140" t="s" s="2">
         <v>573</v>
-      </c>
-      <c r="M140" t="s" s="2">
-        <v>574</v>
       </c>
       <c r="N140" t="s" s="2">
         <v>112</v>
@@ -18231,7 +18227,7 @@
         <v>78</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
@@ -18260,10 +18256,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18289,14 +18285,14 @@
         <v>240</v>
       </c>
       <c r="L141" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="M141" t="s" s="2">
         <v>577</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>578</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>78</v>
@@ -18324,11 +18320,11 @@
         <v>150</v>
       </c>
       <c r="Y141" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="Z141" t="s" s="2">
         <v>580</v>
       </c>
-      <c r="Z141" t="s" s="2">
-        <v>581</v>
-      </c>
       <c r="AA141" t="s" s="2">
         <v>78</v>
       </c>
@@ -18345,7 +18341,7 @@
         <v>78</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
@@ -18363,7 +18359,7 @@
         <v>78</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AM141" t="s" s="2">
         <v>78</v>
@@ -18374,10 +18370,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18400,17 +18396,17 @@
         <v>78</v>
       </c>
       <c r="K142" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="L142" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="L142" t="s" s="2">
+      <c r="M142" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="M142" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>78</v>
@@ -18459,7 +18455,7 @@
         <v>78</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
@@ -18474,10 +18470,10 @@
         <v>100</v>
       </c>
       <c r="AK142" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AL142" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="AL142" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="AM142" t="s" s="2">
         <v>78</v>
@@ -18488,10 +18484,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18514,17 +18510,17 @@
         <v>78</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="L143" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="M143" t="s" s="2">
         <v>591</v>
-      </c>
-      <c r="M143" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>78</v>
@@ -18573,7 +18569,7 @@
         <v>78</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -18588,10 +18584,10 @@
         <v>100</v>
       </c>
       <c r="AK143" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="AL143" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="AL143" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="AM143" t="s" s="2">
         <v>78</v>
@@ -18602,10 +18598,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18628,17 +18624,17 @@
         <v>78</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L144" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="M144" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="M144" t="s" s="2">
-        <v>598</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>78</v>
@@ -18687,7 +18683,7 @@
         <v>78</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>79</v>
@@ -18702,10 +18698,10 @@
         <v>100</v>
       </c>
       <c r="AK144" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="AL144" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="AL144" t="s" s="2">
-        <v>601</v>
       </c>
       <c r="AM144" t="s" s="2">
         <v>78</v>
@@ -18716,10 +18712,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -18742,17 +18738,17 @@
         <v>78</v>
       </c>
       <c r="K145" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="L145" t="s" s="2">
         <v>603</v>
       </c>
-      <c r="L145" t="s" s="2">
+      <c r="M145" t="s" s="2">
         <v>604</v>
-      </c>
-      <c r="M145" t="s" s="2">
-        <v>605</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>78</v>
@@ -18801,7 +18797,7 @@
         <v>78</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>79</v>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-04T13:32:30+00:00</t>
+    <t>2025-06-24T17:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24T17:01:22+00:00</t>
+    <t>2025-07-04T12:19:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04T12:19:33+00:00</t>
+    <t>2025-07-08T13:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-08T13:28:39+00:00</t>
+    <t>2025-07-16T09:34:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-16T09:34:35+00:00</t>
+    <t>2025-07-30T14:55:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-30T14:55:53+00:00</t>
+    <t>2025-10-08T07:32:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -670,7 +670,7 @@
     <t>usePeriod</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {organization-period|5.2.0}
+    <t xml:space="preserve">Extension {organization-period|5.3.0-ballot-tc1}
 </t>
   </si>
   <si>
@@ -4638,7 +4638,7 @@
         <v>80</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>78</v>
+        <v>201</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>117</v>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T07:32:57+00:00</t>
+    <t>2025-10-08T12:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T12:04:30+00:00</t>
+    <t>2025-10-08T16:01:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:25:45+00:00</t>
+    <t>2026-02-04T13:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T13:09:39+00:00</t>
+    <t>2026-02-09T06:47:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T06:47:58+00:00</t>
+    <t>2026-02-11T16:15:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -698,10 +698,10 @@
     <t>closureReason</t>
   </si>
   <si>
-    <t>Organization.extension:members</t>
-  </si>
-  <si>
-    <t>members</t>
+    <t>Organization.extension:member</t>
+  </si>
+  <si>
+    <t>member</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-member|2.2.0-ballot-2}

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T16:15:37+00:00</t>
+    <t>2026-02-17T10:02:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T10:02:14+00:00</t>
+    <t>2026-02-23T09:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T09:26:22+00:00</t>
+    <t>2026-02-23T10:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T10:39:10+00:00</t>
+    <t>2026-02-23T12:56:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T07:09:47+00:00</t>
+    <t>2026-03-25T10:22:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:11+00:00</t>
+    <t>2026-03-25T10:22:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:40+00:00</t>
+    <t>2026-03-25T10:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:25:13+00:00</t>
+    <t>2026-03-25T15:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T15:00:47+00:00</t>
+    <t>2026-03-31T09:16:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1775" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="371">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T09:16:18+00:00</t>
+    <t>2026-05-07T06:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -653,14 +653,18 @@
     <t>description</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-Organization.description}
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-Organization.description|0.1.0}
 </t>
   </si>
   <si>
-    <t>Optional Extensions Element</t>
-  </si>
-  <si>
-    <t>Optional Extension Element - found in all resources.</t>
+    <t>R5: Additional details about the Organization that could be displayed as further information to identify the Organization beyond its name (new)</t>
+  </si>
+  <si>
+    <t>R5: `Organization.description` (new:markdown)</t>
+  </si>
+  <si>
+    <t>Element `Organization.description` has a context of Organization based on following the parent source element upwards and mapping to `Organization`.
+Element `Organization.description` has no mapping targets in FHIR R4. Typically, this is because the element has been added (is a new element).</t>
   </si>
   <si>
     <t>Organization.extension:usePeriod</t>
@@ -3733,7 +3737,9 @@
       <c r="M20" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="N20" s="2"/>
+      <c r="N20" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>78</v>
@@ -3800,7 +3806,7 @@
         <v>78</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>192</v>
+        <v>78</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>78</v>
@@ -3811,13 +3817,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>193</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>78</v>
@@ -3839,13 +3845,13 @@
         <v>78</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>194</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3925,13 +3931,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>193</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>78</v>
@@ -3953,16 +3959,16 @@
         <v>78</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4041,13 +4047,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>193</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>78</v>
@@ -4069,16 +4075,16 @@
         <v>78</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4157,13 +4163,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>193</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>78</v>
@@ -4185,13 +4191,13 @@
         <v>78</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4271,10 +4277,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4300,16 +4306,16 @@
         <v>109</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N25" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>78</v>
@@ -4358,7 +4364,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4387,10 +4393,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4413,17 +4419,17 @@
         <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>78</v>
@@ -4472,7 +4478,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4481,30 +4487,30 @@
         <v>80</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4527,70 +4533,70 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="P27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q27" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="R27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="P27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q27" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="R27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4605,24 +4611,24 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4645,19 +4651,19 @@
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>78</v>
@@ -4686,7 +4692,7 @@
       </c>
       <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>78</v>
@@ -4704,7 +4710,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4719,24 +4725,24 @@
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4762,16 +4768,16 @@
         <v>102</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>78</v>
@@ -4820,7 +4826,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -4829,19 +4835,19 @@
         <v>88</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>78</v>
@@ -4849,10 +4855,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4878,16 +4884,16 @@
         <v>102</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>78</v>
@@ -4936,7 +4942,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -4954,7 +4960,7 @@
         <v>78</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>78</v>
@@ -4965,10 +4971,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4991,19 +4997,19 @@
         <v>78</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>78</v>
@@ -5052,7 +5058,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5061,19 +5067,19 @@
         <v>80</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>78</v>
@@ -5081,10 +5087,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5107,19 +5113,19 @@
         <v>78</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>78</v>
@@ -5168,7 +5174,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5177,19 +5183,19 @@
         <v>80</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>78</v>
@@ -5197,10 +5203,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5223,17 +5229,17 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>78</v>
@@ -5282,7 +5288,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5297,10 +5303,10 @@
         <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>106</v>
@@ -5311,10 +5317,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5423,10 +5429,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5537,10 +5543,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5566,13 +5572,13 @@
         <v>102</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5622,7 +5628,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5631,7 +5637,7 @@
         <v>88</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>100</v>
@@ -5651,10 +5657,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5680,13 +5686,13 @@
         <v>130</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5716,7 +5722,7 @@
       </c>
       <c r="Y37" s="2"/>
       <c r="Z37" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>78</v>
@@ -5734,7 +5740,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5763,10 +5769,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5789,16 +5795,16 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5848,7 +5854,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -5866,7 +5872,7 @@
         <v>78</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>78</v>
@@ -5877,10 +5883,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5906,13 +5912,13 @@
         <v>102</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5962,7 +5968,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -5991,10 +5997,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6017,19 +6023,19 @@
         <v>78</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>78</v>
@@ -6078,7 +6084,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6096,7 +6102,7 @@
         <v>78</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>78</v>
@@ -6107,10 +6113,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6219,10 +6225,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6333,14 +6339,14 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6362,16 +6368,16 @@
         <v>109</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>78</v>
@@ -6420,7 +6426,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6449,10 +6455,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6475,17 +6481,17 @@
         <v>78</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>78</v>
@@ -6513,10 +6519,10 @@
         <v>151</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>78</v>
@@ -6534,7 +6540,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6552,7 +6558,7 @@
         <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>78</v>
@@ -6563,10 +6569,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6589,17 +6595,17 @@
         <v>78</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>78</v>
@@ -6648,7 +6654,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6663,10 +6669,10 @@
         <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
@@ -6677,10 +6683,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6703,17 +6709,17 @@
         <v>78</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>78</v>
@@ -6762,7 +6768,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -6777,10 +6783,10 @@
         <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>78</v>
@@ -6791,10 +6797,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6817,17 +6823,17 @@
         <v>78</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>78</v>
@@ -6876,7 +6882,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -6891,10 +6897,10 @@
         <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>78</v>
@@ -6905,10 +6911,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6931,17 +6937,17 @@
         <v>78</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>78</v>
@@ -6990,7 +6996,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T13:50:40+00:00</t>
+    <t>2026-05-27T14:53:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T14:53:55+00:00</t>
+    <t>2026-05-28T14:22:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T14:22:24+00:00</t>
+    <t>2026-06-12T14:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:04:24+00:00</t>
+    <t>2026-06-12T14:05:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Organization|4.0.1</t>
+    <t>http://hl7.eu/fhir/base/StructureDefinition/organization-eu-core|2.0.0</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -269,7 +269,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}org-1:The organization SHALL at least have a name or an identifier, and possibly more than one {(identifier.count() + name.count()) &gt; 0}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}org-1:The organization SHALL at least have a name or an identifier, and possibly more than one {(identifier.count() + name.count()) &gt; 0}name-or-identifier:identifier or name SHALL be present {identifier.exists() or name.exists()}</t>
   </si>
   <si>
     <t>(also see master files messages)</t>
@@ -741,7 +741,7 @@
 </t>
   </si>
   <si>
-    <t>Identifies this organization  across multiple systems</t>
+    <t>Organization business identifier</t>
   </si>
   <si>
     <t>Identifier for the organization that is used to identify the organization across multiple disparate systems.</t>
@@ -808,7 +808,7 @@
 </t>
   </si>
   <si>
-    <t>Kind of organization</t>
+    <t>Organization type</t>
   </si>
   <si>
     <t>The kind(s) of organization that this is.</t>
@@ -837,7 +837,7 @@
     <t>Organization.name</t>
   </si>
   <si>
-    <t>Name used for the organization</t>
+    <t>Name of the organization</t>
   </si>
   <si>
     <t>A name associated with the organization.</t>
@@ -881,7 +881,7 @@
 </t>
   </si>
   <si>
-    <t>A contact detail for the organization</t>
+    <t>Organization telecom</t>
   </si>
   <si>
     <t>A contact detail for the organization.</t>
@@ -953,7 +953,7 @@
 </t>
   </si>
   <si>
-    <t>The organization of which this organization forms a part</t>
+    <t>The organization of which this organization is part of: e.g. an ERN</t>
   </si>
   <si>
     <t>The organization of which this organization forms a part.</t>
@@ -1049,7 +1049,7 @@
 </t>
   </si>
   <si>
-    <t>Contact for the organization for a certain purpose</t>
+    <t>Organization contact infos</t>
   </si>
   <si>
     <t>Contact for the organization for a certain purpose.</t>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>88</v>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:05:00+00:00</t>
+    <t>2026-06-12T14:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:35:23+00:00</t>
+    <t>2026-06-26T12:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T12:32:04+00:00</t>
+    <t>2026-06-29T09:30:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T09:30:52+00:00</t>
+    <t>2026-07-22T12:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T12:21:07+00:00</t>
+    <t>2026-07-27T15:02:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:02:31+00:00</t>
+    <t>2026-08-03T12:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T12:52:25+00:00</t>
+    <t>2026-08-04T12:22:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:22:31+00:00</t>
+    <t>2026-08-04T12:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:29:23+00:00</t>
+    <t>2026-08-10T16:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
